--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C538997E-0B7F-448F-913A-70319C65E301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9C3E0B-65AD-4CA4-88E5-0AC0C7D41784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1328,15 +1328,15 @@
         <v>5.2171046655269393E-3</v>
       </c>
       <c r="F57" s="7">
-        <f>0.76/1000</f>
-        <v>7.6000000000000004E-4</v>
+        <f>0.75/1000</f>
+        <v>7.5000000000000002E-4</v>
       </c>
       <c r="G57" s="1">
         <v>500</v>
       </c>
       <c r="H57" s="8">
         <f>F57 * G57</f>
-        <v>0.38</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -1357,15 +1357,15 @@
         <v>2.5060693811106649E-2</v>
       </c>
       <c r="F58" s="5">
-        <f>5.97/1000</f>
-        <v>5.9699999999999996E-3</v>
+        <f>6.11/1000</f>
+        <v>6.11E-3</v>
       </c>
       <c r="G58" s="1">
         <v>2000</v>
       </c>
       <c r="H58" s="8">
         <f t="shared" ref="H58:H61" si="0">F58 * G58</f>
-        <v>11.94</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -1386,15 +1386,15 @@
         <v>1.3665389109177362E-2</v>
       </c>
       <c r="F59" s="5">
-        <f>19.6/1000</f>
-        <v>1.9600000000000003E-2</v>
+        <f>19.62/1000</f>
+        <v>1.9620000000000002E-2</v>
       </c>
       <c r="G59" s="1">
         <v>2000</v>
       </c>
       <c r="H59" s="8">
         <f t="shared" si="0"/>
-        <v>39.200000000000003</v>
+        <v>39.24</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -1415,15 +1415,15 @@
         <v>9.946659262648927E-3</v>
       </c>
       <c r="F60" s="5">
-        <f>31.7/1000</f>
-        <v>3.1699999999999999E-2</v>
+        <f>32.19/1000</f>
+        <v>3.2189999999999996E-2</v>
       </c>
       <c r="G60" s="1">
         <v>2000</v>
       </c>
       <c r="H60" s="8">
         <f t="shared" si="0"/>
-        <v>63.4</v>
+        <v>64.38</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -1444,15 +1444,15 @@
         <v>2.7902941770217238E-2</v>
       </c>
       <c r="F61" s="5">
-        <f>57.52/1000</f>
-        <v>5.7520000000000002E-2</v>
+        <f>57.23/1000</f>
+        <v>5.7229999999999996E-2</v>
       </c>
       <c r="G61" s="1">
         <v>3000</v>
       </c>
       <c r="H61" s="8">
         <f t="shared" si="0"/>
-        <v>172.56</v>
+        <v>171.69</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -2763,22 +2763,22 @@
         <v>820</v>
       </c>
       <c r="D62" s="4">
-        <v>857.32013229646702</v>
+        <v>845.23167763420201</v>
       </c>
       <c r="E62" s="3">
         <f>D62/C62-1</f>
-        <v>4.5512356459106229E-2</v>
+        <v>3.0770338578295142E-2</v>
       </c>
       <c r="F62" s="7">
-        <f>2.29/1000</f>
-        <v>2.2899999999999999E-3</v>
+        <f>2.41/1000</f>
+        <v>2.4100000000000002E-3</v>
       </c>
       <c r="G62" s="1">
         <v>2000</v>
       </c>
       <c r="H62" s="8">
         <f>F62 * G62</f>
-        <v>4.58</v>
+        <v>4.82</v>
       </c>
       <c r="O62" s="14"/>
       <c r="P62" s="13"/>
@@ -2799,22 +2799,22 @@
         <v>3055.23</v>
       </c>
       <c r="D63" s="6">
-        <v>3458.5418803481598</v>
+        <v>3342.8548214203502</v>
       </c>
       <c r="E63" s="3">
         <f>D63/C63-1</f>
-        <v>0.13200704377351613</v>
+        <v>9.4141790117388879E-2</v>
       </c>
       <c r="F63" s="5">
-        <f>5.2/1000</f>
-        <v>5.1999999999999998E-3</v>
+        <f>5.28/1000</f>
+        <v>5.28E-3</v>
       </c>
       <c r="G63" s="1">
         <v>2000</v>
       </c>
       <c r="H63" s="8">
         <f t="shared" ref="H63:H66" si="0">F63 * G63</f>
-        <v>10.4</v>
+        <v>10.56</v>
       </c>
       <c r="O63" s="14"/>
       <c r="P63" s="13"/>
@@ -2835,22 +2835,22 @@
         <v>1395.85</v>
       </c>
       <c r="D64" s="4">
-        <v>1340.8187396820399</v>
+        <v>1340.19152350836</v>
       </c>
       <c r="E64" s="3">
         <f>D64/C64-1</f>
-        <v>-3.9424909781108242E-2</v>
+        <v>-3.9874253316359187E-2</v>
       </c>
       <c r="F64" s="5">
-        <f>6.8/1000</f>
-        <v>6.7999999999999996E-3</v>
+        <f>7.04/1000</f>
+        <v>7.0400000000000003E-3</v>
       </c>
       <c r="G64" s="1">
         <v>2000</v>
       </c>
       <c r="H64" s="8">
         <f t="shared" si="0"/>
-        <v>13.6</v>
+        <v>14.08</v>
       </c>
       <c r="O64" s="14"/>
       <c r="P64" s="13"/>
@@ -2871,22 +2871,22 @@
         <v>38684</v>
       </c>
       <c r="D65" s="4">
-        <v>42198.859919729897</v>
+        <v>41967.858722036399</v>
       </c>
       <c r="E65" s="3">
         <f>D65/C65-1</f>
-        <v>9.0860818936250087E-2</v>
+        <v>8.4889326906121276E-2</v>
       </c>
       <c r="F65" s="5">
-        <f>10.04/1000</f>
-        <v>1.0039999999999999E-2</v>
+        <f>10.53/1000</f>
+        <v>1.0529999999999999E-2</v>
       </c>
       <c r="G65" s="1">
         <v>3000</v>
       </c>
       <c r="H65" s="8">
         <f t="shared" si="0"/>
-        <v>30.119999999999997</v>
+        <v>31.59</v>
       </c>
       <c r="O65" s="14"/>
       <c r="P65" s="13"/>
@@ -2907,22 +2907,22 @@
         <v>21736</v>
       </c>
       <c r="D66" s="6">
-        <v>22888.403861594299</v>
+        <v>22609.381084000699</v>
       </c>
       <c r="E66" s="3">
         <f>D66/C66-1</f>
-        <v>5.3018212255902641E-2</v>
+        <v>4.018131597353225E-2</v>
       </c>
       <c r="F66" s="5">
-        <f>12.96/1000</f>
-        <v>1.2960000000000001E-2</v>
+        <f>13.22/1000</f>
+        <v>1.3220000000000001E-2</v>
       </c>
       <c r="G66" s="1">
         <v>4000</v>
       </c>
       <c r="H66" s="1">
         <f t="shared" si="0"/>
-        <v>51.84</v>
+        <v>52.88</v>
       </c>
       <c r="O66" s="14"/>
       <c r="P66" s="13"/>

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9C3E0B-65AD-4CA4-88E5-0AC0C7D41784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECDD440-5C61-4C2D-AEF8-747020BE2B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1328,15 +1328,15 @@
         <v>5.2171046655269393E-3</v>
       </c>
       <c r="F57" s="7">
-        <f>0.75/1000</f>
-        <v>7.5000000000000002E-4</v>
+        <f>0.78/1000</f>
+        <v>7.7999999999999999E-4</v>
       </c>
       <c r="G57" s="1">
         <v>500</v>
       </c>
       <c r="H57" s="8">
         <f>F57 * G57</f>
-        <v>0.375</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -1350,22 +1350,22 @@
         <v>629</v>
       </c>
       <c r="D58" s="6">
-        <v>644.76317640718605</v>
+        <v>646.49116064890904</v>
       </c>
       <c r="E58" s="3">
         <f>D58/C58-1</f>
-        <v>2.5060693811106649E-2</v>
+        <v>2.7807886564243267E-2</v>
       </c>
       <c r="F58" s="5">
-        <f>6.11/1000</f>
-        <v>6.11E-3</v>
+        <f>6.43/1000</f>
+        <v>6.43E-3</v>
       </c>
       <c r="G58" s="1">
         <v>2000</v>
       </c>
       <c r="H58" s="8">
         <f t="shared" ref="H58:H61" si="0">F58 * G58</f>
-        <v>12.22</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -1379,22 +1379,22 @@
         <v>6528</v>
       </c>
       <c r="D59" s="4">
-        <v>6617.2076601047102</v>
+        <v>6620.7322578128596</v>
       </c>
       <c r="E59" s="3">
         <f>D59/C59-1</f>
-        <v>1.3665389109177362E-2</v>
+        <v>1.4205309101234631E-2</v>
       </c>
       <c r="F59" s="5">
-        <f>19.62/1000</f>
-        <v>1.9620000000000002E-2</v>
+        <f>19.68/1000</f>
+        <v>1.968E-2</v>
       </c>
       <c r="G59" s="1">
         <v>2000</v>
       </c>
       <c r="H59" s="8">
         <f t="shared" si="0"/>
-        <v>39.24</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -1408,22 +1408,22 @@
         <v>15780</v>
       </c>
       <c r="D60" s="4">
-        <v>15936.9582831646</v>
+        <v>15854.0921222711</v>
       </c>
       <c r="E60" s="3">
         <f t="shared" ref="E60:E61" si="1">D60/C60-1</f>
-        <v>9.946659262648927E-3</v>
+        <v>4.6953182681306327E-3</v>
       </c>
       <c r="F60" s="5">
-        <f>32.19/1000</f>
-        <v>3.2189999999999996E-2</v>
+        <f>32.82/1000</f>
+        <v>3.2820000000000002E-2</v>
       </c>
       <c r="G60" s="1">
         <v>2000</v>
       </c>
       <c r="H60" s="8">
         <f t="shared" si="0"/>
-        <v>64.38</v>
+        <v>65.64</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -1437,22 +1437,22 @@
         <v>2579</v>
       </c>
       <c r="D61" s="4">
-        <v>2650.9616868253902</v>
+        <v>2632.02609627523</v>
       </c>
       <c r="E61" s="3">
         <f t="shared" si="1"/>
-        <v>2.7902941770217238E-2</v>
+        <v>2.0560719765502222E-2</v>
       </c>
       <c r="F61" s="5">
-        <f>57.23/1000</f>
-        <v>5.7229999999999996E-2</v>
+        <f>59.69/1000</f>
+        <v>5.969E-2</v>
       </c>
       <c r="G61" s="1">
         <v>3000</v>
       </c>
       <c r="H61" s="8">
         <f t="shared" si="0"/>
-        <v>171.69</v>
+        <v>179.07</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -2763,22 +2763,22 @@
         <v>820</v>
       </c>
       <c r="D62" s="4">
-        <v>845.23167763420201</v>
+        <v>820.92130148221202</v>
       </c>
       <c r="E62" s="3">
         <f>D62/C62-1</f>
-        <v>3.0770338578295142E-2</v>
+        <v>1.1235383929415477E-3</v>
       </c>
       <c r="F62" s="7">
-        <f>2.41/1000</f>
-        <v>2.4100000000000002E-3</v>
+        <f>2.22/1000</f>
+        <v>2.2200000000000002E-3</v>
       </c>
       <c r="G62" s="1">
         <v>2000</v>
       </c>
       <c r="H62" s="8">
         <f>F62 * G62</f>
-        <v>4.82</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="O62" s="14"/>
       <c r="P62" s="13"/>
@@ -2799,22 +2799,22 @@
         <v>3055.23</v>
       </c>
       <c r="D63" s="6">
-        <v>3342.8548214203502</v>
+        <v>3272.5263592587498</v>
       </c>
       <c r="E63" s="3">
         <f>D63/C63-1</f>
-        <v>9.4141790117388879E-2</v>
+        <v>7.1122749926764817E-2</v>
       </c>
       <c r="F63" s="5">
-        <f>5.28/1000</f>
-        <v>5.28E-3</v>
+        <f>6.16/1000</f>
+        <v>6.1600000000000005E-3</v>
       </c>
       <c r="G63" s="1">
         <v>2000</v>
       </c>
       <c r="H63" s="8">
         <f t="shared" ref="H63:H66" si="0">F63 * G63</f>
-        <v>10.56</v>
+        <v>12.32</v>
       </c>
       <c r="O63" s="14"/>
       <c r="P63" s="13"/>
@@ -2835,22 +2835,22 @@
         <v>1395.85</v>
       </c>
       <c r="D64" s="4">
-        <v>1340.19152350836</v>
+        <v>1355.0913447805201</v>
       </c>
       <c r="E64" s="3">
         <f>D64/C64-1</f>
-        <v>-3.9874253316359187E-2</v>
+        <v>-2.9199881949693585E-2</v>
       </c>
       <c r="F64" s="5">
-        <f>7.04/1000</f>
-        <v>7.0400000000000003E-3</v>
+        <f>7.84/1000</f>
+        <v>7.8399999999999997E-3</v>
       </c>
       <c r="G64" s="1">
         <v>2000</v>
       </c>
       <c r="H64" s="8">
         <f t="shared" si="0"/>
-        <v>14.08</v>
+        <v>15.68</v>
       </c>
       <c r="O64" s="14"/>
       <c r="P64" s="13"/>
@@ -2871,22 +2871,22 @@
         <v>38684</v>
       </c>
       <c r="D65" s="4">
-        <v>41967.858722036399</v>
+        <v>42456.203201111501</v>
       </c>
       <c r="E65" s="3">
         <f>D65/C65-1</f>
-        <v>8.4889326906121276E-2</v>
+        <v>9.7513266495489193E-2</v>
       </c>
       <c r="F65" s="5">
-        <f>10.53/1000</f>
-        <v>1.0529999999999999E-2</v>
+        <f>11.09/1000</f>
+        <v>1.1089999999999999E-2</v>
       </c>
       <c r="G65" s="1">
         <v>3000</v>
       </c>
       <c r="H65" s="8">
         <f t="shared" si="0"/>
-        <v>31.59</v>
+        <v>33.269999999999996</v>
       </c>
       <c r="O65" s="14"/>
       <c r="P65" s="13"/>
@@ -2907,22 +2907,22 @@
         <v>21736</v>
       </c>
       <c r="D66" s="6">
-        <v>22609.381084000699</v>
+        <v>22991.7161969519</v>
       </c>
       <c r="E66" s="3">
         <f>D66/C66-1</f>
-        <v>4.018131597353225E-2</v>
+        <v>5.7771264121820876E-2</v>
       </c>
       <c r="F66" s="5">
-        <f>13.22/1000</f>
-        <v>1.3220000000000001E-2</v>
+        <f>15.43/1000</f>
+        <v>1.5429999999999999E-2</v>
       </c>
       <c r="G66" s="1">
         <v>4000</v>
       </c>
       <c r="H66" s="1">
         <f t="shared" si="0"/>
-        <v>52.88</v>
+        <v>61.72</v>
       </c>
       <c r="O66" s="14"/>
       <c r="P66" s="13"/>

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F5BF56-71D6-40F8-8A8F-0B9812F33C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F04969-69D9-418E-BE12-30B9C6A50C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="3690" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5445" yWindow="4950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VRPTW Benchmarking" sheetId="1" r:id="rId1"/>
@@ -1713,15 +1713,15 @@
         <v>6.0679091434630017E-3</v>
       </c>
       <c r="F65" s="5">
-        <f>4.43/1000</f>
-        <v>4.4299999999999999E-3</v>
+        <f>4.42/1000</f>
+        <v>4.4200000000000003E-3</v>
       </c>
       <c r="G65" s="1">
         <v>2000</v>
       </c>
       <c r="H65" s="6">
         <f>F65 * G65</f>
-        <v>8.86</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -1742,15 +1742,15 @@
         <v>-2.4680298313238036E-2</v>
       </c>
       <c r="F66" s="4">
-        <f>14.93/1000</f>
-        <v>1.4930000000000001E-2</v>
+        <f>14.74/1000</f>
+        <v>1.474E-2</v>
       </c>
       <c r="G66" s="1">
         <v>2000</v>
       </c>
       <c r="H66" s="6">
         <f t="shared" ref="H66:H70" si="1">F66 * G66</f>
-        <v>29.86</v>
+        <v>29.48</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -1771,15 +1771,15 @@
         <v>-3.7795947102070571E-6</v>
       </c>
       <c r="F67" s="4">
-        <f>5.92/1000</f>
-        <v>5.9199999999999999E-3</v>
+        <f>5.91/1000</f>
+        <v>5.9100000000000003E-3</v>
       </c>
       <c r="G67" s="1">
         <v>2000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" si="1"/>
-        <v>11.84</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -1800,15 +1800,15 @@
         <v>-5.8207624822337323E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>23.85/1000</f>
-        <v>2.3850000000000003E-2</v>
+        <f>23.8/1000</f>
+        <v>2.3800000000000002E-2</v>
       </c>
       <c r="G68" s="1">
         <v>2000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -1829,15 +1829,15 @@
         <v>7.1676315548516722E-3</v>
       </c>
       <c r="F69" s="4">
-        <f>4.87/1000</f>
-        <v>4.8700000000000002E-3</v>
+        <f>4.88/1000</f>
+        <v>4.8799999999999998E-3</v>
       </c>
       <c r="G69" s="1">
         <v>2000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>9.74</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -1858,15 +1858,15 @@
         <v>-1.7050732349624509E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>9.01/1000</f>
-        <v>9.0100000000000006E-3</v>
+        <f>14.58/1000</f>
+        <v>1.4579999999999999E-2</v>
       </c>
       <c r="G70" s="1">
         <v>2000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>18.02</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F04969-69D9-418E-BE12-30B9C6A50C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D9240E-2814-4FD2-B704-5D24527C08CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5445" yWindow="4950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VRPTW Benchmarking" sheetId="1" r:id="rId1"/>
@@ -1706,22 +1706,22 @@
         <v>1645.79</v>
       </c>
       <c r="D65" s="6">
-        <v>1655.7765041892201</v>
+        <v>1671.24036467372</v>
       </c>
       <c r="E65" s="3">
         <f>D65/C65-1</f>
-        <v>6.0679091434630017E-3</v>
+        <v>1.5463919864454168E-2</v>
       </c>
       <c r="F65" s="5">
-        <f>4.42/1000</f>
-        <v>4.4200000000000003E-3</v>
+        <f>5.4/1000</f>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="G65" s="1">
         <v>2000</v>
       </c>
       <c r="H65" s="6">
         <f>F65 * G65</f>
-        <v>8.84</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -1735,22 +1735,22 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="D66" s="24">
-        <v>1221.46113480145</v>
+        <v>1224.5023993416801</v>
       </c>
       <c r="E66" s="3">
         <f t="shared" ref="E66:E70" si="0">D66/C66-1</f>
-        <v>-2.4680298313238036E-2</v>
+        <v>-2.2251890941430874E-2</v>
       </c>
       <c r="F66" s="4">
-        <f>14.74/1000</f>
-        <v>1.474E-2</v>
+        <f>16.66/1000</f>
+        <v>1.6660000000000001E-2</v>
       </c>
       <c r="G66" s="1">
         <v>2000</v>
       </c>
       <c r="H66" s="6">
         <f t="shared" ref="H66:H70" si="1">F66 * G66</f>
-        <v>29.48</v>
+        <v>33.32</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -1764,22 +1764,22 @@
         <v>828.94</v>
       </c>
       <c r="D67" s="6">
-        <v>828.93686694276096</v>
+        <v>828.93686694277699</v>
       </c>
       <c r="E67" s="3">
         <f t="shared" si="0"/>
-        <v>-3.7795947102070571E-6</v>
+        <v>-3.7795946908891764E-6</v>
       </c>
       <c r="F67" s="4">
-        <f>5.91/1000</f>
-        <v>5.9100000000000003E-3</v>
+        <f>6.55/1000</f>
+        <v>6.5499999999999994E-3</v>
       </c>
       <c r="G67" s="1">
         <v>2000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" si="1"/>
-        <v>11.82</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -1793,22 +1793,22 @@
         <v>591.55999999999995</v>
       </c>
       <c r="D68" s="6">
-        <v>591.55655666974599</v>
+        <v>591.55655666806399</v>
       </c>
       <c r="E68" s="3">
         <f t="shared" si="0"/>
-        <v>-5.8207624822337323E-6</v>
+        <v>-5.8207653255148983E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>23.8/1000</f>
-        <v>2.3800000000000002E-2</v>
+        <f>28.24/1000</f>
+        <v>2.8239999999999998E-2</v>
       </c>
       <c r="G68" s="1">
         <v>2000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>47.6</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -1822,22 +1822,22 @@
         <v>1696.94</v>
       </c>
       <c r="D69" s="6">
-        <v>1709.10304069069</v>
+        <v>1668.3899931731401</v>
       </c>
       <c r="E69" s="3">
         <f t="shared" si="0"/>
-        <v>7.1676315548516722E-3</v>
+        <v>-1.6824405592926084E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>4.88/1000</f>
-        <v>4.8799999999999998E-3</v>
+        <f>5.81/1000</f>
+        <v>5.8099999999999992E-3</v>
       </c>
       <c r="G69" s="1">
         <v>2000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>9.76</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -1851,22 +1851,22 @@
         <v>1406.91</v>
       </c>
       <c r="D70" s="24">
-        <v>1382.9211541499899</v>
+        <v>1354.4467482727</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-1.7050732349624509E-2</v>
+        <v>-3.7289699929135556E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>14.58/1000</f>
-        <v>1.4579999999999999E-2</v>
+        <f>17.37/1000</f>
+        <v>1.737E-2</v>
       </c>
       <c r="G70" s="1">
         <v>2000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>29.16</v>
+        <v>34.74</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D9240E-2814-4FD2-B704-5D24527C08CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF76458-9B20-4749-A95E-5C7FD9842AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1713,15 +1713,15 @@
         <v>1.5463919864454168E-2</v>
       </c>
       <c r="F65" s="5">
-        <f>5.4/1000</f>
-        <v>5.4000000000000003E-3</v>
+        <f>4.88/1000</f>
+        <v>4.8799999999999998E-3</v>
       </c>
       <c r="G65" s="1">
         <v>2000</v>
       </c>
       <c r="H65" s="6">
         <f>F65 * G65</f>
-        <v>10.8</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -1742,15 +1742,15 @@
         <v>-2.2251890941430874E-2</v>
       </c>
       <c r="F66" s="4">
-        <f>16.66/1000</f>
-        <v>1.6660000000000001E-2</v>
+        <f>14.31/1000</f>
+        <v>1.431E-2</v>
       </c>
       <c r="G66" s="1">
         <v>2000</v>
       </c>
       <c r="H66" s="6">
         <f t="shared" ref="H66:H70" si="1">F66 * G66</f>
-        <v>33.32</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -1771,15 +1771,15 @@
         <v>-3.7795946908891764E-6</v>
       </c>
       <c r="F67" s="4">
-        <f>6.55/1000</f>
-        <v>6.5499999999999994E-3</v>
+        <f>6.1/1000</f>
+        <v>6.0999999999999995E-3</v>
       </c>
       <c r="G67" s="1">
         <v>2000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" si="1"/>
-        <v>13.1</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -1800,15 +1800,15 @@
         <v>-5.8207653255148983E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>28.24/1000</f>
-        <v>2.8239999999999998E-2</v>
+        <f>24.84/1000</f>
+        <v>2.4840000000000001E-2</v>
       </c>
       <c r="G68" s="1">
         <v>2000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>56.48</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -1829,15 +1829,15 @@
         <v>-1.6824405592926084E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>5.81/1000</f>
-        <v>5.8099999999999992E-3</v>
+        <f>5.12/1000</f>
+        <v>5.1200000000000004E-3</v>
       </c>
       <c r="G69" s="1">
         <v>2000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>11.62</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -1858,15 +1858,15 @@
         <v>-3.7289699929135556E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>17.37/1000</f>
-        <v>1.737E-2</v>
+        <f>15.52/1000</f>
+        <v>1.5519999999999999E-2</v>
       </c>
       <c r="G70" s="1">
         <v>2000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>34.74</v>
+        <v>31.04</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF76458-9B20-4749-A95E-5C7FD9842AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D9E1FC-41CF-47EF-ABBF-A07A56A0CD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1713,15 +1713,15 @@
         <v>1.5463919864454168E-2</v>
       </c>
       <c r="F65" s="5">
-        <f>4.88/1000</f>
-        <v>4.8799999999999998E-3</v>
+        <f>4.82/1000</f>
+        <v>4.8200000000000005E-3</v>
       </c>
       <c r="G65" s="1">
         <v>2000</v>
       </c>
       <c r="H65" s="6">
         <f>F65 * G65</f>
-        <v>9.76</v>
+        <v>9.64</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -1742,15 +1742,15 @@
         <v>-2.2251890941430874E-2</v>
       </c>
       <c r="F66" s="4">
-        <f>14.31/1000</f>
-        <v>1.431E-2</v>
+        <f>14.49/1000</f>
+        <v>1.4489999999999999E-2</v>
       </c>
       <c r="G66" s="1">
         <v>2000</v>
       </c>
       <c r="H66" s="6">
         <f t="shared" ref="H66:H70" si="1">F66 * G66</f>
-        <v>28.62</v>
+        <v>28.98</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -1771,15 +1771,15 @@
         <v>-3.7795946908891764E-6</v>
       </c>
       <c r="F67" s="4">
-        <f>6.1/1000</f>
-        <v>6.0999999999999995E-3</v>
+        <f>6.07/1000</f>
+        <v>6.0699999999999999E-3</v>
       </c>
       <c r="G67" s="1">
         <v>2000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" si="1"/>
-        <v>12.2</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -1800,15 +1800,15 @@
         <v>-5.8207653255148983E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>24.84/1000</f>
-        <v>2.4840000000000001E-2</v>
+        <f>24.92/1000</f>
+        <v>2.4920000000000001E-2</v>
       </c>
       <c r="G68" s="1">
         <v>2000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>49.68</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -1829,15 +1829,15 @@
         <v>-1.6824405592926084E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>5.12/1000</f>
-        <v>5.1200000000000004E-3</v>
+        <f>5.1/1000</f>
+        <v>5.0999999999999995E-3</v>
       </c>
       <c r="G69" s="1">
         <v>2000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>10.24</v>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -1858,15 +1858,15 @@
         <v>-3.7289699929135556E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>15.52/1000</f>
-        <v>1.5519999999999999E-2</v>
+        <f>15.5/1000</f>
+        <v>1.55E-2</v>
       </c>
       <c r="G70" s="1">
         <v>2000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>31.04</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D9E1FC-41CF-47EF-ABBF-A07A56A0CD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D8B8BC-F3FE-40BD-90BE-AE5D6B6259B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1713,15 +1713,15 @@
         <v>1.5463919864454168E-2</v>
       </c>
       <c r="F65" s="5">
-        <f>4.82/1000</f>
-        <v>4.8200000000000005E-3</v>
+        <f>4.76/1000</f>
+        <v>4.7599999999999995E-3</v>
       </c>
       <c r="G65" s="1">
         <v>2000</v>
       </c>
       <c r="H65" s="6">
         <f>F65 * G65</f>
-        <v>9.64</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -1742,15 +1742,15 @@
         <v>-2.2251890941430874E-2</v>
       </c>
       <c r="F66" s="4">
-        <f>14.49/1000</f>
-        <v>1.4489999999999999E-2</v>
+        <f>14.52/1000</f>
+        <v>1.452E-2</v>
       </c>
       <c r="G66" s="1">
         <v>2000</v>
       </c>
       <c r="H66" s="6">
         <f t="shared" ref="H66:H70" si="1">F66 * G66</f>
-        <v>28.98</v>
+        <v>29.04</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -1771,15 +1771,15 @@
         <v>-3.7795946908891764E-6</v>
       </c>
       <c r="F67" s="4">
-        <f>6.07/1000</f>
-        <v>6.0699999999999999E-3</v>
+        <f>6.11/1000</f>
+        <v>6.11E-3</v>
       </c>
       <c r="G67" s="1">
         <v>2000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" si="1"/>
-        <v>12.14</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -1800,15 +1800,15 @@
         <v>-5.8207653255148983E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>24.92/1000</f>
-        <v>2.4920000000000001E-2</v>
+        <f>25.06/1000</f>
+        <v>2.5059999999999999E-2</v>
       </c>
       <c r="G68" s="1">
         <v>2000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>49.84</v>
+        <v>50.12</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -1829,15 +1829,15 @@
         <v>-1.6824405592926084E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>5.1/1000</f>
-        <v>5.0999999999999995E-3</v>
+        <f>5.07/1000</f>
+        <v>5.0699999999999999E-3</v>
       </c>
       <c r="G69" s="1">
         <v>2000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>10.199999999999999</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -1858,15 +1858,15 @@
         <v>-3.7289699929135556E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>15.5/1000</f>
-        <v>1.55E-2</v>
+        <f>15.62/1000</f>
+        <v>1.5619999999999998E-2</v>
       </c>
       <c r="G70" s="1">
         <v>2000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D8B8BC-F3FE-40BD-90BE-AE5D6B6259B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA01ACD-DE25-4516-9B17-5BB7D9031C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1713,15 +1713,15 @@
         <v>1.5463919864454168E-2</v>
       </c>
       <c r="F65" s="5">
-        <f>4.76/1000</f>
-        <v>4.7599999999999995E-3</v>
+        <f>4.55/1000</f>
+        <v>4.5500000000000002E-3</v>
       </c>
       <c r="G65" s="1">
         <v>2000</v>
       </c>
       <c r="H65" s="6">
         <f>F65 * G65</f>
-        <v>9.52</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -1742,15 +1742,15 @@
         <v>-2.2251890941430874E-2</v>
       </c>
       <c r="F66" s="4">
-        <f>14.52/1000</f>
-        <v>1.452E-2</v>
+        <f>14.16/1000</f>
+        <v>1.4160000000000001E-2</v>
       </c>
       <c r="G66" s="1">
         <v>2000</v>
       </c>
       <c r="H66" s="6">
         <f t="shared" ref="H66:H70" si="1">F66 * G66</f>
-        <v>29.04</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -1771,15 +1771,15 @@
         <v>-3.7795946908891764E-6</v>
       </c>
       <c r="F67" s="4">
-        <f>6.11/1000</f>
-        <v>6.11E-3</v>
+        <f>6.15/1000</f>
+        <v>6.1500000000000001E-3</v>
       </c>
       <c r="G67" s="1">
         <v>2000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" si="1"/>
-        <v>12.22</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -1800,15 +1800,15 @@
         <v>-5.8207653255148983E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>25.06/1000</f>
-        <v>2.5059999999999999E-2</v>
+        <f>24.62/1000</f>
+        <v>2.462E-2</v>
       </c>
       <c r="G68" s="1">
         <v>2000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>50.12</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -1829,15 +1829,15 @@
         <v>-1.6824405592926084E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>5.07/1000</f>
-        <v>5.0699999999999999E-3</v>
+        <f>4.91/1000</f>
+        <v>4.9100000000000003E-3</v>
       </c>
       <c r="G69" s="1">
         <v>2000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>10.14</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -1858,15 +1858,15 @@
         <v>-3.7289699929135556E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>15.62/1000</f>
-        <v>1.5619999999999998E-2</v>
+        <f>15.23/1000</f>
+        <v>1.523E-2</v>
       </c>
       <c r="G70" s="1">
         <v>2000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>31.24</v>
+        <v>30.46</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA01ACD-DE25-4516-9B17-5BB7D9031C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CDADDA-2C92-4B4F-A8AB-CDA056112A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1706,22 +1706,22 @@
         <v>1645.79</v>
       </c>
       <c r="D65" s="6">
-        <v>1671.24036467372</v>
+        <v>1660.7914269042301</v>
       </c>
       <c r="E65" s="3">
         <f>D65/C65-1</f>
-        <v>1.5463919864454168E-2</v>
+        <v>9.115031021108555E-3</v>
       </c>
       <c r="F65" s="5">
-        <f>4.55/1000</f>
-        <v>4.5500000000000002E-3</v>
+        <f>4.67/1000</f>
+        <v>4.6699999999999997E-3</v>
       </c>
       <c r="G65" s="1">
         <v>2000</v>
       </c>
       <c r="H65" s="6">
         <f>F65 * G65</f>
-        <v>9.1</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -1742,15 +1742,15 @@
         <v>-2.2251890941430874E-2</v>
       </c>
       <c r="F66" s="4">
-        <f>14.16/1000</f>
-        <v>1.4160000000000001E-2</v>
+        <f>14.22/1000</f>
+        <v>1.422E-2</v>
       </c>
       <c r="G66" s="1">
         <v>2000</v>
       </c>
       <c r="H66" s="6">
         <f t="shared" ref="H66:H70" si="1">F66 * G66</f>
-        <v>28.32</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -1771,15 +1771,15 @@
         <v>-3.7795946908891764E-6</v>
       </c>
       <c r="F67" s="4">
-        <f>6.15/1000</f>
-        <v>6.1500000000000001E-3</v>
+        <f>6.13/1000</f>
+        <v>6.13E-3</v>
       </c>
       <c r="G67" s="1">
         <v>2000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" si="1"/>
-        <v>12.3</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -1800,15 +1800,15 @@
         <v>-5.8207653255148983E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>24.62/1000</f>
-        <v>2.462E-2</v>
+        <f>24.68/1000</f>
+        <v>2.4680000000000001E-2</v>
       </c>
       <c r="G68" s="1">
         <v>2000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>49.24</v>
+        <v>49.36</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -1822,22 +1822,22 @@
         <v>1696.94</v>
       </c>
       <c r="D69" s="6">
-        <v>1668.3899931731401</v>
+        <v>1672.0440954870601</v>
       </c>
       <c r="E69" s="3">
         <f t="shared" si="0"/>
-        <v>-1.6824405592926084E-2</v>
+        <v>-1.4671057617205108E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>4.91/1000</f>
-        <v>4.9100000000000003E-3</v>
+        <f>4.75/1000</f>
+        <v>4.7499999999999999E-3</v>
       </c>
       <c r="G69" s="1">
         <v>2000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>9.82</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -1851,22 +1851,22 @@
         <v>1406.91</v>
       </c>
       <c r="D70" s="24">
-        <v>1354.4467482727</v>
+        <v>1358.17333404533</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-3.7289699929135556E-2</v>
+        <v>-3.4640926537354955E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>15.23/1000</f>
-        <v>1.523E-2</v>
+        <f>15.05/1000</f>
+        <v>1.5050000000000001E-2</v>
       </c>
       <c r="G70" s="1">
         <v>2000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>30.46</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CDADDA-2C92-4B4F-A8AB-CDA056112A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D07934-135F-4EB4-B338-EC1A93DD034A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1706,22 +1706,22 @@
         <v>1645.79</v>
       </c>
       <c r="D65" s="6">
-        <v>1660.7914269042301</v>
+        <v>1647.99912450019</v>
       </c>
       <c r="E65" s="3">
         <f>D65/C65-1</f>
-        <v>9.115031021108555E-3</v>
+        <v>1.34228820213389E-3</v>
       </c>
       <c r="F65" s="5">
-        <f>4.67/1000</f>
-        <v>4.6699999999999997E-3</v>
+        <f>4.71/1000</f>
+        <v>4.7099999999999998E-3</v>
       </c>
       <c r="G65" s="1">
         <v>2000</v>
       </c>
       <c r="H65" s="6">
         <f>F65 * G65</f>
-        <v>9.34</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -1735,22 +1735,22 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="D66" s="24">
-        <v>1224.5023993416801</v>
+        <v>1201.06719688372</v>
       </c>
       <c r="E66" s="3">
         <f t="shared" ref="E66:E70" si="0">D66/C66-1</f>
-        <v>-2.2251890941430874E-2</v>
+        <v>-4.0964573661361969E-2</v>
       </c>
       <c r="F66" s="4">
-        <f>14.22/1000</f>
-        <v>1.422E-2</v>
+        <f>13.07/1000</f>
+        <v>1.307E-2</v>
       </c>
       <c r="G66" s="1">
         <v>2000</v>
       </c>
       <c r="H66" s="6">
         <f t="shared" ref="H66:H70" si="1">F66 * G66</f>
-        <v>28.44</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -1800,15 +1800,15 @@
         <v>-5.8207653255148983E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>24.68/1000</f>
-        <v>2.4680000000000001E-2</v>
+        <f>24.34/1000</f>
+        <v>2.4340000000000001E-2</v>
       </c>
       <c r="G68" s="1">
         <v>2000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>49.36</v>
+        <v>48.68</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -1822,22 +1822,22 @@
         <v>1696.94</v>
       </c>
       <c r="D69" s="6">
-        <v>1672.0440954870601</v>
+        <v>1678.1751810066401</v>
       </c>
       <c r="E69" s="3">
         <f t="shared" si="0"/>
-        <v>-1.4671057617205108E-2</v>
+        <v>-1.1058033279526702E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>4.75/1000</f>
-        <v>4.7499999999999999E-3</v>
+        <f>4.74/1000</f>
+        <v>4.7400000000000003E-3</v>
       </c>
       <c r="G69" s="1">
         <v>2000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -1851,22 +1851,22 @@
         <v>1406.91</v>
       </c>
       <c r="D70" s="24">
-        <v>1358.17333404533</v>
+        <v>1409.21629394568</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-3.4640926537354955E-2</v>
+        <v>1.6392618900142875E-3</v>
       </c>
       <c r="F70" s="4">
-        <f>15.05/1000</f>
-        <v>1.5050000000000001E-2</v>
+        <f>14.85/1000</f>
+        <v>1.485E-2</v>
       </c>
       <c r="G70" s="1">
         <v>2000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>30.1</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D07934-135F-4EB4-B338-EC1A93DD034A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC42350-65BE-4F42-A032-770924E9118F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-113" yWindow="-113" windowWidth="48309" windowHeight="26546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VRPTW Benchmarking" sheetId="1" r:id="rId1"/>
@@ -115,9 +115,6 @@
     <t>ALNS parameters</t>
   </si>
   <si>
-    <t>Traveling Salesman Problem (TSP) Benchmarking</t>
-  </si>
-  <si>
     <t>Benchmarking</t>
   </si>
   <si>
@@ -275,6 +272,9 @@
   </si>
   <si>
     <t>n = ceil(x, digits=-(length(digits(x))-1))</t>
+  </si>
+  <si>
+    <t>Vehicle Routing Problem with Time-Windows (VRPTW) Benchmarking</t>
   </si>
 </sst>
 </file>
@@ -786,22 +786,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X280"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="3" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.05" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -809,7 +809,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
     </row>
-    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15.05" x14ac:dyDescent="0.3">
       <c r="A2" s="19"/>
       <c r="B2" s="20"/>
       <c r="C2" s="21"/>
@@ -817,125 +817,125 @@
       <c r="E2" s="21"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="8"/>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>25</v>
       </c>
@@ -954,27 +954,27 @@
       <c r="W18" s="12"/>
       <c r="X18" s="12"/>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" s="11"/>
       <c r="L19" s="12"/>
       <c r="W19" s="12"/>
       <c r="X19" s="12"/>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B20" s="11"/>
       <c r="L20" s="12"/>
       <c r="W20" s="12"/>
       <c r="X20" s="12"/>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -989,9 +989,9 @@
       <c r="W21" s="12"/>
       <c r="X21" s="12"/>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -1006,9 +1006,9 @@
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -1023,9 +1023,9 @@
       <c r="W23" s="12"/>
       <c r="X23" s="12"/>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -1040,9 +1040,9 @@
       <c r="W24" s="12"/>
       <c r="X24" s="12"/>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -1057,7 +1057,7 @@
       <c r="W25" s="12"/>
       <c r="X25" s="12"/>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>8</v>
       </c>
@@ -1074,9 +1074,9 @@
       <c r="W26" s="12"/>
       <c r="X26" s="12"/>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -1091,9 +1091,9 @@
       <c r="W27" s="12"/>
       <c r="X27" s="12"/>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -1108,9 +1108,9 @@
       <c r="W28" s="12"/>
       <c r="X28" s="12"/>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -1125,9 +1125,9 @@
       <c r="W29" s="12"/>
       <c r="X29" s="12"/>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -1142,9 +1142,9 @@
       <c r="W30" s="12"/>
       <c r="X30" s="12"/>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -1159,9 +1159,9 @@
       <c r="W31" s="12"/>
       <c r="X31" s="12"/>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -1176,9 +1176,9 @@
       <c r="W32" s="12"/>
       <c r="X32" s="12"/>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -1193,9 +1193,9 @@
       <c r="W33" s="12"/>
       <c r="X33" s="12"/>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -1210,9 +1210,9 @@
       <c r="W34" s="12"/>
       <c r="X34" s="12"/>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -1227,7 +1227,7 @@
       <c r="W35" s="12"/>
       <c r="X35" s="12"/>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
         <v>6</v>
       </c>
@@ -1244,7 +1244,7 @@
       <c r="W36" s="12"/>
       <c r="X36" s="12"/>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
         <v>9</v>
       </c>
@@ -1261,9 +1261,9 @@
       <c r="W37" s="12"/>
       <c r="X37" s="12"/>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -1278,9 +1278,9 @@
       <c r="W38" s="12"/>
       <c r="X38" s="12"/>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -1295,9 +1295,9 @@
       <c r="W39" s="12"/>
       <c r="X39" s="12"/>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -1312,9 +1312,9 @@
       <c r="W40" s="12"/>
       <c r="X40" s="12"/>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -1329,7 +1329,7 @@
       <c r="W41" s="12"/>
       <c r="X41" s="12"/>
     </row>
-    <row r="42" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>7</v>
       </c>
@@ -1346,7 +1346,7 @@
       <c r="W42" s="12"/>
       <c r="X42" s="12"/>
     </row>
-    <row r="43" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
         <v>21</v>
       </c>
@@ -1363,7 +1363,7 @@
       <c r="W43" s="12"/>
       <c r="X43" s="12"/>
     </row>
-    <row r="44" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
         <v>22</v>
       </c>
@@ -1380,9 +1380,9 @@
       <c r="W44" s="12"/>
       <c r="X44" s="12"/>
     </row>
-    <row r="45" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
@@ -1397,9 +1397,9 @@
       <c r="W45" s="12"/>
       <c r="X45" s="12"/>
     </row>
-    <row r="46" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -1414,9 +1414,9 @@
       <c r="W46" s="12"/>
       <c r="X46" s="12"/>
     </row>
-    <row r="47" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -1431,7 +1431,7 @@
       <c r="W47" s="12"/>
       <c r="X47" s="12"/>
     </row>
-    <row r="48" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
         <v>10</v>
       </c>
@@ -1448,7 +1448,7 @@
       <c r="W48" s="12"/>
       <c r="X48" s="12"/>
     </row>
-    <row r="49" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>7</v>
       </c>
@@ -1465,7 +1465,7 @@
       <c r="W49" s="12"/>
       <c r="X49" s="12"/>
     </row>
-    <row r="50" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>11</v>
       </c>
@@ -1482,7 +1482,7 @@
       <c r="W50" s="12"/>
       <c r="X50" s="12"/>
     </row>
-    <row r="51" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
         <v>12</v>
       </c>
@@ -1499,7 +1499,7 @@
       <c r="W51" s="12"/>
       <c r="X51" s="12"/>
     </row>
-    <row r="52" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
         <v>13</v>
       </c>
@@ -1516,7 +1516,7 @@
       <c r="W52" s="12"/>
       <c r="X52" s="12"/>
     </row>
-    <row r="53" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
         <v>14</v>
       </c>
@@ -1533,7 +1533,7 @@
       <c r="W53" s="12"/>
       <c r="X53" s="12"/>
     </row>
-    <row r="54" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
         <v>15</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="W54" s="12"/>
       <c r="X54" s="12"/>
     </row>
-    <row r="55" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
         <v>16</v>
       </c>
@@ -1567,7 +1567,7 @@
       <c r="W55" s="12"/>
       <c r="X55" s="12"/>
     </row>
-    <row r="56" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
         <v>17</v>
       </c>
@@ -1584,7 +1584,7 @@
       <c r="W56" s="12"/>
       <c r="X56" s="12"/>
     </row>
-    <row r="57" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
         <v>18</v>
       </c>
@@ -1601,7 +1601,7 @@
       <c r="W57" s="12"/>
       <c r="X57" s="12"/>
     </row>
-    <row r="58" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
         <v>19</v>
       </c>
@@ -1618,7 +1618,7 @@
       <c r="W58" s="12"/>
       <c r="X58" s="12"/>
     </row>
-    <row r="59" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
         <v>20</v>
       </c>
@@ -1635,9 +1635,9 @@
       <c r="W59" s="12"/>
       <c r="X59" s="12"/>
     </row>
-    <row r="60" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -1649,9 +1649,9 @@
       <c r="U60" s="12"/>
       <c r="V60" s="12"/>
     </row>
-    <row r="61" spans="1:24" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -1663,13 +1663,13 @@
       <c r="U61" s="12"/>
       <c r="V61" s="12"/>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B63" s="7"/>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
         <v>2</v>
       </c>
@@ -1695,9 +1695,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B65" s="2">
         <v>100</v>
@@ -1724,9 +1724,9 @@
         <v>9.42</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B66" s="2">
         <v>100</v>
@@ -1753,9 +1753,9 @@
         <v>26.14</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B67" s="2">
         <v>100</v>
@@ -1782,9 +1782,9 @@
         <v>12.26</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B68" s="2">
         <v>100</v>
@@ -1811,9 +1811,9 @@
         <v>48.68</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B69" s="2">
         <v>100</v>
@@ -1840,9 +1840,9 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B70" s="2">
         <v>100</v>
@@ -1869,634 +1869,634 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B71" s="7"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B72" s="7"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B73" s="7"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B74" s="7"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B75" s="7"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B76" s="7"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B77" s="7"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B78" s="7"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B79" s="7"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B80" s="7"/>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B81" s="7"/>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B82" s="7"/>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B83" s="7"/>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B84" s="7"/>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B85" s="7"/>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B86" s="7"/>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B87" s="7"/>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B88" s="7"/>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B89" s="7"/>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B90" s="7"/>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B91" s="7"/>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B92" s="7"/>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B93" s="7"/>
     </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B94" s="7"/>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B95" s="7"/>
     </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B96" s="7"/>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B97" s="7"/>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B98" s="7"/>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B99" s="7"/>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B100" s="7"/>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B101" s="7"/>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B102" s="7"/>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B103" s="7"/>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B104" s="7"/>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B105" s="7"/>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B106" s="7"/>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B107" s="7"/>
     </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B108" s="7"/>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B109" s="7"/>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B110" s="7"/>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B111" s="7"/>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B112" s="7"/>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B113" s="7"/>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B114" s="7"/>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B115" s="7"/>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B116" s="7"/>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B117" s="7"/>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B118" s="7"/>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B119" s="7"/>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B120" s="7"/>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B121" s="7"/>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B122" s="7"/>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B123" s="7"/>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B124" s="7"/>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B125" s="7"/>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B126" s="7"/>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B127" s="7"/>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B128" s="7"/>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B129" s="7"/>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B130" s="7"/>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B131" s="7"/>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B132" s="7"/>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B133" s="7"/>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B134" s="7"/>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B135" s="7"/>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B136" s="7"/>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B137" s="7"/>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B138" s="7"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B139" s="7"/>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B140" s="7"/>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B141" s="7"/>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B142" s="7"/>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B143" s="7"/>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B144" s="7"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B145" s="7"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B146" s="7"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B147" s="7"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B148" s="7"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B149" s="7"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B150" s="7"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B151" s="7"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B152" s="7"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B153" s="7"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B154" s="7"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B155" s="7"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B156" s="7"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B157" s="7"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B158" s="7"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B159" s="7"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B160" s="7"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B161" s="7"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B162" s="7"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B163" s="7"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B164" s="7"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B165" s="7"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B166" s="7"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B167" s="7"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B168" s="7"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B169" s="7"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B170" s="7"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B171" s="7"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B172" s="7"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B173" s="7"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B174" s="7"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B175" s="7"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B176" s="7"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B177" s="7"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B178" s="7"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B179" s="7"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B180" s="7"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B181" s="7"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B182" s="7"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B183" s="7"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B184" s="7"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B185" s="7"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B186" s="7"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B187" s="7"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B188" s="7"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B189" s="7"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B190" s="7"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B191" s="7"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B192" s="7"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B193" s="7"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B194" s="7"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B195" s="7"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B196" s="7"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B197" s="7"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B198" s="7"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B199" s="7"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B200" s="7"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B201" s="7"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B202" s="7"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B203" s="7"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B204" s="7"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B205" s="7"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B206" s="7"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B207" s="7"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B208" s="7"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B209" s="7"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B210" s="7"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B211" s="7"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B212" s="7"/>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B213" s="7"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B214" s="7"/>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B215" s="7"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B216" s="7"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B217" s="7"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B218" s="7"/>
     </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B219" s="7"/>
     </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B220" s="7"/>
     </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B221" s="7"/>
     </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B222" s="7"/>
     </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B223" s="7"/>
     </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B224" s="7"/>
     </row>
-    <row r="225" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B225" s="7"/>
     </row>
-    <row r="226" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B226" s="7"/>
     </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B227" s="7"/>
     </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B228" s="7"/>
     </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B229" s="7"/>
     </row>
-    <row r="230" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B230" s="7"/>
     </row>
-    <row r="231" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B231" s="7"/>
     </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B232" s="7"/>
     </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B233" s="7"/>
     </row>
-    <row r="234" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B234" s="7"/>
     </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B235" s="7"/>
     </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B236" s="7"/>
     </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B237" s="7"/>
     </row>
-    <row r="238" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B238" s="7"/>
     </row>
-    <row r="239" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B239" s="7"/>
     </row>
-    <row r="240" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B240" s="7"/>
     </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="241" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B241" s="7"/>
     </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="242" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B242" s="7"/>
     </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="243" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B243" s="7"/>
     </row>
-    <row r="244" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="244" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B244" s="7"/>
     </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="245" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B245" s="7"/>
     </row>
-    <row r="246" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="246" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B246" s="7"/>
     </row>
-    <row r="247" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="247" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B247" s="7"/>
     </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="248" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B248" s="7"/>
     </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="249" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B249" s="7"/>
     </row>
-    <row r="250" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="250" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B250" s="7"/>
     </row>
-    <row r="251" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="251" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B251" s="7"/>
     </row>
-    <row r="252" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="252" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B252" s="7"/>
     </row>
-    <row r="253" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="253" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B253" s="7"/>
     </row>
-    <row r="254" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="254" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B254" s="7"/>
     </row>
-    <row r="255" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="255" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B255" s="7"/>
     </row>
-    <row r="256" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="256" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B256" s="7"/>
     </row>
-    <row r="257" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="257" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B257" s="7"/>
     </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="258" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B258" s="7"/>
     </row>
-    <row r="259" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="259" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B259" s="7"/>
     </row>
-    <row r="260" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="260" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B260" s="7"/>
     </row>
-    <row r="261" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="261" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B261" s="7"/>
     </row>
-    <row r="262" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="262" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B262" s="7"/>
     </row>
-    <row r="263" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="263" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B263" s="7"/>
     </row>
-    <row r="264" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="264" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B264" s="7"/>
     </row>
-    <row r="265" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="265" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B265" s="7"/>
     </row>
-    <row r="266" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="266" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B266" s="7"/>
     </row>
-    <row r="267" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="267" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B267" s="7"/>
     </row>
-    <row r="268" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="268" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B268" s="7"/>
     </row>
-    <row r="269" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="269" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B269" s="7"/>
     </row>
-    <row r="270" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="270" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B270" s="7"/>
     </row>
-    <row r="271" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="271" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B271" s="7"/>
     </row>
-    <row r="272" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="272" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B272" s="7"/>
     </row>
-    <row r="273" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="273" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B273" s="7"/>
     </row>
-    <row r="274" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="274" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B274" s="7"/>
     </row>
-    <row r="275" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="275" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B275" s="7"/>
     </row>
-    <row r="276" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="276" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B276" s="7"/>
     </row>
-    <row r="277" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="277" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B277" s="7"/>
     </row>
-    <row r="278" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="278" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B278" s="7"/>
     </row>
-    <row r="279" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="279" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B279" s="7"/>
     </row>
-    <row r="280" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="280" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B280" s="7"/>
     </row>
   </sheetData>

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC42350-65BE-4F42-A032-770924E9118F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDF6E20-244C-4D8A-8720-43F00A46FDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="48309" windowHeight="26546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1706,22 +1706,22 @@
         <v>1645.79</v>
       </c>
       <c r="D65" s="6">
-        <v>1647.99912450019</v>
+        <v>1643.0888648786899</v>
       </c>
       <c r="E65" s="3">
         <f>D65/C65-1</f>
-        <v>1.34228820213389E-3</v>
+        <v>-1.6412392354492322E-3</v>
       </c>
       <c r="F65" s="5">
-        <f>4.71/1000</f>
-        <v>4.7099999999999998E-3</v>
+        <f>4.79/1000</f>
+        <v>4.79E-3</v>
       </c>
       <c r="G65" s="1">
         <v>2000</v>
       </c>
       <c r="H65" s="6">
         <f>F65 * G65</f>
-        <v>9.42</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -1735,22 +1735,22 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="D66" s="24">
-        <v>1201.06719688372</v>
+        <v>1196.2386137594799</v>
       </c>
       <c r="E66" s="3">
         <f t="shared" ref="E66:E70" si="0">D66/C66-1</f>
-        <v>-4.0964573661361969E-2</v>
+        <v>-4.4820130025886917E-2</v>
       </c>
       <c r="F66" s="4">
-        <f>13.07/1000</f>
-        <v>1.307E-2</v>
+        <f>12.42/1000</f>
+        <v>1.242E-2</v>
       </c>
       <c r="G66" s="1">
         <v>2000</v>
       </c>
       <c r="H66" s="6">
         <f t="shared" ref="H66:H70" si="1">F66 * G66</f>
-        <v>26.14</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -1764,22 +1764,22 @@
         <v>828.94</v>
       </c>
       <c r="D67" s="6">
-        <v>828.93686694277699</v>
+        <v>828.93686694224698</v>
       </c>
       <c r="E67" s="3">
         <f t="shared" si="0"/>
-        <v>-3.7795946908891764E-6</v>
+        <v>-3.7795953302666163E-6</v>
       </c>
       <c r="F67" s="4">
-        <f>6.13/1000</f>
-        <v>6.13E-3</v>
+        <f>6.65/1000</f>
+        <v>6.6500000000000005E-3</v>
       </c>
       <c r="G67" s="1">
         <v>2000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" si="1"/>
-        <v>12.26</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -1793,22 +1793,22 @@
         <v>591.55999999999995</v>
       </c>
       <c r="D68" s="6">
-        <v>591.55655666806399</v>
+        <v>591.55655666872997</v>
       </c>
       <c r="E68" s="3">
         <f t="shared" si="0"/>
-        <v>-5.8207653255148983E-6</v>
+        <v>-5.8207641997487514E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>24.34/1000</f>
-        <v>2.4340000000000001E-2</v>
+        <f>22.92/1000</f>
+        <v>2.2920000000000003E-2</v>
       </c>
       <c r="G68" s="1">
         <v>2000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>48.68</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -1822,22 +1822,22 @@
         <v>1696.94</v>
       </c>
       <c r="D69" s="6">
-        <v>1678.1751810066401</v>
+        <v>1670.2230616634599</v>
       </c>
       <c r="E69" s="3">
         <f t="shared" si="0"/>
-        <v>-1.1058033279526702E-2</v>
+        <v>-1.57441856144237E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>4.74/1000</f>
-        <v>4.7400000000000003E-3</v>
+        <f>12.69/1000</f>
+        <v>1.269E-2</v>
       </c>
       <c r="G69" s="1">
         <v>2000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>9.48</v>
+        <v>25.38</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -1851,22 +1851,22 @@
         <v>1406.91</v>
       </c>
       <c r="D70" s="24">
-        <v>1409.21629394568</v>
+        <v>1297.91070367663</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>1.6392618900142875E-3</v>
+        <v>-7.7474249471089163E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>14.85/1000</f>
-        <v>1.485E-2</v>
+        <f>5.25/1000</f>
+        <v>5.2500000000000003E-3</v>
       </c>
       <c r="G70" s="1">
         <v>2000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>29.7</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDF6E20-244C-4D8A-8720-43F00A46FDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F631D79-84C4-4324-A7BE-FCEAED795386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-113" yWindow="-113" windowWidth="48309" windowHeight="26546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-113" yWindow="-113" windowWidth="48309" windowHeight="26546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="VRPTW Benchmarking" sheetId="1" r:id="rId1"/>
+    <sheet name="VRP Benchmarking" sheetId="2" r:id="rId1"/>
+    <sheet name="VRPTW Benchmarking" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="93">
   <si>
     <t>Best known</t>
   </si>
@@ -271,10 +272,49 @@
     <t>x = length(N)</t>
   </si>
   <si>
-    <t>n = ceil(x, digits=-(length(digits(x))-1))</t>
-  </si>
-  <si>
     <t>Vehicle Routing Problem with Time-Windows (VRPTW) Benchmarking</t>
+  </si>
+  <si>
+    <t>Vehicle Routing Problem (VRP) Benchmarking</t>
+  </si>
+  <si>
+    <t>Initializtion</t>
+  </si>
+  <si>
+    <t>:random</t>
+  </si>
+  <si>
+    <t>                    :worstnode!     ,  </t>
+  </si>
+  <si>
+    <t>                    :relatedroute!  ,</t>
+  </si>
+  <si>
+    <t>                    :worstroute!</t>
+  </si>
+  <si>
+    <t>                    :regret2!       ,</t>
+  </si>
+  <si>
+    <t>m-n101-k10</t>
+  </si>
+  <si>
+    <t>tai150a</t>
+  </si>
+  <si>
+    <t>cmt10</t>
+  </si>
+  <si>
+    <t>x-n251-k28</t>
+  </si>
+  <si>
+    <t>x-n303-k21</t>
+  </si>
+  <si>
+    <t>χ   = ALNSParameters(</t>
+  </si>
+  <si>
+    <t>n = max(200, ceil(x, digits=-(length(digits(x))-1)))</t>
   </si>
 </sst>
 </file>
@@ -464,7 +504,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -504,6 +544,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,6 +834,1549 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB48D86-1312-4781-AFB7-1DCAC26244E4}">
+  <dimension ref="A1:X274"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.05" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.05" x14ac:dyDescent="0.3">
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+    </row>
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="L19" s="12"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12"/>
+    </row>
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="L20" s="12"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+    </row>
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="L21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+    </row>
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="L22" s="12"/>
+      <c r="U22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+    </row>
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+    </row>
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="U24" s="12"/>
+      <c r="V24" s="12"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="12"/>
+    </row>
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="U25" s="12"/>
+      <c r="V25" s="12"/>
+      <c r="W25" s="12"/>
+      <c r="X25" s="12"/>
+    </row>
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="U26" s="12"/>
+      <c r="V26" s="12"/>
+      <c r="W26" s="12"/>
+      <c r="X26" s="12"/>
+    </row>
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="L27" s="12"/>
+      <c r="U27" s="12"/>
+      <c r="V27" s="12"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
+    </row>
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="L28" s="12"/>
+      <c r="U28" s="12"/>
+      <c r="V28" s="12"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="12"/>
+    </row>
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="L29" s="12"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
+    </row>
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="L30" s="12"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+    </row>
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="L31" s="12"/>
+      <c r="U31" s="12"/>
+      <c r="V31" s="12"/>
+      <c r="W31" s="12"/>
+      <c r="X31" s="12"/>
+    </row>
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="L32" s="12"/>
+      <c r="U32" s="12"/>
+      <c r="V32" s="12"/>
+      <c r="W32" s="12"/>
+      <c r="X32" s="12"/>
+    </row>
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="L33" s="12"/>
+      <c r="U33" s="12"/>
+      <c r="V33" s="12"/>
+      <c r="W33" s="12"/>
+      <c r="X33" s="12"/>
+    </row>
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="L34" s="12"/>
+      <c r="U34" s="12"/>
+      <c r="V34" s="12"/>
+      <c r="W34" s="12"/>
+      <c r="X34" s="12"/>
+    </row>
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="L35" s="12"/>
+      <c r="U35" s="12"/>
+      <c r="V35" s="12"/>
+      <c r="W35" s="12"/>
+      <c r="X35" s="12"/>
+    </row>
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="L36" s="12"/>
+      <c r="U36" s="12"/>
+      <c r="V36" s="12"/>
+      <c r="W36" s="12"/>
+      <c r="X36" s="12"/>
+    </row>
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="L37" s="12"/>
+      <c r="U37" s="12"/>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
+      <c r="X37" s="12"/>
+    </row>
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="L38" s="12"/>
+      <c r="U38" s="12"/>
+      <c r="V38" s="12"/>
+      <c r="W38" s="12"/>
+      <c r="X38" s="12"/>
+    </row>
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="L39" s="12"/>
+      <c r="U39" s="12"/>
+      <c r="V39" s="12"/>
+      <c r="W39" s="12"/>
+      <c r="X39" s="12"/>
+    </row>
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="L40" s="12"/>
+      <c r="U40" s="12"/>
+      <c r="V40" s="12"/>
+      <c r="W40" s="12"/>
+      <c r="X40" s="12"/>
+    </row>
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="11"/>
+      <c r="L41" s="12"/>
+      <c r="U41" s="12"/>
+      <c r="V41" s="12"/>
+      <c r="W41" s="12"/>
+      <c r="X41" s="12"/>
+    </row>
+    <row r="42" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="11"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="L42" s="12"/>
+      <c r="U42" s="12"/>
+      <c r="V42" s="12"/>
+      <c r="W42" s="12"/>
+      <c r="X42" s="12"/>
+    </row>
+    <row r="43" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" s="11"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="L43" s="12"/>
+      <c r="U43" s="12"/>
+      <c r="V43" s="12"/>
+      <c r="W43" s="12"/>
+      <c r="X43" s="12"/>
+    </row>
+    <row r="44" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="11"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="L44" s="12"/>
+      <c r="U44" s="12"/>
+      <c r="V44" s="12"/>
+      <c r="W44" s="12"/>
+      <c r="X44" s="12"/>
+    </row>
+    <row r="45" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" s="11"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="L45" s="12"/>
+      <c r="U45" s="12"/>
+      <c r="V45" s="12"/>
+      <c r="W45" s="12"/>
+      <c r="X45" s="12"/>
+    </row>
+    <row r="46" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="11"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="L46" s="12"/>
+      <c r="U46" s="12"/>
+      <c r="V46" s="12"/>
+      <c r="W46" s="12"/>
+      <c r="X46" s="12"/>
+    </row>
+    <row r="47" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="11"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="L47" s="12"/>
+      <c r="U47" s="12"/>
+      <c r="V47" s="12"/>
+      <c r="W47" s="12"/>
+      <c r="X47" s="12"/>
+    </row>
+    <row r="48" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="11"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="L48" s="12"/>
+      <c r="U48" s="12"/>
+      <c r="V48" s="12"/>
+      <c r="W48" s="12"/>
+      <c r="X48" s="12"/>
+    </row>
+    <row r="49" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" s="11"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="L49" s="12"/>
+      <c r="U49" s="12"/>
+      <c r="V49" s="12"/>
+      <c r="W49" s="12"/>
+      <c r="X49" s="12"/>
+    </row>
+    <row r="50" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="11"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
+      <c r="L50" s="12"/>
+      <c r="U50" s="12"/>
+      <c r="V50" s="12"/>
+      <c r="W50" s="12"/>
+      <c r="X50" s="12"/>
+    </row>
+    <row r="51" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" s="11"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
+      <c r="L51" s="12"/>
+      <c r="U51" s="12"/>
+      <c r="V51" s="12"/>
+      <c r="W51" s="12"/>
+      <c r="X51" s="12"/>
+    </row>
+    <row r="52" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B52" s="11"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
+      <c r="L52" s="12"/>
+      <c r="U52" s="12"/>
+      <c r="V52" s="12"/>
+      <c r="W52" s="12"/>
+      <c r="X52" s="12"/>
+    </row>
+    <row r="53" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" s="11"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="L53" s="12"/>
+      <c r="U53" s="12"/>
+      <c r="V53" s="12"/>
+      <c r="W53" s="12"/>
+      <c r="X53" s="12"/>
+    </row>
+    <row r="54" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" s="11"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="L54" s="12"/>
+      <c r="U54" s="12"/>
+      <c r="V54" s="12"/>
+      <c r="W54" s="12"/>
+      <c r="X54" s="12"/>
+    </row>
+    <row r="55" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55" s="11"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="L55" s="12"/>
+      <c r="U55" s="12"/>
+      <c r="V55" s="12"/>
+      <c r="W55" s="12"/>
+      <c r="X55" s="12"/>
+    </row>
+    <row r="56" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56" s="11"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="L56" s="12"/>
+      <c r="U56" s="12"/>
+      <c r="V56" s="12"/>
+      <c r="W56" s="12"/>
+      <c r="X56" s="12"/>
+    </row>
+    <row r="57" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B57" s="11"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="L57" s="12"/>
+      <c r="U57" s="12"/>
+      <c r="V57" s="12"/>
+      <c r="W57" s="12"/>
+      <c r="X57" s="12"/>
+    </row>
+    <row r="58" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B58" s="11"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="L58" s="12"/>
+      <c r="U58" s="12"/>
+      <c r="V58" s="12"/>
+      <c r="W58" s="12"/>
+      <c r="X58" s="12"/>
+    </row>
+    <row r="59" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A59" s="26"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="L59" s="12"/>
+      <c r="U59" s="12"/>
+      <c r="V59" s="12"/>
+      <c r="W59" s="12"/>
+      <c r="X59" s="12"/>
+    </row>
+    <row r="60" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A60" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B60" s="7"/>
+      <c r="U60" s="12"/>
+      <c r="V60" s="12"/>
+    </row>
+    <row r="61" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+      <c r="A61" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G61" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H61" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="U61" s="12"/>
+      <c r="V61" s="12"/>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B62" s="2">
+        <v>100</v>
+      </c>
+      <c r="C62" s="28">
+        <v>820</v>
+      </c>
+      <c r="D62" s="28">
+        <v>827.69699099363697</v>
+      </c>
+      <c r="E62" s="3">
+        <f>D62/C62-1</f>
+        <v>9.3865743824841363E-3</v>
+      </c>
+      <c r="F62" s="5">
+        <f>3.16/1000</f>
+        <v>3.16E-3</v>
+      </c>
+      <c r="G62" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H62" s="6">
+        <f>F62 * G62</f>
+        <v>6.32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B63" s="1">
+        <v>150</v>
+      </c>
+      <c r="C63" s="28">
+        <v>3055.23</v>
+      </c>
+      <c r="D63" s="29">
+        <v>3176.3473615429598</v>
+      </c>
+      <c r="E63" s="3">
+        <f>D63/C63-1</f>
+        <v>3.9642632974591141E-2</v>
+      </c>
+      <c r="F63" s="4">
+        <f>8.8/1000</f>
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="G63" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H63" s="6">
+        <f t="shared" ref="H63:H66" si="0">F63 * G63</f>
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B64" s="2">
+        <v>200</v>
+      </c>
+      <c r="C64" s="28">
+        <v>1395.85</v>
+      </c>
+      <c r="D64" s="28">
+        <v>1363.1950523400101</v>
+      </c>
+      <c r="E64" s="3">
+        <f>D64/C64-1</f>
+        <v>-2.3394310033305721E-2</v>
+      </c>
+      <c r="F64" s="4">
+        <f>13.07/1000</f>
+        <v>1.307E-2</v>
+      </c>
+      <c r="G64" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H64" s="6">
+        <f t="shared" si="0"/>
+        <v>26.14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B65" s="1">
+        <v>250</v>
+      </c>
+      <c r="C65" s="28">
+        <v>38684</v>
+      </c>
+      <c r="D65" s="28">
+        <v>42104.2256917017</v>
+      </c>
+      <c r="E65" s="3">
+        <f>D65/C65-1</f>
+        <v>8.8414478639791572E-2</v>
+      </c>
+      <c r="F65" s="4">
+        <f>18.63/1000</f>
+        <v>1.8630000000000001E-2</v>
+      </c>
+      <c r="G65" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H65" s="6">
+        <f t="shared" si="0"/>
+        <v>55.89</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B66" s="7">
+        <v>302</v>
+      </c>
+      <c r="C66" s="30">
+        <v>21736</v>
+      </c>
+      <c r="D66" s="29">
+        <v>22685.325526915502</v>
+      </c>
+      <c r="E66" s="3">
+        <f>D66/C66-1</f>
+        <v>4.367526347605355E-2</v>
+      </c>
+      <c r="F66" s="4">
+        <f>27.5/1000</f>
+        <v>2.75E-2</v>
+      </c>
+      <c r="G66" s="1">
+        <v>4000</v>
+      </c>
+      <c r="H66" s="1">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B67" s="7"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B68" s="7"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B69" s="7"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B70" s="7"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B71" s="7"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B72" s="7"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B73" s="7"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B74" s="7"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B75" s="7"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B76" s="7"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B77" s="7"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B78" s="7"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B79" s="7"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B80" s="7"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81" s="7"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B82" s="7"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="7"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="7"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B85" s="7"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="7"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="7"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B88" s="7"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B89" s="7"/>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B90" s="7"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B91" s="7"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B92" s="7"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B93" s="7"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B94" s="7"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B95" s="7"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96" s="7"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="7"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="7"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99" s="7"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="7"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="7"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="7"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" s="7"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="7"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="7"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="7"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="7"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="7"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="7"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" s="7"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="7"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="7"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="7"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="7"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="7"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="7"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="7"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="7"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="7"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="7"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" s="7"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" s="7"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="7"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="7"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="7"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="7"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="7"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128" s="7"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="7"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="7"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="7"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" s="7"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133" s="7"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134" s="7"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B135" s="7"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="7"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B137" s="7"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138" s="7"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="7"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B140" s="7"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B141" s="7"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B142" s="7"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B143" s="7"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B144" s="7"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145" s="7"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146" s="7"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147" s="7"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148" s="7"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" s="7"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150" s="7"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151" s="7"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B152" s="7"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B153" s="7"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B154" s="7"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B155" s="7"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B156" s="7"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B157" s="7"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B158" s="7"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B159" s="7"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B160" s="7"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" s="7"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" s="7"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B163" s="7"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B164" s="7"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B165" s="7"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B166" s="7"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B167" s="7"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B168" s="7"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B169" s="7"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B170" s="7"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B171" s="7"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B172" s="7"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B173" s="7"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B174" s="7"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B175" s="7"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B176" s="7"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B177" s="7"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B178" s="7"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B179" s="7"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B180" s="7"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B181" s="7"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B182" s="7"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B183" s="7"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B184" s="7"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B185" s="7"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B186" s="7"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B187" s="7"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B188" s="7"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B189" s="7"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B190" s="7"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B191" s="7"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B192" s="7"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B193" s="7"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B194" s="7"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B195" s="7"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B196" s="7"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B197" s="7"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B198" s="7"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B199" s="7"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B200" s="7"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B201" s="7"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B202" s="7"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B203" s="7"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B204" s="7"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B205" s="7"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B206" s="7"/>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B207" s="7"/>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B208" s="7"/>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B209" s="7"/>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B210" s="7"/>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B211" s="7"/>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B212" s="7"/>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B213" s="7"/>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B214" s="7"/>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B215" s="7"/>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B216" s="7"/>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B217" s="7"/>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B218" s="7"/>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B219" s="7"/>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B220" s="7"/>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B221" s="7"/>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B222" s="7"/>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B223" s="7"/>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B224" s="7"/>
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B225" s="7"/>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B226" s="7"/>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B227" s="7"/>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B228" s="7"/>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B229" s="7"/>
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B230" s="7"/>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B231" s="7"/>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B232" s="7"/>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B233" s="7"/>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B234" s="7"/>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B235" s="7"/>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B236" s="7"/>
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B237" s="7"/>
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B238" s="7"/>
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B239" s="7"/>
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B240" s="7"/>
+    </row>
+    <row r="241" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B241" s="7"/>
+    </row>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B242" s="7"/>
+    </row>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B243" s="7"/>
+    </row>
+    <row r="244" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B244" s="7"/>
+    </row>
+    <row r="245" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B245" s="7"/>
+    </row>
+    <row r="246" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B246" s="7"/>
+    </row>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B247" s="7"/>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B248" s="7"/>
+    </row>
+    <row r="249" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B249" s="7"/>
+    </row>
+    <row r="250" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B250" s="7"/>
+    </row>
+    <row r="251" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B251" s="7"/>
+    </row>
+    <row r="252" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B252" s="7"/>
+    </row>
+    <row r="253" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B253" s="7"/>
+    </row>
+    <row r="254" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B254" s="7"/>
+    </row>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B255" s="7"/>
+    </row>
+    <row r="256" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B256" s="7"/>
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B257" s="7"/>
+    </row>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B258" s="7"/>
+    </row>
+    <row r="259" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B259" s="7"/>
+    </row>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B260" s="7"/>
+    </row>
+    <row r="261" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B261" s="7"/>
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B262" s="7"/>
+    </row>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B263" s="7"/>
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B264" s="7"/>
+    </row>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B265" s="7"/>
+    </row>
+    <row r="266" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B266" s="7"/>
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B267" s="7"/>
+    </row>
+    <row r="268" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B268" s="7"/>
+    </row>
+    <row r="269" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B269" s="7"/>
+    </row>
+    <row r="270" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B270" s="7"/>
+    </row>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B271" s="7"/>
+    </row>
+    <row r="272" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B272" s="7"/>
+    </row>
+    <row r="273" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B273" s="7"/>
+    </row>
+    <row r="274" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B274" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X280"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.15" x14ac:dyDescent="0.25"/>
@@ -801,7 +2394,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.05" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -965,7 +2558,7 @@
     </row>
     <row r="20" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B20" s="11"/>
       <c r="L20" s="12"/>
@@ -1713,15 +3306,15 @@
         <v>-1.6412392354492322E-3</v>
       </c>
       <c r="F65" s="5">
-        <f>4.79/1000</f>
-        <v>4.79E-3</v>
+        <f>4.77/1000</f>
+        <v>4.7699999999999999E-3</v>
       </c>
       <c r="G65" s="1">
         <v>2000</v>
       </c>
       <c r="H65" s="6">
         <f>F65 * G65</f>
-        <v>9.58</v>
+        <v>9.5399999999999991</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -1742,15 +3335,15 @@
         <v>-4.4820130025886917E-2</v>
       </c>
       <c r="F66" s="4">
-        <f>12.42/1000</f>
-        <v>1.242E-2</v>
+        <f>12.27/1000</f>
+        <v>1.227E-2</v>
       </c>
       <c r="G66" s="1">
         <v>2000</v>
       </c>
       <c r="H66" s="6">
         <f t="shared" ref="H66:H70" si="1">F66 * G66</f>
-        <v>24.84</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -1771,15 +3364,15 @@
         <v>-3.7795953302666163E-6</v>
       </c>
       <c r="F67" s="4">
-        <f>6.65/1000</f>
-        <v>6.6500000000000005E-3</v>
+        <f>6.41/1000</f>
+        <v>6.4099999999999999E-3</v>
       </c>
       <c r="G67" s="1">
         <v>2000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" si="1"/>
-        <v>13.3</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -1800,15 +3393,15 @@
         <v>-5.8207641997487514E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>22.92/1000</f>
-        <v>2.2920000000000003E-2</v>
+        <f>22.76/1000</f>
+        <v>2.2760000000000002E-2</v>
       </c>
       <c r="G68" s="1">
         <v>2000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>45.84</v>
+        <v>45.52</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -1829,15 +3422,15 @@
         <v>-1.57441856144237E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>12.69/1000</f>
-        <v>1.269E-2</v>
+        <f>5.4/1000</f>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="G69" s="1">
         <v>2000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>25.38</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -1858,15 +3451,15 @@
         <v>-7.7474249471089163E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>5.25/1000</f>
-        <v>5.2500000000000003E-3</v>
+        <f>12.43/1000</f>
+        <v>1.243E-2</v>
       </c>
       <c r="G70" s="1">
         <v>2000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>24.86</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F631D79-84C4-4324-A7BE-FCEAED795386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D4A533-99DC-41D3-8F91-867C52A8358E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-113" yWindow="-113" windowWidth="48309" windowHeight="26546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VRP Benchmarking" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
   <si>
     <t>Best known</t>
   </si>
@@ -71,15 +71,6 @@
     <t>                    :swap!</t>
   </si>
   <si>
-    <t>        σ₁  =   33                      ,</t>
-  </si>
-  <si>
-    <t>        σ₂  =   9                       ,</t>
-  </si>
-  <si>
-    <t>        σ₃  =   13                      ,</t>
-  </si>
-  <si>
     <t>        ω   =   0.05                    ,</t>
   </si>
   <si>
@@ -89,9 +80,6 @@
     <t>        𝜃   =   0.99975                 ,</t>
   </si>
   <si>
-    <t>        C̲   =   30                      ,</t>
-  </si>
-  <si>
     <t>        C̅   =   60                      ,</t>
   </si>
   <si>
@@ -284,18 +272,6 @@
     <t>:random</t>
   </si>
   <si>
-    <t>                    :worstnode!     ,  </t>
-  </si>
-  <si>
-    <t>                    :relatedroute!  ,</t>
-  </si>
-  <si>
-    <t>                    :worstroute!</t>
-  </si>
-  <si>
-    <t>                    :regret2!       ,</t>
-  </si>
-  <si>
     <t>m-n101-k10</t>
   </si>
   <si>
@@ -311,10 +287,19 @@
     <t>x-n303-k21</t>
   </si>
   <si>
-    <t>χ   = ALNSParameters(</t>
-  </si>
-  <si>
     <t>n = max(200, ceil(x, digits=-(length(digits(x))-1)))</t>
+  </si>
+  <si>
+    <t>        σ₁  =   15                      ,</t>
+  </si>
+  <si>
+    <t>        σ₂  =   10                      ,</t>
+  </si>
+  <si>
+    <t>        σ₃  =   3                       ,</t>
+  </si>
+  <si>
+    <t>        C̲   =   4                       ,</t>
   </si>
 </sst>
 </file>
@@ -504,7 +489,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -544,13 +529,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -836,22 +814,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB48D86-1312-4781-AFB7-1DCAC26244E4}">
   <dimension ref="A1:X274"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="3" width="9.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.05" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -859,7 +837,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
     </row>
-    <row r="2" spans="1:6" ht="15.05" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="19"/>
       <c r="B2" s="20"/>
       <c r="C2" s="21"/>
@@ -867,122 +845,122 @@
       <c r="E2" s="21"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="22"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -992,9 +970,9 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B18" s="8"/>
       <c r="L18" s="12"/>
@@ -1011,1364 +989,1231 @@
       <c r="W18" s="12"/>
       <c r="X18" s="12"/>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="L19" s="12"/>
+        <v>73</v>
+      </c>
+      <c r="B19" s="12"/>
       <c r="W19" s="12"/>
       <c r="X19" s="12"/>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="11"/>
-      <c r="L20" s="12"/>
+        <v>83</v>
+      </c>
+      <c r="B20" s="12"/>
       <c r="W20" s="12"/>
       <c r="X20" s="12"/>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="L21" s="12"/>
+        <v>51</v>
+      </c>
+      <c r="B21" s="12"/>
       <c r="U21" s="12"/>
       <c r="V21" s="12"/>
       <c r="W21" s="12"/>
       <c r="X21" s="12"/>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="L22" s="12"/>
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="12"/>
       <c r="U22" s="12"/>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="25" t="s">
-        <v>57</v>
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
       <c r="H23" s="12"/>
-      <c r="L23" s="12"/>
       <c r="U23" s="12"/>
       <c r="V23" s="12"/>
       <c r="W23" s="12"/>
       <c r="X23" s="12"/>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="25" t="s">
-        <v>58</v>
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
       <c r="H24" s="12"/>
-      <c r="L24" s="12"/>
       <c r="U24" s="12"/>
       <c r="V24" s="12"/>
       <c r="W24" s="12"/>
       <c r="X24" s="12"/>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="25" t="s">
-        <v>59</v>
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
       <c r="H25" s="12"/>
-      <c r="L25" s="12"/>
       <c r="U25" s="12"/>
       <c r="V25" s="12"/>
       <c r="W25" s="12"/>
       <c r="X25" s="12"/>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="25" t="s">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
       <c r="H26" s="12"/>
-      <c r="L26" s="12"/>
       <c r="U26" s="12"/>
       <c r="V26" s="12"/>
       <c r="W26" s="12"/>
       <c r="X26" s="12"/>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="L27" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="B27" s="12"/>
       <c r="U27" s="12"/>
       <c r="V27" s="12"/>
       <c r="W27" s="12"/>
       <c r="X27" s="12"/>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="L28" s="12"/>
+        <v>57</v>
+      </c>
+      <c r="B28" s="12"/>
       <c r="U28" s="12"/>
       <c r="V28" s="12"/>
       <c r="W28" s="12"/>
       <c r="X28" s="12"/>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="L29" s="12"/>
+        <v>58</v>
+      </c>
+      <c r="B29" s="12"/>
       <c r="U29" s="12"/>
       <c r="V29" s="12"/>
       <c r="W29" s="12"/>
       <c r="X29" s="12"/>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="11"/>
-      <c r="L30" s="12"/>
+        <v>59</v>
+      </c>
+      <c r="B30" s="12"/>
       <c r="U30" s="12"/>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
       <c r="X30" s="12"/>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="11"/>
-      <c r="L31" s="12"/>
+        <v>60</v>
+      </c>
+      <c r="B31" s="12"/>
       <c r="U31" s="12"/>
       <c r="V31" s="12"/>
       <c r="W31" s="12"/>
       <c r="X31" s="12"/>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B32" s="11"/>
-      <c r="L32" s="12"/>
+        <v>61</v>
+      </c>
+      <c r="B32" s="12"/>
       <c r="U32" s="12"/>
       <c r="V32" s="12"/>
       <c r="W32" s="12"/>
       <c r="X32" s="12"/>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="11"/>
-      <c r="L33" s="12"/>
+        <v>62</v>
+      </c>
+      <c r="B33" s="12"/>
       <c r="U33" s="12"/>
       <c r="V33" s="12"/>
       <c r="W33" s="12"/>
       <c r="X33" s="12"/>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="11"/>
-      <c r="L34" s="12"/>
+        <v>63</v>
+      </c>
+      <c r="B34" s="12"/>
       <c r="U34" s="12"/>
       <c r="V34" s="12"/>
       <c r="W34" s="12"/>
       <c r="X34" s="12"/>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="11"/>
-      <c r="L35" s="12"/>
+        <v>64</v>
+      </c>
+      <c r="B35" s="12"/>
       <c r="U35" s="12"/>
       <c r="V35" s="12"/>
       <c r="W35" s="12"/>
       <c r="X35" s="12"/>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="L36" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="B36" s="12"/>
       <c r="U36" s="12"/>
       <c r="V36" s="12"/>
       <c r="W36" s="12"/>
       <c r="X36" s="12"/>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="L37" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="B37" s="12"/>
       <c r="U37" s="12"/>
       <c r="V37" s="12"/>
       <c r="W37" s="12"/>
       <c r="X37" s="12"/>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B38" s="11"/>
-      <c r="L38" s="12"/>
+        <v>65</v>
+      </c>
+      <c r="B38" s="12"/>
       <c r="U38" s="12"/>
       <c r="V38" s="12"/>
       <c r="W38" s="12"/>
       <c r="X38" s="12"/>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="L39" s="12"/>
+        <v>66</v>
+      </c>
+      <c r="B39" s="12"/>
       <c r="U39" s="12"/>
       <c r="V39" s="12"/>
       <c r="W39" s="12"/>
       <c r="X39" s="12"/>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="L40" s="12"/>
+        <v>67</v>
+      </c>
+      <c r="B40" s="12"/>
       <c r="U40" s="12"/>
       <c r="V40" s="12"/>
       <c r="W40" s="12"/>
       <c r="X40" s="12"/>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B41" s="11"/>
-      <c r="L41" s="12"/>
+        <v>68</v>
+      </c>
+      <c r="B41" s="12"/>
       <c r="U41" s="12"/>
       <c r="V41" s="12"/>
       <c r="W41" s="12"/>
       <c r="X41" s="12"/>
     </row>
-    <row r="42" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
+        <v>7</v>
+      </c>
+      <c r="B42" s="12"/>
       <c r="H42" s="9"/>
-      <c r="L42" s="12"/>
       <c r="U42" s="12"/>
       <c r="V42" s="12"/>
       <c r="W42" s="12"/>
       <c r="X42" s="12"/>
     </row>
-    <row r="43" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
+        <v>17</v>
+      </c>
+      <c r="B43" s="12"/>
       <c r="H43" s="9"/>
-      <c r="L43" s="12"/>
       <c r="U43" s="12"/>
       <c r="V43" s="12"/>
       <c r="W43" s="12"/>
       <c r="X43" s="12"/>
     </row>
-    <row r="44" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
+        <v>18</v>
+      </c>
+      <c r="B44" s="12"/>
       <c r="H44" s="9"/>
-      <c r="L44" s="12"/>
       <c r="U44" s="12"/>
       <c r="V44" s="12"/>
       <c r="W44" s="12"/>
       <c r="X44" s="12"/>
     </row>
-    <row r="45" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
+        <v>69</v>
+      </c>
+      <c r="B45" s="12"/>
       <c r="H45" s="9"/>
-      <c r="L45" s="12"/>
       <c r="U45" s="12"/>
       <c r="V45" s="12"/>
       <c r="W45" s="12"/>
       <c r="X45" s="12"/>
     </row>
-    <row r="46" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="B46" s="12"/>
       <c r="H46" s="9"/>
-      <c r="L46" s="12"/>
       <c r="U46" s="12"/>
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
       <c r="X46" s="12"/>
     </row>
-    <row r="47" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="B47" s="12"/>
       <c r="H47" s="9"/>
-      <c r="L47" s="12"/>
       <c r="U47" s="12"/>
       <c r="V47" s="12"/>
       <c r="W47" s="12"/>
       <c r="X47" s="12"/>
     </row>
-    <row r="48" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="B48" s="12"/>
       <c r="H48" s="9"/>
-      <c r="L48" s="12"/>
       <c r="U48" s="12"/>
       <c r="V48" s="12"/>
       <c r="W48" s="12"/>
       <c r="X48" s="12"/>
     </row>
-    <row r="49" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
+        <v>7</v>
+      </c>
+      <c r="B49" s="12"/>
       <c r="H49" s="9"/>
-      <c r="L49" s="12"/>
       <c r="U49" s="12"/>
       <c r="V49" s="12"/>
       <c r="W49" s="12"/>
       <c r="X49" s="12"/>
     </row>
-    <row r="50" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
+        <v>84</v>
+      </c>
+      <c r="B50" s="12"/>
       <c r="H50" s="9"/>
-      <c r="L50" s="12"/>
       <c r="U50" s="12"/>
       <c r="V50" s="12"/>
       <c r="W50" s="12"/>
       <c r="X50" s="12"/>
     </row>
-    <row r="51" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
+        <v>85</v>
+      </c>
+      <c r="B51" s="12"/>
       <c r="H51" s="9"/>
-      <c r="L51" s="12"/>
       <c r="U51" s="12"/>
       <c r="V51" s="12"/>
       <c r="W51" s="12"/>
       <c r="X51" s="12"/>
     </row>
-    <row r="52" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B52" s="11"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
+        <v>86</v>
+      </c>
+      <c r="B52" s="12"/>
       <c r="H52" s="9"/>
-      <c r="L52" s="12"/>
       <c r="U52" s="12"/>
       <c r="V52" s="12"/>
       <c r="W52" s="12"/>
       <c r="X52" s="12"/>
     </row>
-    <row r="53" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="L53" s="12"/>
+        <v>11</v>
+      </c>
+      <c r="B53" s="12"/>
       <c r="U53" s="12"/>
       <c r="V53" s="12"/>
       <c r="W53" s="12"/>
       <c r="X53" s="12"/>
     </row>
-    <row r="54" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="L54" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="B54" s="12"/>
       <c r="U54" s="12"/>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
       <c r="X54" s="12"/>
     </row>
-    <row r="55" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B55" s="11"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="L55" s="12"/>
+        <v>13</v>
+      </c>
+      <c r="B55" s="12"/>
       <c r="U55" s="12"/>
       <c r="V55" s="12"/>
       <c r="W55" s="12"/>
       <c r="X55" s="12"/>
     </row>
-    <row r="56" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B56" s="11"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="L56" s="12"/>
+        <v>87</v>
+      </c>
+      <c r="B56" s="12"/>
       <c r="U56" s="12"/>
       <c r="V56" s="12"/>
       <c r="W56" s="12"/>
       <c r="X56" s="12"/>
     </row>
-    <row r="57" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B57" s="11"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="L57" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="B57" s="12"/>
       <c r="U57" s="12"/>
       <c r="V57" s="12"/>
       <c r="W57" s="12"/>
       <c r="X57" s="12"/>
     </row>
-    <row r="58" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B58" s="11"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="L58" s="12"/>
+        <v>15</v>
+      </c>
+      <c r="B58" s="12"/>
       <c r="U58" s="12"/>
       <c r="V58" s="12"/>
       <c r="W58" s="12"/>
       <c r="X58" s="12"/>
     </row>
-    <row r="59" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
-      <c r="A59" s="26"/>
-      <c r="B59" s="27"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="L59" s="12"/>
+    <row r="59" spans="1:24" ht="14" x14ac:dyDescent="0.3">
+      <c r="A59" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B59" s="12"/>
       <c r="U59" s="12"/>
       <c r="V59" s="12"/>
       <c r="W59" s="12"/>
       <c r="X59" s="12"/>
     </row>
-    <row r="60" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
-      <c r="A60" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B60" s="7"/>
+    <row r="60" spans="1:24" ht="14" x14ac:dyDescent="0.3">
+      <c r="A60" s="12" t="s">
+        <v>72</v>
+      </c>
       <c r="U60" s="12"/>
       <c r="V60" s="12"/>
     </row>
-    <row r="61" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
-      <c r="A61" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B61" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C61" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F61" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="G61" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H61" s="18" t="s">
-        <v>5</v>
+    <row r="61" spans="1:24" ht="14" x14ac:dyDescent="0.3">
+      <c r="A61" s="12" t="s">
+        <v>50</v>
       </c>
       <c r="U61" s="12"/>
       <c r="V61" s="12"/>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B62" s="2">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A63" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="7"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A64" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G64" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H64" s="18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B65" s="2">
         <v>100</v>
       </c>
-      <c r="C62" s="28">
+      <c r="C65" s="25">
         <v>820</v>
       </c>
-      <c r="D62" s="28">
-        <v>827.69699099363697</v>
-      </c>
-      <c r="E62" s="3">
-        <f>D62/C62-1</f>
-        <v>9.3865743824841363E-3</v>
-      </c>
-      <c r="F62" s="5">
-        <f>3.16/1000</f>
-        <v>3.16E-3</v>
-      </c>
-      <c r="G62" s="1">
-        <v>2000</v>
-      </c>
-      <c r="H62" s="6">
-        <f>F62 * G62</f>
-        <v>6.32</v>
-      </c>
-    </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B63" s="1">
-        <v>150</v>
-      </c>
-      <c r="C63" s="28">
-        <v>3055.23</v>
-      </c>
-      <c r="D63" s="29">
-        <v>3176.3473615429598</v>
-      </c>
-      <c r="E63" s="3">
-        <f>D63/C63-1</f>
-        <v>3.9642632974591141E-2</v>
-      </c>
-      <c r="F63" s="4">
-        <f>8.8/1000</f>
-        <v>8.8000000000000005E-3</v>
-      </c>
-      <c r="G63" s="1">
-        <v>2000</v>
-      </c>
-      <c r="H63" s="6">
-        <f t="shared" ref="H63:H66" si="0">F63 * G63</f>
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B64" s="2">
-        <v>200</v>
-      </c>
-      <c r="C64" s="28">
-        <v>1395.85</v>
-      </c>
-      <c r="D64" s="28">
-        <v>1363.1950523400101</v>
-      </c>
-      <c r="E64" s="3">
-        <f>D64/C64-1</f>
-        <v>-2.3394310033305721E-2</v>
-      </c>
-      <c r="F64" s="4">
-        <f>13.07/1000</f>
-        <v>1.307E-2</v>
-      </c>
-      <c r="G64" s="1">
-        <v>2000</v>
-      </c>
-      <c r="H64" s="6">
-        <f t="shared" si="0"/>
-        <v>26.14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B65" s="1">
-        <v>250</v>
-      </c>
-      <c r="C65" s="28">
-        <v>38684</v>
-      </c>
-      <c r="D65" s="28">
-        <v>42104.2256917017</v>
+      <c r="D65" s="25">
+        <v>819.55754418734</v>
       </c>
       <c r="E65" s="3">
         <f>D65/C65-1</f>
-        <v>8.8414478639791572E-2</v>
-      </c>
-      <c r="F65" s="4">
-        <f>18.63/1000</f>
-        <v>1.8630000000000001E-2</v>
+        <v>-5.3958025934142118E-4</v>
+      </c>
+      <c r="F65" s="5">
+        <f>3.34/1000</f>
+        <v>3.3399999999999997E-3</v>
       </c>
       <c r="G65" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="H65" s="6">
-        <f t="shared" si="0"/>
-        <v>55.89</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+        <f>F65 * G65</f>
+        <v>6.68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B66" s="7">
-        <v>302</v>
-      </c>
-      <c r="C66" s="30">
-        <v>21736</v>
-      </c>
-      <c r="D66" s="29">
-        <v>22685.325526915502</v>
+        <v>79</v>
+      </c>
+      <c r="B66" s="1">
+        <v>150</v>
+      </c>
+      <c r="C66" s="25">
+        <v>3055.23</v>
+      </c>
+      <c r="D66" s="26">
+        <v>3248.97084620633</v>
       </c>
       <c r="E66" s="3">
         <f>D66/C66-1</f>
-        <v>4.367526347605355E-2</v>
+        <v>6.3412851473155785E-2</v>
       </c>
       <c r="F66" s="4">
-        <f>27.5/1000</f>
-        <v>2.75E-2</v>
+        <f>8.61/1000</f>
+        <v>8.6099999999999996E-3</v>
       </c>
       <c r="G66" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H66" s="6">
+        <f t="shared" ref="H66:H69" si="0">F66 * G66</f>
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B67" s="2">
+        <v>200</v>
+      </c>
+      <c r="C67" s="25">
+        <v>1395.85</v>
+      </c>
+      <c r="D67" s="25">
+        <v>1350.25450876236</v>
+      </c>
+      <c r="E67" s="3">
+        <f>D67/C67-1</f>
+        <v>-3.2665036528022218E-2</v>
+      </c>
+      <c r="F67" s="4">
+        <f>11.26/1000</f>
+        <v>1.1259999999999999E-2</v>
+      </c>
+      <c r="G67" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H67" s="6">
+        <f t="shared" si="0"/>
+        <v>22.52</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B68" s="1">
+        <v>250</v>
+      </c>
+      <c r="C68" s="25">
+        <v>38684</v>
+      </c>
+      <c r="D68" s="25">
+        <v>41926.235613395198</v>
+      </c>
+      <c r="E68" s="3">
+        <f>D68/C68-1</f>
+        <v>8.3813349534567205E-2</v>
+      </c>
+      <c r="F68" s="4">
+        <f>17.68/1000</f>
+        <v>1.7680000000000001E-2</v>
+      </c>
+      <c r="G68" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H68" s="6">
+        <f t="shared" si="0"/>
+        <v>53.040000000000006</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B69" s="7">
+        <v>302</v>
+      </c>
+      <c r="C69" s="27">
+        <v>21736</v>
+      </c>
+      <c r="D69" s="26">
+        <v>22966.074241357201</v>
+      </c>
+      <c r="E69" s="3">
+        <f>D69/C69-1</f>
+        <v>5.6591564287688634E-2</v>
+      </c>
+      <c r="F69" s="4">
+        <f>24.64/1000</f>
+        <v>2.4640000000000002E-2</v>
+      </c>
+      <c r="G69" s="1">
         <v>4000</v>
       </c>
-      <c r="H66" s="1">
+      <c r="H69" s="1">
         <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B67" s="7"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B68" s="7"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="7"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+        <v>98.56</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B70" s="7"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B71" s="7"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B72" s="7"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B73" s="7"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B74" s="7"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B75" s="7"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B76" s="7"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B77" s="7"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B78" s="7"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B79" s="7"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B80" s="7"/>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B81" s="7"/>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B82" s="7"/>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B83" s="7"/>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B84" s="7"/>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B85" s="7"/>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B86" s="7"/>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B87" s="7"/>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B88" s="7"/>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B89" s="7"/>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B90" s="7"/>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B91" s="7"/>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B92" s="7"/>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B93" s="7"/>
     </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B94" s="7"/>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B95" s="7"/>
     </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B96" s="7"/>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B97" s="7"/>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B98" s="7"/>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B99" s="7"/>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B100" s="7"/>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B101" s="7"/>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B102" s="7"/>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B103" s="7"/>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B104" s="7"/>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B105" s="7"/>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B106" s="7"/>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B107" s="7"/>
     </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B108" s="7"/>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B109" s="7"/>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B110" s="7"/>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B111" s="7"/>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B112" s="7"/>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B113" s="7"/>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B114" s="7"/>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B115" s="7"/>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B116" s="7"/>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B117" s="7"/>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B118" s="7"/>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B119" s="7"/>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B120" s="7"/>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B121" s="7"/>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B122" s="7"/>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B123" s="7"/>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B124" s="7"/>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B125" s="7"/>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B126" s="7"/>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B127" s="7"/>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B128" s="7"/>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B129" s="7"/>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B130" s="7"/>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B131" s="7"/>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B132" s="7"/>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B133" s="7"/>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B134" s="7"/>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B135" s="7"/>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B136" s="7"/>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B137" s="7"/>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B138" s="7"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B139" s="7"/>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B140" s="7"/>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B141" s="7"/>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B142" s="7"/>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B143" s="7"/>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B144" s="7"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B145" s="7"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B146" s="7"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B147" s="7"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B148" s="7"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B149" s="7"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B150" s="7"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B151" s="7"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B152" s="7"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B153" s="7"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B154" s="7"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B155" s="7"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B156" s="7"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B157" s="7"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B158" s="7"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B159" s="7"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B160" s="7"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B161" s="7"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B162" s="7"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B163" s="7"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B164" s="7"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B165" s="7"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B166" s="7"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B167" s="7"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B168" s="7"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B169" s="7"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B170" s="7"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B171" s="7"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B172" s="7"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B173" s="7"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B174" s="7"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B175" s="7"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B176" s="7"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B177" s="7"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B178" s="7"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B179" s="7"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B180" s="7"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B181" s="7"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B182" s="7"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B183" s="7"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B184" s="7"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B185" s="7"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B186" s="7"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B187" s="7"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B188" s="7"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B189" s="7"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B190" s="7"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B191" s="7"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B192" s="7"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B193" s="7"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B194" s="7"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B195" s="7"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B196" s="7"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B197" s="7"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B198" s="7"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B199" s="7"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B200" s="7"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B201" s="7"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B202" s="7"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B203" s="7"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B204" s="7"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B205" s="7"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B206" s="7"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B207" s="7"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B208" s="7"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B209" s="7"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B210" s="7"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B211" s="7"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B212" s="7"/>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B213" s="7"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B214" s="7"/>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B215" s="7"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B216" s="7"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B217" s="7"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B218" s="7"/>
     </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B219" s="7"/>
     </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B220" s="7"/>
     </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B221" s="7"/>
     </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B222" s="7"/>
     </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B223" s="7"/>
     </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B224" s="7"/>
     </row>
-    <row r="225" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B225" s="7"/>
     </row>
-    <row r="226" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B226" s="7"/>
     </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B227" s="7"/>
     </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B228" s="7"/>
     </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B229" s="7"/>
     </row>
-    <row r="230" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B230" s="7"/>
     </row>
-    <row r="231" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B231" s="7"/>
     </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B232" s="7"/>
     </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B233" s="7"/>
     </row>
-    <row r="234" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B234" s="7"/>
     </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B235" s="7"/>
     </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B236" s="7"/>
     </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B237" s="7"/>
     </row>
-    <row r="238" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B238" s="7"/>
     </row>
-    <row r="239" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B239" s="7"/>
     </row>
-    <row r="240" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B240" s="7"/>
     </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B241" s="7"/>
     </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B242" s="7"/>
     </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B243" s="7"/>
     </row>
-    <row r="244" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B244" s="7"/>
     </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B245" s="7"/>
     </row>
-    <row r="246" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B246" s="7"/>
     </row>
-    <row r="247" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B247" s="7"/>
     </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B248" s="7"/>
     </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B249" s="7"/>
     </row>
-    <row r="250" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B250" s="7"/>
     </row>
-    <row r="251" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B251" s="7"/>
     </row>
-    <row r="252" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B252" s="7"/>
     </row>
-    <row r="253" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B253" s="7"/>
     </row>
-    <row r="254" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B254" s="7"/>
     </row>
-    <row r="255" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B255" s="7"/>
     </row>
-    <row r="256" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B256" s="7"/>
     </row>
-    <row r="257" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B257" s="7"/>
     </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B258" s="7"/>
     </row>
-    <row r="259" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B259" s="7"/>
     </row>
-    <row r="260" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B260" s="7"/>
     </row>
-    <row r="261" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B261" s="7"/>
     </row>
-    <row r="262" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B262" s="7"/>
     </row>
-    <row r="263" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B263" s="7"/>
     </row>
-    <row r="264" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B264" s="7"/>
     </row>
-    <row r="265" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B265" s="7"/>
     </row>
-    <row r="266" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B266" s="7"/>
     </row>
-    <row r="267" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B267" s="7"/>
     </row>
-    <row r="268" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B268" s="7"/>
     </row>
-    <row r="269" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B269" s="7"/>
     </row>
-    <row r="270" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B270" s="7"/>
     </row>
-    <row r="271" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B271" s="7"/>
     </row>
-    <row r="272" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B272" s="7"/>
     </row>
-    <row r="273" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B273" s="7"/>
     </row>
-    <row r="274" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B274" s="7"/>
     </row>
   </sheetData>
@@ -2379,22 +2224,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X280"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="3" width="9.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.05" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -2402,7 +2247,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
     </row>
-    <row r="2" spans="1:6" ht="15.05" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="19"/>
       <c r="B2" s="20"/>
       <c r="C2" s="21"/>
@@ -2410,127 +2255,127 @@
       <c r="E2" s="21"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:6" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="8"/>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B18" s="8"/>
       <c r="L18" s="12"/>
@@ -2547,27 +2392,27 @@
       <c r="W18" s="12"/>
       <c r="X18" s="12"/>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B19" s="11"/>
       <c r="L19" s="12"/>
       <c r="W19" s="12"/>
       <c r="X19" s="12"/>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B20" s="11"/>
       <c r="L20" s="12"/>
       <c r="W20" s="12"/>
       <c r="X20" s="12"/>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -2582,9 +2427,9 @@
       <c r="W21" s="12"/>
       <c r="X21" s="12"/>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -2599,9 +2444,9 @@
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -2616,9 +2461,9 @@
       <c r="W23" s="12"/>
       <c r="X23" s="12"/>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -2633,9 +2478,9 @@
       <c r="W24" s="12"/>
       <c r="X24" s="12"/>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -2650,7 +2495,7 @@
       <c r="W25" s="12"/>
       <c r="X25" s="12"/>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="12" t="s">
         <v>8</v>
       </c>
@@ -2667,9 +2512,9 @@
       <c r="W26" s="12"/>
       <c r="X26" s="12"/>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -2684,9 +2529,9 @@
       <c r="W27" s="12"/>
       <c r="X27" s="12"/>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -2701,9 +2546,9 @@
       <c r="W28" s="12"/>
       <c r="X28" s="12"/>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -2718,9 +2563,9 @@
       <c r="W29" s="12"/>
       <c r="X29" s="12"/>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -2735,9 +2580,9 @@
       <c r="W30" s="12"/>
       <c r="X30" s="12"/>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -2752,9 +2597,9 @@
       <c r="W31" s="12"/>
       <c r="X31" s="12"/>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -2769,9 +2614,9 @@
       <c r="W32" s="12"/>
       <c r="X32" s="12"/>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -2786,9 +2631,9 @@
       <c r="W33" s="12"/>
       <c r="X33" s="12"/>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -2803,9 +2648,9 @@
       <c r="W34" s="12"/>
       <c r="X34" s="12"/>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -2820,7 +2665,7 @@
       <c r="W35" s="12"/>
       <c r="X35" s="12"/>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
         <v>6</v>
       </c>
@@ -2837,7 +2682,7 @@
       <c r="W36" s="12"/>
       <c r="X36" s="12"/>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12" t="s">
         <v>9</v>
       </c>
@@ -2854,9 +2699,9 @@
       <c r="W37" s="12"/>
       <c r="X37" s="12"/>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -2871,9 +2716,9 @@
       <c r="W38" s="12"/>
       <c r="X38" s="12"/>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -2888,9 +2733,9 @@
       <c r="W39" s="12"/>
       <c r="X39" s="12"/>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -2905,9 +2750,9 @@
       <c r="W40" s="12"/>
       <c r="X40" s="12"/>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="12.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -2922,7 +2767,7 @@
       <c r="W41" s="12"/>
       <c r="X41" s="12"/>
     </row>
-    <row r="42" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>7</v>
       </c>
@@ -2939,9 +2784,9 @@
       <c r="W42" s="12"/>
       <c r="X42" s="12"/>
     </row>
-    <row r="43" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -2956,9 +2801,9 @@
       <c r="W43" s="12"/>
       <c r="X43" s="12"/>
     </row>
-    <row r="44" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -2973,9 +2818,9 @@
       <c r="W44" s="12"/>
       <c r="X44" s="12"/>
     </row>
-    <row r="45" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
@@ -2990,9 +2835,9 @@
       <c r="W45" s="12"/>
       <c r="X45" s="12"/>
     </row>
-    <row r="46" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -3007,9 +2852,9 @@
       <c r="W46" s="12"/>
       <c r="X46" s="12"/>
     </row>
-    <row r="47" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -3024,7 +2869,7 @@
       <c r="W47" s="12"/>
       <c r="X47" s="12"/>
     </row>
-    <row r="48" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
         <v>10</v>
       </c>
@@ -3041,7 +2886,7 @@
       <c r="W48" s="12"/>
       <c r="X48" s="12"/>
     </row>
-    <row r="49" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
         <v>7</v>
       </c>
@@ -3058,9 +2903,9 @@
       <c r="W49" s="12"/>
       <c r="X49" s="12"/>
     </row>
-    <row r="50" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
@@ -3075,9 +2920,9 @@
       <c r="W50" s="12"/>
       <c r="X50" s="12"/>
     </row>
-    <row r="51" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
@@ -3092,9 +2937,9 @@
       <c r="W51" s="12"/>
       <c r="X51" s="12"/>
     </row>
-    <row r="52" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -3109,9 +2954,9 @@
       <c r="W52" s="12"/>
       <c r="X52" s="12"/>
     </row>
-    <row r="53" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -3126,9 +2971,9 @@
       <c r="W53" s="12"/>
       <c r="X53" s="12"/>
     </row>
-    <row r="54" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
@@ -3143,9 +2988,9 @@
       <c r="W54" s="12"/>
       <c r="X54" s="12"/>
     </row>
-    <row r="55" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
@@ -3160,9 +3005,9 @@
       <c r="W55" s="12"/>
       <c r="X55" s="12"/>
     </row>
-    <row r="56" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
@@ -3177,9 +3022,9 @@
       <c r="W56" s="12"/>
       <c r="X56" s="12"/>
     </row>
-    <row r="57" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
@@ -3194,9 +3039,9 @@
       <c r="W57" s="12"/>
       <c r="X57" s="12"/>
     </row>
-    <row r="58" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
@@ -3211,9 +3056,9 @@
       <c r="W58" s="12"/>
       <c r="X58" s="12"/>
     </row>
-    <row r="59" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -3228,9 +3073,9 @@
       <c r="W59" s="12"/>
       <c r="X59" s="12"/>
     </row>
-    <row r="60" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -3242,9 +3087,9 @@
       <c r="U60" s="12"/>
       <c r="V60" s="12"/>
     </row>
-    <row r="61" spans="1:24" ht="15.05" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -3256,18 +3101,18 @@
       <c r="U61" s="12"/>
       <c r="V61" s="12"/>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B63" s="7"/>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64" s="18" t="s">
         <v>2</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C64" s="18" t="s">
         <v>0</v>
@@ -3282,15 +3127,15 @@
         <v>4</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H64" s="18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B65" s="2">
         <v>100</v>
@@ -3299,27 +3144,27 @@
         <v>1645.79</v>
       </c>
       <c r="D65" s="6">
-        <v>1643.0888648786899</v>
+        <v>1646.14187215677</v>
       </c>
       <c r="E65" s="3">
         <f>D65/C65-1</f>
-        <v>-1.6412392354492322E-3</v>
+        <v>2.1380137002302568E-4</v>
       </c>
       <c r="F65" s="5">
-        <f>4.77/1000</f>
-        <v>4.7699999999999999E-3</v>
+        <f>4.87/1000</f>
+        <v>4.8700000000000002E-3</v>
       </c>
       <c r="G65" s="1">
         <v>2000</v>
       </c>
       <c r="H65" s="6">
         <f>F65 * G65</f>
-        <v>9.5399999999999991</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+        <v>9.74</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B66" s="2">
         <v>100</v>
@@ -3328,27 +3173,27 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="D66" s="24">
-        <v>1196.2386137594799</v>
+        <v>1252.52213113828</v>
       </c>
       <c r="E66" s="3">
         <f t="shared" ref="E66:E70" si="0">D66/C66-1</f>
-        <v>-4.4820130025886917E-2</v>
+        <v>1.2147459479239231E-4</v>
       </c>
       <c r="F66" s="4">
-        <f>12.27/1000</f>
-        <v>1.227E-2</v>
+        <f>12.99/1000</f>
+        <v>1.299E-2</v>
       </c>
       <c r="G66" s="1">
         <v>2000</v>
       </c>
       <c r="H66" s="6">
         <f t="shared" ref="H66:H70" si="1">F66 * G66</f>
-        <v>24.54</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+        <v>25.98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B67" s="2">
         <v>100</v>
@@ -3357,27 +3202,27 @@
         <v>828.94</v>
       </c>
       <c r="D67" s="6">
-        <v>828.93686694224698</v>
+        <v>828.93686694232395</v>
       </c>
       <c r="E67" s="3">
         <f t="shared" si="0"/>
-        <v>-3.7795953302666163E-6</v>
+        <v>-3.7795952374519715E-6</v>
       </c>
       <c r="F67" s="4">
-        <f>6.41/1000</f>
-        <v>6.4099999999999999E-3</v>
+        <f>6.45/1000</f>
+        <v>6.45E-3</v>
       </c>
       <c r="G67" s="1">
         <v>2000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" si="1"/>
-        <v>12.82</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B68" s="2">
         <v>100</v>
@@ -3386,27 +3231,27 @@
         <v>591.55999999999995</v>
       </c>
       <c r="D68" s="6">
-        <v>591.55655666872997</v>
+        <v>591.556556669016</v>
       </c>
       <c r="E68" s="3">
         <f t="shared" si="0"/>
-        <v>-5.8207641997487514E-6</v>
+        <v>-5.8207637161356018E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>22.76/1000</f>
-        <v>2.2760000000000002E-2</v>
+        <f>19.75/1000</f>
+        <v>1.975E-2</v>
       </c>
       <c r="G68" s="1">
         <v>2000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>45.52</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B69" s="2">
         <v>100</v>
@@ -3415,11 +3260,11 @@
         <v>1696.94</v>
       </c>
       <c r="D69" s="6">
-        <v>1670.2230616634599</v>
+        <v>1674.22713950244</v>
       </c>
       <c r="E69" s="3">
         <f t="shared" si="0"/>
-        <v>-1.57441856144237E-2</v>
+        <v>-1.3384598452249374E-2</v>
       </c>
       <c r="F69" s="4">
         <f>5.4/1000</f>
@@ -3433,9 +3278,9 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B70" s="2">
         <v>100</v>
@@ -3444,652 +3289,652 @@
         <v>1406.91</v>
       </c>
       <c r="D70" s="24">
-        <v>1297.91070367663</v>
+        <v>1328.0509959371</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-7.7474249471089163E-2</v>
+        <v>-5.6051207300324868E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>12.43/1000</f>
-        <v>1.243E-2</v>
+        <f>10.83/1000</f>
+        <v>1.0829999999999999E-2</v>
       </c>
       <c r="G70" s="1">
         <v>2000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>24.86</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+        <v>21.66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B71" s="7"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B72" s="7"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B73" s="7"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B74" s="7"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B75" s="7"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B76" s="7"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B77" s="7"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B78" s="7"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B79" s="7"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B80" s="7"/>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B81" s="7"/>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B82" s="7"/>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B83" s="7"/>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B84" s="7"/>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B85" s="7"/>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B86" s="7"/>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B87" s="7"/>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B88" s="7"/>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B89" s="7"/>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B90" s="7"/>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B91" s="7"/>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B92" s="7"/>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B93" s="7"/>
     </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B94" s="7"/>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B95" s="7"/>
     </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B96" s="7"/>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B97" s="7"/>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B98" s="7"/>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B99" s="7"/>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B100" s="7"/>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B101" s="7"/>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B102" s="7"/>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B103" s="7"/>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B104" s="7"/>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B105" s="7"/>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B106" s="7"/>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B107" s="7"/>
     </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B108" s="7"/>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B109" s="7"/>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B110" s="7"/>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B111" s="7"/>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B112" s="7"/>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B113" s="7"/>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B114" s="7"/>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B115" s="7"/>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B116" s="7"/>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B117" s="7"/>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B118" s="7"/>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B119" s="7"/>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B120" s="7"/>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B121" s="7"/>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B122" s="7"/>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B123" s="7"/>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B124" s="7"/>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B125" s="7"/>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B126" s="7"/>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B127" s="7"/>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B128" s="7"/>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B129" s="7"/>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B130" s="7"/>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B131" s="7"/>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B132" s="7"/>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B133" s="7"/>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B134" s="7"/>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B135" s="7"/>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B136" s="7"/>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B137" s="7"/>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B138" s="7"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B139" s="7"/>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B140" s="7"/>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B141" s="7"/>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B142" s="7"/>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B143" s="7"/>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B144" s="7"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B145" s="7"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B146" s="7"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B147" s="7"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B148" s="7"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B149" s="7"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B150" s="7"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B151" s="7"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B152" s="7"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B153" s="7"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B154" s="7"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B155" s="7"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B156" s="7"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B157" s="7"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B158" s="7"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B159" s="7"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B160" s="7"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B161" s="7"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B162" s="7"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B163" s="7"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B164" s="7"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B165" s="7"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B166" s="7"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B167" s="7"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B168" s="7"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B169" s="7"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B170" s="7"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B171" s="7"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B172" s="7"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B173" s="7"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B174" s="7"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B175" s="7"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B176" s="7"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B177" s="7"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B178" s="7"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B179" s="7"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B180" s="7"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B181" s="7"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B182" s="7"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B183" s="7"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B184" s="7"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B185" s="7"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B186" s="7"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B187" s="7"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B188" s="7"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B189" s="7"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B190" s="7"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B191" s="7"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B192" s="7"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B193" s="7"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B194" s="7"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B195" s="7"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B196" s="7"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B197" s="7"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B198" s="7"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B199" s="7"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B200" s="7"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B201" s="7"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B202" s="7"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B203" s="7"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B204" s="7"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B205" s="7"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B206" s="7"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B207" s="7"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B208" s="7"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B209" s="7"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B210" s="7"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B211" s="7"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B212" s="7"/>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B213" s="7"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B214" s="7"/>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B215" s="7"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B216" s="7"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B217" s="7"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B218" s="7"/>
     </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B219" s="7"/>
     </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B220" s="7"/>
     </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B221" s="7"/>
     </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B222" s="7"/>
     </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B223" s="7"/>
     </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B224" s="7"/>
     </row>
-    <row r="225" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B225" s="7"/>
     </row>
-    <row r="226" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B226" s="7"/>
     </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B227" s="7"/>
     </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B228" s="7"/>
     </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B229" s="7"/>
     </row>
-    <row r="230" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B230" s="7"/>
     </row>
-    <row r="231" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B231" s="7"/>
     </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B232" s="7"/>
     </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B233" s="7"/>
     </row>
-    <row r="234" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B234" s="7"/>
     </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B235" s="7"/>
     </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B236" s="7"/>
     </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B237" s="7"/>
     </row>
-    <row r="238" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B238" s="7"/>
     </row>
-    <row r="239" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B239" s="7"/>
     </row>
-    <row r="240" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B240" s="7"/>
     </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B241" s="7"/>
     </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B242" s="7"/>
     </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B243" s="7"/>
     </row>
-    <row r="244" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B244" s="7"/>
     </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B245" s="7"/>
     </row>
-    <row r="246" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B246" s="7"/>
     </row>
-    <row r="247" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B247" s="7"/>
     </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B248" s="7"/>
     </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B249" s="7"/>
     </row>
-    <row r="250" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B250" s="7"/>
     </row>
-    <row r="251" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B251" s="7"/>
     </row>
-    <row r="252" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B252" s="7"/>
     </row>
-    <row r="253" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B253" s="7"/>
     </row>
-    <row r="254" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B254" s="7"/>
     </row>
-    <row r="255" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B255" s="7"/>
     </row>
-    <row r="256" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B256" s="7"/>
     </row>
-    <row r="257" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B257" s="7"/>
     </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B258" s="7"/>
     </row>
-    <row r="259" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B259" s="7"/>
     </row>
-    <row r="260" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B260" s="7"/>
     </row>
-    <row r="261" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B261" s="7"/>
     </row>
-    <row r="262" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B262" s="7"/>
     </row>
-    <row r="263" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B263" s="7"/>
     </row>
-    <row r="264" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B264" s="7"/>
     </row>
-    <row r="265" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B265" s="7"/>
     </row>
-    <row r="266" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B266" s="7"/>
     </row>
-    <row r="267" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B267" s="7"/>
     </row>
-    <row r="268" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B268" s="7"/>
     </row>
-    <row r="269" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B269" s="7"/>
     </row>
-    <row r="270" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B270" s="7"/>
     </row>
-    <row r="271" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B271" s="7"/>
     </row>
-    <row r="272" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B272" s="7"/>
     </row>
-    <row r="273" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B273" s="7"/>
     </row>
-    <row r="274" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B274" s="7"/>
     </row>
-    <row r="275" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B275" s="7"/>
     </row>
-    <row r="276" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B276" s="7"/>
     </row>
-    <row r="277" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B277" s="7"/>
     </row>
-    <row r="278" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B278" s="7"/>
     </row>
-    <row r="279" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B279" s="7"/>
     </row>
-    <row r="280" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B280" s="7"/>
     </row>
   </sheetData>

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D4A533-99DC-41D3-8F91-867C52A8358E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8630F1D6-8AC1-4ADB-A04E-FD2A55301E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VRP Benchmarking" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="89">
   <si>
     <t>Best known</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t>        C̲   =   4                       ,</t>
+  </si>
+  <si>
+    <t>n = max(500, ceil(x, digits=-(length(digits(x))-1)))</t>
   </si>
 </sst>
 </file>
@@ -2403,7 +2406,7 @@
     </row>
     <row r="20" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B20" s="11"/>
       <c r="L20" s="12"/>
@@ -3144,22 +3147,22 @@
         <v>1645.79</v>
       </c>
       <c r="D65" s="6">
-        <v>1646.14187215677</v>
+        <v>1645.83732633817</v>
       </c>
       <c r="E65" s="3">
         <f>D65/C65-1</f>
-        <v>2.1380137002302568E-4</v>
+        <v>2.8756000565177686E-5</v>
       </c>
       <c r="F65" s="5">
-        <f>4.87/1000</f>
-        <v>4.8700000000000002E-3</v>
+        <f>4.68/1000</f>
+        <v>4.6800000000000001E-3</v>
       </c>
       <c r="G65" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H65" s="6">
         <f>F65 * G65</f>
-        <v>9.74</v>
+        <v>23.400000000000002</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
@@ -3173,22 +3176,22 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="D66" s="24">
-        <v>1252.52213113828</v>
+        <v>1184.5618570060401</v>
       </c>
       <c r="E66" s="3">
         <f t="shared" ref="E66:E70" si="0">D66/C66-1</f>
-        <v>1.2147459479239231E-4</v>
+        <v>-5.4143857641080317E-2</v>
       </c>
       <c r="F66" s="4">
-        <f>12.99/1000</f>
-        <v>1.299E-2</v>
+        <f>11.57/1000</f>
+        <v>1.157E-2</v>
       </c>
       <c r="G66" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f t="shared" ref="H66:H70" si="1">F66 * G66</f>
-        <v>25.98</v>
+        <v>57.85</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -3202,22 +3205,22 @@
         <v>828.94</v>
       </c>
       <c r="D67" s="6">
-        <v>828.93686694232395</v>
+        <v>828.93686694150995</v>
       </c>
       <c r="E67" s="3">
         <f t="shared" si="0"/>
-        <v>-3.7795952374519715E-6</v>
+        <v>-3.7795962194442367E-6</v>
       </c>
       <c r="F67" s="4">
-        <f>6.45/1000</f>
-        <v>6.45E-3</v>
+        <f>5.94/1000</f>
+        <v>5.94E-3</v>
       </c>
       <c r="G67" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" si="1"/>
-        <v>12.9</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -3231,22 +3234,22 @@
         <v>591.55999999999995</v>
       </c>
       <c r="D68" s="6">
-        <v>591.556556669016</v>
+        <v>591.55655666593805</v>
       </c>
       <c r="E68" s="3">
         <f t="shared" si="0"/>
-        <v>-5.8207637161356018E-6</v>
+        <v>-5.820768919306829E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>19.75/1000</f>
-        <v>1.975E-2</v>
+        <f>21.03/1000</f>
+        <v>2.103E-2</v>
       </c>
       <c r="G68" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>39.5</v>
+        <v>105.15</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -3260,22 +3263,22 @@
         <v>1696.94</v>
       </c>
       <c r="D69" s="6">
-        <v>1674.22713950244</v>
+        <v>1675.1266262731599</v>
       </c>
       <c r="E69" s="3">
         <f t="shared" si="0"/>
-        <v>-1.3384598452249374E-2</v>
+        <v>-1.2854534471955503E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>5.4/1000</f>
-        <v>5.4000000000000003E-3</v>
+        <f>4.92/1000</f>
+        <v>4.9199999999999999E-3</v>
       </c>
       <c r="G69" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>10.8</v>
+        <v>24.599999999999998</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -3289,22 +3292,22 @@
         <v>1406.91</v>
       </c>
       <c r="D70" s="24">
-        <v>1328.0509959371</v>
+        <v>1310.3079013464001</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-5.6051207300324868E-2</v>
+        <v>-6.8662600062264101E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>10.83/1000</f>
-        <v>1.0829999999999999E-2</v>
+        <f>9.42/1000</f>
+        <v>9.4199999999999996E-3</v>
       </c>
       <c r="G70" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>21.66</v>
+        <v>47.099999999999994</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8630F1D6-8AC1-4ADB-A04E-FD2A55301E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC696659-528D-4C69-98D7-B64DB642E9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VRP Benchmarking" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="89">
   <si>
     <t>Best known</t>
   </si>
@@ -161,9 +161,6 @@
     <t>Initialization</t>
   </si>
   <si>
-    <t>:cw_init</t>
-  </si>
-  <si>
     <t>rng</t>
   </si>
   <si>
@@ -191,9 +188,6 @@
     <t>    );</t>
   </si>
   <si>
-    <t>χ = ALNSParameters(</t>
-  </si>
-  <si>
     <t>        k̲   =   n ÷ 25                  ,</t>
   </si>
   <si>
@@ -233,12 +227,6 @@
     <t>                    :worstvehicle!  </t>
   </si>
   <si>
-    <t>                    :best!          ,</t>
-  </si>
-  <si>
-    <t>                    :greedy!        ,</t>
-  </si>
-  <si>
     <t>                    :regret2!       ,</t>
   </si>
   <si>
@@ -257,9 +245,6 @@
     <t>        ρ   =   0.1</t>
   </si>
   <si>
-    <t>x = length(N)</t>
-  </si>
-  <si>
     <t>Vehicle Routing Problem with Time-Windows (VRPTW) Benchmarking</t>
   </si>
   <si>
@@ -287,22 +272,37 @@
     <t>x-n303-k21</t>
   </si>
   <si>
-    <t>n = max(200, ceil(x, digits=-(length(digits(x))-1)))</t>
-  </si>
-  <si>
     <t>        σ₁  =   15                      ,</t>
   </si>
   <si>
-    <t>        σ₂  =   10                      ,</t>
-  </si>
-  <si>
-    <t>        σ₃  =   3                       ,</t>
-  </si>
-  <si>
-    <t>        C̲   =   4                       ,</t>
-  </si>
-  <si>
-    <t>n = max(500, ceil(x, digits=-(length(digits(x))-1)))</t>
+    <t>                    :bestprecise!   ,</t>
+  </si>
+  <si>
+    <t>                    :greedyprecise! ,</t>
+  </si>
+  <si>
+    <t>    n = max(500, ceil(x, digits=-(length(digits(x))-1)));</t>
+  </si>
+  <si>
+    <t>    χ = ALNSParameters(</t>
+  </si>
+  <si>
+    <t>        σ₂  =   10                      ,</t>
+  </si>
+  <si>
+    <t>        σ₃  =   3                       ,</t>
+  </si>
+  <si>
+    <t>        C̲   =   4                       ,</t>
+  </si>
+  <si>
+    <t>    x = length(N)</t>
+  </si>
+  <si>
+    <t>                    :bestperturb!   ,</t>
+  </si>
+  <si>
+    <t>                    :greedyperturb! ,</t>
   </si>
 </sst>
 </file>
@@ -832,7 +832,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -947,20 +947,20 @@
     </row>
     <row r="15" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -994,7 +994,7 @@
     </row>
     <row r="19" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B19" s="12"/>
       <c r="W19" s="12"/>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="20" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B20" s="12"/>
       <c r="W20" s="12"/>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="21" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B21" s="12"/>
       <c r="U21" s="12"/>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="22" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B22" s="12"/>
       <c r="U22" s="12"/>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="23" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B23" s="12"/>
       <c r="H23" s="12"/>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="24" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B24" s="12"/>
       <c r="H24" s="12"/>
@@ -1052,7 +1052,7 @@
     </row>
     <row r="25" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B25" s="12"/>
       <c r="H25" s="12"/>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="27" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B27" s="12"/>
       <c r="U27" s="12"/>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="28" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B28" s="12"/>
       <c r="U28" s="12"/>
@@ -1094,7 +1094,7 @@
     </row>
     <row r="29" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B29" s="12"/>
       <c r="U29" s="12"/>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="30" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B30" s="12"/>
       <c r="U30" s="12"/>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="31" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B31" s="12"/>
       <c r="U31" s="12"/>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="32" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B32" s="12"/>
       <c r="U32" s="12"/>
@@ -1134,7 +1134,7 @@
     </row>
     <row r="33" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B33" s="12"/>
       <c r="U33" s="12"/>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="34" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B34" s="12"/>
       <c r="U34" s="12"/>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="35" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B35" s="12"/>
       <c r="U35" s="12"/>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="38" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B38" s="12"/>
       <c r="U38" s="12"/>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="39" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="B39" s="12"/>
       <c r="U39" s="12"/>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="40" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B40" s="12"/>
       <c r="U40" s="12"/>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="41" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B41" s="12"/>
       <c r="U41" s="12"/>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="45" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B45" s="12"/>
       <c r="H45" s="9"/>
@@ -1268,7 +1268,7 @@
     </row>
     <row r="46" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B46" s="12"/>
       <c r="H46" s="9"/>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="47" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B47" s="12"/>
       <c r="H47" s="9"/>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="50" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B50" s="12"/>
       <c r="H50" s="9"/>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="51" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B51" s="12"/>
       <c r="H51" s="9"/>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="52" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B52" s="12"/>
       <c r="H52" s="9"/>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="56" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B56" s="12"/>
       <c r="U56" s="12"/>
@@ -1415,14 +1415,14 @@
     </row>
     <row r="60" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="U60" s="12"/>
       <c r="V60" s="12"/>
     </row>
     <row r="61" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="U61" s="12"/>
       <c r="V61" s="12"/>
@@ -1461,7 +1461,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B65" s="2">
         <v>100</v>
@@ -1470,27 +1470,27 @@
         <v>820</v>
       </c>
       <c r="D65" s="25">
-        <v>819.55754418734</v>
+        <v>819.55754418720403</v>
       </c>
       <c r="E65" s="3">
         <f>D65/C65-1</f>
-        <v>-5.3958025934142118E-4</v>
+        <v>-5.395802595072885E-4</v>
       </c>
       <c r="F65" s="5">
-        <f>3.34/1000</f>
-        <v>3.3399999999999997E-3</v>
+        <f>3.06/1000</f>
+        <v>3.0600000000000002E-3</v>
       </c>
       <c r="G65" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H65" s="6">
         <f>F65 * G65</f>
-        <v>6.68</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B66" s="1">
         <v>150</v>
@@ -1499,27 +1499,27 @@
         <v>3055.23</v>
       </c>
       <c r="D66" s="26">
-        <v>3248.97084620633</v>
+        <v>3285.5122007330101</v>
       </c>
       <c r="E66" s="3">
         <f>D66/C66-1</f>
-        <v>6.3412851473155785E-2</v>
+        <v>7.5373114539006858E-2</v>
       </c>
       <c r="F66" s="4">
-        <f>8.61/1000</f>
-        <v>8.6099999999999996E-3</v>
+        <f>8.64/1000</f>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="G66" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f t="shared" ref="H66:H69" si="0">F66 * G66</f>
-        <v>17.22</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B67" s="2">
         <v>200</v>
@@ -1528,27 +1528,27 @@
         <v>1395.85</v>
       </c>
       <c r="D67" s="25">
-        <v>1350.25450876236</v>
+        <v>1348.1244809024799</v>
       </c>
       <c r="E67" s="3">
         <f>D67/C67-1</f>
-        <v>-3.2665036528022218E-2</v>
+        <v>-3.4191008416033175E-2</v>
       </c>
       <c r="F67" s="4">
-        <f>11.26/1000</f>
-        <v>1.1259999999999999E-2</v>
+        <f>10.63/1000</f>
+        <v>1.0630000000000001E-2</v>
       </c>
       <c r="G67" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" si="0"/>
-        <v>22.52</v>
+        <v>53.150000000000006</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B68" s="1">
         <v>250</v>
@@ -1557,27 +1557,27 @@
         <v>38684</v>
       </c>
       <c r="D68" s="25">
-        <v>41926.235613395198</v>
+        <v>41961.925811757901</v>
       </c>
       <c r="E68" s="3">
         <f>D68/C68-1</f>
-        <v>8.3813349534567205E-2</v>
+        <v>8.473595832276648E-2</v>
       </c>
       <c r="F68" s="4">
-        <f>17.68/1000</f>
-        <v>1.7680000000000001E-2</v>
+        <f>15.83/1000</f>
+        <v>1.583E-2</v>
       </c>
       <c r="G68" s="1">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="0"/>
-        <v>53.040000000000006</v>
+        <v>79.150000000000006</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B69" s="7">
         <v>302</v>
@@ -1586,22 +1586,22 @@
         <v>21736</v>
       </c>
       <c r="D69" s="26">
-        <v>22966.074241357201</v>
+        <v>23011.023699336001</v>
       </c>
       <c r="E69" s="3">
         <f>D69/C69-1</f>
-        <v>5.6591564287688634E-2</v>
+        <v>5.8659537142804696E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>24.64/1000</f>
-        <v>2.4640000000000002E-2</v>
+        <f>22.25/1000</f>
+        <v>2.2249999999999999E-2</v>
       </c>
       <c r="G69" s="1">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H69" s="1">
         <f t="shared" si="0"/>
-        <v>98.56</v>
+        <v>111.25</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -2221,12 +2221,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X280"/>
+  <dimension ref="A1:X282"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
@@ -2242,7 +2243,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -2357,11 +2358,11 @@
     </row>
     <row r="15" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -2370,7 +2371,7 @@
         <v>40</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2397,7 +2398,7 @@
     </row>
     <row r="19" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B19" s="11"/>
       <c r="L19" s="12"/>
@@ -2406,7 +2407,7 @@
     </row>
     <row r="20" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B20" s="11"/>
       <c r="L20" s="12"/>
@@ -2415,7 +2416,7 @@
     </row>
     <row r="21" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -2432,7 +2433,7 @@
     </row>
     <row r="22" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -2449,7 +2450,7 @@
     </row>
     <row r="23" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -2466,7 +2467,7 @@
     </row>
     <row r="24" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -2483,7 +2484,7 @@
     </row>
     <row r="25" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -2517,7 +2518,7 @@
     </row>
     <row r="27" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -2534,7 +2535,7 @@
     </row>
     <row r="28" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -2551,7 +2552,7 @@
     </row>
     <row r="29" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -2568,7 +2569,7 @@
     </row>
     <row r="30" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -2585,7 +2586,7 @@
     </row>
     <row r="31" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -2602,7 +2603,7 @@
     </row>
     <row r="32" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -2619,7 +2620,7 @@
     </row>
     <row r="33" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -2636,7 +2637,7 @@
     </row>
     <row r="34" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -2653,7 +2654,7 @@
     </row>
     <row r="35" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -2704,7 +2705,7 @@
     </row>
     <row r="38" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -2721,7 +2722,7 @@
     </row>
     <row r="39" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -2738,7 +2739,7 @@
     </row>
     <row r="40" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -2755,7 +2756,7 @@
     </row>
     <row r="41" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -2770,9 +2771,9 @@
       <c r="W41" s="12"/>
       <c r="X41" s="12"/>
     </row>
-    <row r="42" spans="1:24" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -2787,9 +2788,9 @@
       <c r="W42" s="12"/>
       <c r="X42" s="12"/>
     </row>
-    <row r="43" spans="1:24" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="12" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -2806,7 +2807,7 @@
     </row>
     <row r="44" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -2823,7 +2824,7 @@
     </row>
     <row r="45" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
@@ -2840,7 +2841,7 @@
     </row>
     <row r="46" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -2857,7 +2858,7 @@
     </row>
     <row r="47" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -2874,7 +2875,7 @@
     </row>
     <row r="48" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -2891,7 +2892,7 @@
     </row>
     <row r="49" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -2908,7 +2909,7 @@
     </row>
     <row r="50" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
@@ -2925,7 +2926,7 @@
     </row>
     <row r="51" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
@@ -2942,7 +2943,7 @@
     </row>
     <row r="52" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -2959,7 +2960,7 @@
     </row>
     <row r="53" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -2976,7 +2977,7 @@
     </row>
     <row r="54" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
@@ -2993,7 +2994,7 @@
     </row>
     <row r="55" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
@@ -3010,7 +3011,7 @@
     </row>
     <row r="56" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
@@ -3027,7 +3028,7 @@
     </row>
     <row r="57" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
@@ -3044,7 +3045,7 @@
     </row>
     <row r="58" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
@@ -3061,7 +3062,7 @@
     </row>
     <row r="59" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -3078,7 +3079,7 @@
     </row>
     <row r="60" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -3087,12 +3088,15 @@
       <c r="F60" s="12"/>
       <c r="G60" s="12"/>
       <c r="H60" s="12"/>
+      <c r="L60" s="12"/>
       <c r="U60" s="12"/>
       <c r="V60" s="12"/>
+      <c r="W60" s="12"/>
+      <c r="X60" s="12"/>
     </row>
     <row r="61" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -3101,220 +3105,245 @@
       <c r="F61" s="12"/>
       <c r="G61" s="12"/>
       <c r="H61" s="12"/>
+      <c r="L61" s="12"/>
       <c r="U61" s="12"/>
       <c r="V61" s="12"/>
-    </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A63" s="17" t="s">
+      <c r="W61" s="12"/>
+      <c r="X61" s="12"/>
+    </row>
+    <row r="62" spans="1:24" ht="14" x14ac:dyDescent="0.3">
+      <c r="A62" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="U62" s="12"/>
+      <c r="V62" s="12"/>
+    </row>
+    <row r="63" spans="1:24" ht="14" x14ac:dyDescent="0.3">
+      <c r="A63" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="U63" s="12"/>
+      <c r="V63" s="12"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B63" s="7"/>
-    </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A64" s="18" t="s">
+      <c r="B65" s="7"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="B66" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="C66" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D64" s="18" t="s">
+      <c r="D66" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E64" s="18" t="s">
+      <c r="E66" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="F64" s="18" t="s">
+      <c r="F66" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G64" s="18" t="s">
+      <c r="G66" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="H64" s="18" t="s">
+      <c r="H66" s="18" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="2">
-        <v>100</v>
-      </c>
-      <c r="C65" s="6">
-        <v>1645.79</v>
-      </c>
-      <c r="D65" s="6">
-        <v>1645.83732633817</v>
-      </c>
-      <c r="E65" s="3">
-        <f>D65/C65-1</f>
-        <v>2.8756000565177686E-5</v>
-      </c>
-      <c r="F65" s="5">
-        <f>4.68/1000</f>
-        <v>4.6800000000000001E-3</v>
-      </c>
-      <c r="G65" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H65" s="6">
-        <f>F65 * G65</f>
-        <v>23.400000000000002</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B66" s="2">
-        <v>100</v>
-      </c>
-      <c r="C66" s="24">
-        <v>1252.3699999999999</v>
-      </c>
-      <c r="D66" s="24">
-        <v>1184.5618570060401</v>
-      </c>
-      <c r="E66" s="3">
-        <f t="shared" ref="E66:E70" si="0">D66/C66-1</f>
-        <v>-5.4143857641080317E-2</v>
-      </c>
-      <c r="F66" s="4">
-        <f>11.57/1000</f>
-        <v>1.157E-2</v>
-      </c>
-      <c r="G66" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H66" s="6">
-        <f t="shared" ref="H66:H70" si="1">F66 * G66</f>
-        <v>57.85</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B67" s="2">
         <v>100</v>
       </c>
       <c r="C67" s="6">
-        <v>828.94</v>
+        <v>1645.79</v>
       </c>
       <c r="D67" s="6">
-        <v>828.93686694150995</v>
+        <v>1649.8569104814301</v>
       </c>
       <c r="E67" s="3">
-        <f t="shared" si="0"/>
-        <v>-3.7795962194442367E-6</v>
-      </c>
-      <c r="F67" s="4">
-        <f>5.94/1000</f>
-        <v>5.94E-3</v>
+        <f>D67/C67-1</f>
+        <v>2.4710992784195973E-3</v>
+      </c>
+      <c r="F67" s="5">
+        <f>4.52/1000</f>
+        <v>4.5199999999999997E-3</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
-        <f t="shared" si="1"/>
-        <v>29.7</v>
+        <f>F67 * G67</f>
+        <v>22.599999999999998</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>47</v>
+      <c r="A68" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="B68" s="2">
         <v>100</v>
       </c>
-      <c r="C68" s="6">
-        <v>591.55999999999995</v>
-      </c>
-      <c r="D68" s="6">
-        <v>591.55655666593805</v>
+      <c r="C68" s="24">
+        <v>1252.3699999999999</v>
+      </c>
+      <c r="D68" s="24">
+        <v>1220.42533986741</v>
       </c>
       <c r="E68" s="3">
-        <f t="shared" si="0"/>
-        <v>-5.820768919306829E-6</v>
+        <f t="shared" ref="E68:E72" si="0">D68/C68-1</f>
+        <v>-2.5507366139870702E-2</v>
       </c>
       <c r="F68" s="4">
-        <f>21.03/1000</f>
-        <v>2.103E-2</v>
+        <f>10.78/1000</f>
+        <v>1.078E-2</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
-        <f t="shared" si="1"/>
-        <v>105.15</v>
+        <f t="shared" ref="H68:H72" si="1">F68 * G68</f>
+        <v>53.9</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B69" s="2">
         <v>100</v>
       </c>
       <c r="C69" s="6">
-        <v>1696.94</v>
+        <v>828.94</v>
       </c>
       <c r="D69" s="6">
-        <v>1675.1266262731599</v>
+        <v>828.93686694144105</v>
       </c>
       <c r="E69" s="3">
         <f t="shared" si="0"/>
-        <v>-1.2854534471955503E-2</v>
+        <v>-3.779596302488919E-6</v>
       </c>
       <c r="F69" s="4">
-        <f>4.92/1000</f>
-        <v>4.9199999999999999E-3</v>
+        <f>5.75/1000</f>
+        <v>5.7499999999999999E-3</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>24.599999999999998</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
-        <v>49</v>
+      <c r="A70" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="B70" s="2">
         <v>100</v>
       </c>
-      <c r="C70" s="24">
-        <v>1406.91</v>
-      </c>
-      <c r="D70" s="24">
-        <v>1310.3079013464001</v>
+      <c r="C70" s="6">
+        <v>591.55999999999995</v>
+      </c>
+      <c r="D70" s="6">
+        <v>591.55655666571897</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-6.8662600062264101E-2</v>
+        <v>-5.8207692896772301E-6</v>
       </c>
       <c r="F70" s="4">
-        <f>9.42/1000</f>
-        <v>9.4199999999999996E-3</v>
+        <f>19.81/1000</f>
+        <v>1.9809999999999998E-2</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>47.099999999999994</v>
+        <v>99.049999999999983</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B71" s="7"/>
+      <c r="A71" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B71" s="2">
+        <v>100</v>
+      </c>
+      <c r="C71" s="6">
+        <v>1696.94</v>
+      </c>
+      <c r="D71" s="6">
+        <v>1664.8291484931301</v>
+      </c>
+      <c r="E71" s="3">
+        <f t="shared" si="0"/>
+        <v>-1.8922797215499609E-2</v>
+      </c>
+      <c r="F71" s="4">
+        <f>4.78/1000</f>
+        <v>4.7800000000000004E-3</v>
+      </c>
+      <c r="G71" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H71" s="6">
+        <f t="shared" si="1"/>
+        <v>23.900000000000002</v>
+      </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B72" s="7"/>
+      <c r="A72" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B72" s="2">
+        <v>100</v>
+      </c>
+      <c r="C72" s="24">
+        <v>1406.91</v>
+      </c>
+      <c r="D72" s="24">
+        <v>1299.28562051327</v>
+      </c>
+      <c r="E72" s="3">
+        <f t="shared" si="0"/>
+        <v>-7.6496989492384038E-2</v>
+      </c>
+      <c r="F72" s="4">
+        <f>9.33/1000</f>
+        <v>9.3299999999999998E-3</v>
+      </c>
+      <c r="G72" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H72" s="6">
+        <f t="shared" si="1"/>
+        <v>46.65</v>
+      </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B73" s="7"/>
@@ -3939,6 +3968,12 @@
     </row>
     <row r="280" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B280" s="7"/>
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B281" s="7"/>
+    </row>
+    <row r="282" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B282" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC696659-528D-4C69-98D7-B64DB642E9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2C3543-A3C2-447F-AA51-31DFD276D1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2C3543-A3C2-447F-AA51-31DFD276D1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB94505-E4A1-4643-9A20-E64ED73834C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="89">
   <si>
     <t>Best known</t>
   </si>
@@ -77,9 +77,6 @@
     <t>        τ   =   0.5                     ,</t>
   </si>
   <si>
-    <t>        𝜃   =   0.99975                 ,</t>
-  </si>
-  <si>
     <t>        C̅   =   60                      ,</t>
   </si>
   <si>
@@ -164,9 +161,6 @@
     <t>rng</t>
   </si>
   <si>
-    <t>MersenneTwister(1234)</t>
-  </si>
-  <si>
     <t>r101</t>
   </si>
   <si>
@@ -303,6 +297,12 @@
   </si>
   <si>
     <t>                    :greedyperturb! ,</t>
+  </si>
+  <si>
+    <t>MersenneTwister(1104); MersenneTwister(1234); MersenneTwister(1403)</t>
+  </si>
+  <si>
+    <t>        𝜃   =   0.9975                 ,</t>
   </si>
 </sst>
 </file>
@@ -816,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB48D86-1312-4781-AFB7-1DCAC26244E4}">
-  <dimension ref="A1:X274"/>
+  <dimension ref="A1:X276"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
@@ -832,7 +832,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -850,16 +850,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -867,11 +867,11 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -879,35 +879,35 @@
     </row>
     <row r="6" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="1"/>
     </row>
@@ -919,7 +919,7 @@
     </row>
     <row r="12" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -927,40 +927,40 @@
     </row>
     <row r="13" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -975,7 +975,7 @@
     </row>
     <row r="18" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="8"/>
       <c r="L18" s="12"/>
@@ -994,7 +994,7 @@
     </row>
     <row r="19" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B19" s="12"/>
       <c r="W19" s="12"/>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="20" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B20" s="12"/>
       <c r="W20" s="12"/>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="21" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B21" s="12"/>
       <c r="U21" s="12"/>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="22" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B22" s="12"/>
       <c r="U22" s="12"/>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="23" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B23" s="12"/>
       <c r="H23" s="12"/>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="24" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B24" s="12"/>
       <c r="H24" s="12"/>
@@ -1052,7 +1052,7 @@
     </row>
     <row r="25" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B25" s="12"/>
       <c r="H25" s="12"/>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="27" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B27" s="12"/>
       <c r="U27" s="12"/>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="28" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B28" s="12"/>
       <c r="U28" s="12"/>
@@ -1094,7 +1094,7 @@
     </row>
     <row r="29" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B29" s="12"/>
       <c r="U29" s="12"/>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="30" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B30" s="12"/>
       <c r="U30" s="12"/>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="31" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B31" s="12"/>
       <c r="U31" s="12"/>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="32" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B32" s="12"/>
       <c r="U32" s="12"/>
@@ -1134,7 +1134,7 @@
     </row>
     <row r="33" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B33" s="12"/>
       <c r="U33" s="12"/>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="34" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B34" s="12"/>
       <c r="U34" s="12"/>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="35" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B35" s="12"/>
       <c r="U35" s="12"/>
@@ -1184,9 +1184,16 @@
     </row>
     <row r="38" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="L38" s="12"/>
       <c r="U38" s="12"/>
       <c r="V38" s="12"/>
       <c r="W38" s="12"/>
@@ -1194,9 +1201,16 @@
     </row>
     <row r="39" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="L39" s="12"/>
       <c r="U39" s="12"/>
       <c r="V39" s="12"/>
       <c r="W39" s="12"/>
@@ -1204,9 +1218,16 @@
     </row>
     <row r="40" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="L40" s="12"/>
       <c r="U40" s="12"/>
       <c r="V40" s="12"/>
       <c r="W40" s="12"/>
@@ -1214,31 +1235,50 @@
     </row>
     <row r="41" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="L41" s="12"/>
       <c r="U41" s="12"/>
       <c r="V41" s="12"/>
       <c r="W41" s="12"/>
       <c r="X41" s="12"/>
     </row>
-    <row r="42" spans="1:24" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="B42" s="12"/>
-      <c r="H42" s="9"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="L42" s="12"/>
       <c r="U42" s="12"/>
       <c r="V42" s="12"/>
       <c r="W42" s="12"/>
       <c r="X42" s="12"/>
     </row>
-    <row r="43" spans="1:24" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="12" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="B43" s="12"/>
-      <c r="H43" s="9"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="L43" s="12"/>
       <c r="U43" s="12"/>
       <c r="V43" s="12"/>
       <c r="W43" s="12"/>
@@ -1246,7 +1286,7 @@
     </row>
     <row r="44" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B44" s="12"/>
       <c r="H44" s="9"/>
@@ -1257,7 +1297,7 @@
     </row>
     <row r="45" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="B45" s="12"/>
       <c r="H45" s="9"/>
@@ -1268,7 +1308,7 @@
     </row>
     <row r="46" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="B46" s="12"/>
       <c r="H46" s="9"/>
@@ -1279,7 +1319,7 @@
     </row>
     <row r="47" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B47" s="12"/>
       <c r="H47" s="9"/>
@@ -1290,7 +1330,7 @@
     </row>
     <row r="48" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="B48" s="12"/>
       <c r="H48" s="9"/>
@@ -1301,7 +1341,7 @@
     </row>
     <row r="49" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B49" s="12"/>
       <c r="H49" s="9"/>
@@ -1312,7 +1352,7 @@
     </row>
     <row r="50" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="B50" s="12"/>
       <c r="H50" s="9"/>
@@ -1323,7 +1363,7 @@
     </row>
     <row r="51" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="B51" s="12"/>
       <c r="H51" s="9"/>
@@ -1334,7 +1374,7 @@
     </row>
     <row r="52" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B52" s="12"/>
       <c r="H52" s="9"/>
@@ -1345,9 +1385,10 @@
     </row>
     <row r="53" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="B53" s="12"/>
+      <c r="H53" s="9"/>
       <c r="U53" s="12"/>
       <c r="V53" s="12"/>
       <c r="W53" s="12"/>
@@ -1355,9 +1396,10 @@
     </row>
     <row r="54" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="B54" s="12"/>
+      <c r="H54" s="9"/>
       <c r="U54" s="12"/>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
@@ -1365,7 +1407,7 @@
     </row>
     <row r="55" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B55" s="12"/>
       <c r="U55" s="12"/>
@@ -1375,7 +1417,7 @@
     </row>
     <row r="56" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="B56" s="12"/>
       <c r="U56" s="12"/>
@@ -1385,7 +1427,7 @@
     </row>
     <row r="57" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="B57" s="12"/>
       <c r="U57" s="12"/>
@@ -1395,7 +1437,7 @@
     </row>
     <row r="58" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="B58" s="12"/>
       <c r="U58" s="12"/>
@@ -1405,7 +1447,7 @@
     </row>
     <row r="59" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B59" s="12"/>
       <c r="U59" s="12"/>
@@ -1415,201 +1457,215 @@
     </row>
     <row r="60" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
-        <v>68</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B60" s="12"/>
       <c r="U60" s="12"/>
       <c r="V60" s="12"/>
+      <c r="W60" s="12"/>
+      <c r="X60" s="12"/>
     </row>
     <row r="61" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
-        <v>49</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B61" s="12"/>
       <c r="U61" s="12"/>
       <c r="V61" s="12"/>
-    </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A63" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B63" s="7"/>
-    </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A64" s="18" t="s">
+      <c r="W61" s="12"/>
+      <c r="X61" s="12"/>
+    </row>
+    <row r="62" spans="1:24" ht="14" x14ac:dyDescent="0.3">
+      <c r="A62" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="U62" s="12"/>
+      <c r="V62" s="12"/>
+    </row>
+    <row r="63" spans="1:24" ht="14" x14ac:dyDescent="0.3">
+      <c r="A63" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="U63" s="12"/>
+      <c r="V63" s="12"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B65" s="7"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="B66" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G66" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C64" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E64" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F64" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="G64" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="H64" s="18" t="s">
+      <c r="H66" s="18" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B65" s="2">
-        <v>100</v>
-      </c>
-      <c r="C65" s="25">
-        <v>820</v>
-      </c>
-      <c r="D65" s="25">
-        <v>819.55754418720403</v>
-      </c>
-      <c r="E65" s="3">
-        <f>D65/C65-1</f>
-        <v>-5.395802595072885E-4</v>
-      </c>
-      <c r="F65" s="5">
-        <f>3.06/1000</f>
-        <v>3.0600000000000002E-3</v>
-      </c>
-      <c r="G65" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H65" s="6">
-        <f>F65 * G65</f>
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B66" s="1">
-        <v>150</v>
-      </c>
-      <c r="C66" s="25">
-        <v>3055.23</v>
-      </c>
-      <c r="D66" s="26">
-        <v>3285.5122007330101</v>
-      </c>
-      <c r="E66" s="3">
-        <f>D66/C66-1</f>
-        <v>7.5373114539006858E-2</v>
-      </c>
-      <c r="F66" s="4">
-        <f>8.64/1000</f>
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="G66" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H66" s="6">
-        <f t="shared" ref="H66:H69" si="0">F66 * G66</f>
-        <v>43.2</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B67" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C67" s="25">
-        <v>1395.85</v>
+        <v>820</v>
       </c>
       <c r="D67" s="25">
-        <v>1348.1244809024799</v>
+        <v>819.55754418737604</v>
       </c>
       <c r="E67" s="3">
         <f>D67/C67-1</f>
-        <v>-3.4191008416033175E-2</v>
-      </c>
-      <c r="F67" s="4">
+        <v>-5.3958025929756737E-4</v>
+      </c>
+      <c r="F67" s="5">
+        <f>3.01/1000</f>
+        <v>3.0099999999999997E-3</v>
+      </c>
+      <c r="G67" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H67" s="6">
+        <f>F67 * G67</f>
+        <v>15.049999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="1">
+        <v>150</v>
+      </c>
+      <c r="C68" s="25">
+        <v>3055.23</v>
+      </c>
+      <c r="D68" s="26">
+        <v>3128.3186327508502</v>
+      </c>
+      <c r="E68" s="3">
+        <f>D68/C68-1</f>
+        <v>2.3922465002913063E-2</v>
+      </c>
+      <c r="F68" s="4">
+        <f>8.1/1000</f>
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="G68" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H68" s="6">
+        <f t="shared" ref="H68:H71" si="0">F68 * G68</f>
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="2">
+        <v>200</v>
+      </c>
+      <c r="C69" s="25">
+        <v>1395.85</v>
+      </c>
+      <c r="D69" s="25">
+        <v>1336.37747640726</v>
+      </c>
+      <c r="E69" s="3">
+        <f>D69/C69-1</f>
+        <v>-4.2606672344979724E-2</v>
+      </c>
+      <c r="F69" s="4">
         <f>10.63/1000</f>
         <v>1.0630000000000001E-2</v>
       </c>
-      <c r="G67" s="1">
+      <c r="G69" s="1">
         <v>5000</v>
       </c>
-      <c r="H67" s="6">
+      <c r="H69" s="6">
         <f t="shared" si="0"/>
         <v>53.150000000000006</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B68" s="1">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="1">
         <v>250</v>
       </c>
-      <c r="C68" s="25">
+      <c r="C70" s="25">
         <v>38684</v>
       </c>
-      <c r="D68" s="25">
-        <v>41961.925811757901</v>
-      </c>
-      <c r="E68" s="3">
-        <f>D68/C68-1</f>
-        <v>8.473595832276648E-2</v>
-      </c>
-      <c r="F68" s="4">
-        <f>15.83/1000</f>
-        <v>1.583E-2</v>
-      </c>
-      <c r="G68" s="1">
+      <c r="D70" s="25">
+        <v>40485.081394866203</v>
+      </c>
+      <c r="E70" s="3">
+        <f>D70/C70-1</f>
+        <v>4.6558820051344263E-2</v>
+      </c>
+      <c r="F70" s="4">
+        <f>15.56/1000</f>
+        <v>1.5560000000000001E-2</v>
+      </c>
+      <c r="G70" s="1">
         <v>5000</v>
       </c>
-      <c r="H68" s="6">
+      <c r="H70" s="6">
         <f t="shared" si="0"/>
-        <v>79.150000000000006</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B69" s="7">
+        <v>77.800000000000011</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="7">
         <v>302</v>
       </c>
-      <c r="C69" s="27">
+      <c r="C71" s="27">
         <v>21736</v>
       </c>
-      <c r="D69" s="26">
-        <v>23011.023699336001</v>
-      </c>
-      <c r="E69" s="3">
-        <f>D69/C69-1</f>
-        <v>5.8659537142804696E-2</v>
-      </c>
-      <c r="F69" s="4">
+      <c r="D71" s="26">
+        <v>22748.082711906602</v>
+      </c>
+      <c r="E71" s="3">
+        <f>D71/C71-1</f>
+        <v>4.6562509749107583E-2</v>
+      </c>
+      <c r="F71" s="4">
         <f>22.25/1000</f>
         <v>2.2249999999999999E-2</v>
       </c>
-      <c r="G69" s="1">
+      <c r="G71" s="1">
         <v>5000</v>
       </c>
-      <c r="H69" s="1">
+      <c r="H71" s="1">
         <f t="shared" si="0"/>
         <v>111.25</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B70" s="7"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B71" s="7"/>
-    </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B72" s="7"/>
     </row>
@@ -2218,6 +2274,12 @@
     </row>
     <row r="274" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B274" s="7"/>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B275" s="7"/>
+    </row>
+    <row r="276" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B276" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2243,7 +2305,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -2261,16 +2323,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2278,11 +2340,11 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -2290,35 +2352,35 @@
     </row>
     <row r="6" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="1"/>
     </row>
@@ -2330,7 +2392,7 @@
     </row>
     <row r="12" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -2338,40 +2400,40 @@
     </row>
     <row r="13" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2379,7 +2441,7 @@
     </row>
     <row r="18" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="8"/>
       <c r="L18" s="12"/>
@@ -2398,7 +2460,7 @@
     </row>
     <row r="19" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B19" s="11"/>
       <c r="L19" s="12"/>
@@ -2407,7 +2469,7 @@
     </row>
     <row r="20" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B20" s="11"/>
       <c r="L20" s="12"/>
@@ -2416,7 +2478,7 @@
     </row>
     <row r="21" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -2433,7 +2495,7 @@
     </row>
     <row r="22" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -2450,7 +2512,7 @@
     </row>
     <row r="23" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -2467,7 +2529,7 @@
     </row>
     <row r="24" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -2484,7 +2546,7 @@
     </row>
     <row r="25" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -2518,7 +2580,7 @@
     </row>
     <row r="27" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -2535,7 +2597,7 @@
     </row>
     <row r="28" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -2552,7 +2614,7 @@
     </row>
     <row r="29" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -2569,7 +2631,7 @@
     </row>
     <row r="30" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -2586,7 +2648,7 @@
     </row>
     <row r="31" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -2603,7 +2665,7 @@
     </row>
     <row r="32" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -2620,7 +2682,7 @@
     </row>
     <row r="33" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -2637,7 +2699,7 @@
     </row>
     <row r="34" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -2654,7 +2716,7 @@
     </row>
     <row r="35" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -2705,7 +2767,7 @@
     </row>
     <row r="38" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -2722,7 +2784,7 @@
     </row>
     <row r="39" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -2739,7 +2801,7 @@
     </row>
     <row r="40" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -2756,7 +2818,7 @@
     </row>
     <row r="41" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -2773,7 +2835,7 @@
     </row>
     <row r="42" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -2790,7 +2852,7 @@
     </row>
     <row r="43" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -2824,7 +2886,7 @@
     </row>
     <row r="45" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
@@ -2841,7 +2903,7 @@
     </row>
     <row r="46" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -2858,7 +2920,7 @@
     </row>
     <row r="47" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -2875,7 +2937,7 @@
     </row>
     <row r="48" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -2892,7 +2954,7 @@
     </row>
     <row r="49" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -2943,7 +3005,7 @@
     </row>
     <row r="52" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -2960,7 +3022,7 @@
     </row>
     <row r="53" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -2977,7 +3039,7 @@
     </row>
     <row r="54" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
@@ -3028,7 +3090,7 @@
     </row>
     <row r="57" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
@@ -3045,7 +3107,7 @@
     </row>
     <row r="58" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
@@ -3062,7 +3124,7 @@
     </row>
     <row r="59" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -3079,7 +3141,7 @@
     </row>
     <row r="60" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -3096,7 +3158,7 @@
     </row>
     <row r="61" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -3113,7 +3175,7 @@
     </row>
     <row r="62" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
@@ -3127,7 +3189,7 @@
     </row>
     <row r="63" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
@@ -3141,7 +3203,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B65" s="7"/>
     </row>
@@ -3150,7 +3212,7 @@
         <v>2</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>0</v>
@@ -3165,7 +3227,7 @@
         <v>4</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H66" s="18" t="s">
         <v>5</v>
@@ -3173,7 +3235,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B67" s="2">
         <v>100</v>
@@ -3182,143 +3244,143 @@
         <v>1645.79</v>
       </c>
       <c r="D67" s="6">
-        <v>1649.8569104814301</v>
+        <v>1660.75617352522</v>
       </c>
       <c r="E67" s="3">
         <f>D67/C67-1</f>
-        <v>2.4710992784195973E-3</v>
+        <v>9.093610682541442E-3</v>
       </c>
       <c r="F67" s="5">
+        <f>4.27/1000</f>
+        <v>4.2699999999999995E-3</v>
+      </c>
+      <c r="G67" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H67" s="6">
+        <f>F67 * G67</f>
+        <v>21.349999999999998</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="2">
+        <v>100</v>
+      </c>
+      <c r="C68" s="24">
+        <v>1252.3699999999999</v>
+      </c>
+      <c r="D68" s="24">
+        <v>1176.7066208282699</v>
+      </c>
+      <c r="E68" s="3">
+        <f t="shared" ref="E68:E72" si="0">D68/C68-1</f>
+        <v>-6.0416154308814418E-2</v>
+      </c>
+      <c r="F68" s="4">
+        <f>10.79/1000</f>
+        <v>1.0789999999999999E-2</v>
+      </c>
+      <c r="G68" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H68" s="6">
+        <f t="shared" ref="H68:H72" si="1">F68 * G68</f>
+        <v>53.949999999999996</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="2">
+        <v>100</v>
+      </c>
+      <c r="C69" s="6">
+        <v>828.94</v>
+      </c>
+      <c r="D69" s="6">
+        <v>828.93686694282201</v>
+      </c>
+      <c r="E69" s="3">
+        <f t="shared" si="0"/>
+        <v>-3.7795946365992705E-6</v>
+      </c>
+      <c r="F69" s="4">
+        <f>5.16/1000</f>
+        <v>5.1600000000000005E-3</v>
+      </c>
+      <c r="G69" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H69" s="6">
+        <f t="shared" si="1"/>
+        <v>25.800000000000004</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" s="2">
+        <v>100</v>
+      </c>
+      <c r="C70" s="6">
+        <v>591.55999999999995</v>
+      </c>
+      <c r="D70" s="6">
+        <v>591.55655667122903</v>
+      </c>
+      <c r="E70" s="3">
+        <f t="shared" si="0"/>
+        <v>-5.8207599751280981E-6</v>
+      </c>
+      <c r="F70" s="4">
+        <f>18.95/1000</f>
+        <v>1.8949999999999998E-2</v>
+      </c>
+      <c r="G70" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H70" s="6">
+        <f t="shared" si="1"/>
+        <v>94.749999999999986</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B71" s="2">
+        <v>100</v>
+      </c>
+      <c r="C71" s="6">
+        <v>1696.94</v>
+      </c>
+      <c r="D71" s="6">
+        <v>1650.1981722923999</v>
+      </c>
+      <c r="E71" s="3">
+        <f t="shared" si="0"/>
+        <v>-2.7544773361226738E-2</v>
+      </c>
+      <c r="F71" s="4">
         <f>4.52/1000</f>
         <v>4.5199999999999997E-3</v>
       </c>
-      <c r="G67" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H67" s="6">
-        <f>F67 * G67</f>
-        <v>22.599999999999998</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B68" s="2">
-        <v>100</v>
-      </c>
-      <c r="C68" s="24">
-        <v>1252.3699999999999</v>
-      </c>
-      <c r="D68" s="24">
-        <v>1220.42533986741</v>
-      </c>
-      <c r="E68" s="3">
-        <f t="shared" ref="E68:E72" si="0">D68/C68-1</f>
-        <v>-2.5507366139870702E-2</v>
-      </c>
-      <c r="F68" s="4">
-        <f>10.78/1000</f>
-        <v>1.078E-2</v>
-      </c>
-      <c r="G68" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H68" s="6">
-        <f t="shared" ref="H68:H72" si="1">F68 * G68</f>
-        <v>53.9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" s="2">
-        <v>100</v>
-      </c>
-      <c r="C69" s="6">
-        <v>828.94</v>
-      </c>
-      <c r="D69" s="6">
-        <v>828.93686694144105</v>
-      </c>
-      <c r="E69" s="3">
-        <f t="shared" si="0"/>
-        <v>-3.779596302488919E-6</v>
-      </c>
-      <c r="F69" s="4">
-        <f>5.75/1000</f>
-        <v>5.7499999999999999E-3</v>
-      </c>
-      <c r="G69" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H69" s="6">
-        <f t="shared" si="1"/>
-        <v>28.75</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B70" s="2">
-        <v>100</v>
-      </c>
-      <c r="C70" s="6">
-        <v>591.55999999999995</v>
-      </c>
-      <c r="D70" s="6">
-        <v>591.55655666571897</v>
-      </c>
-      <c r="E70" s="3">
-        <f t="shared" si="0"/>
-        <v>-5.8207692896772301E-6</v>
-      </c>
-      <c r="F70" s="4">
-        <f>19.81/1000</f>
-        <v>1.9809999999999998E-2</v>
-      </c>
-      <c r="G70" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H70" s="6">
-        <f t="shared" si="1"/>
-        <v>99.049999999999983</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B71" s="2">
-        <v>100</v>
-      </c>
-      <c r="C71" s="6">
-        <v>1696.94</v>
-      </c>
-      <c r="D71" s="6">
-        <v>1664.8291484931301</v>
-      </c>
-      <c r="E71" s="3">
-        <f t="shared" si="0"/>
-        <v>-1.8922797215499609E-2</v>
-      </c>
-      <c r="F71" s="4">
-        <f>4.78/1000</f>
-        <v>4.7800000000000004E-3</v>
-      </c>
       <c r="G71" s="1">
         <v>5000</v>
       </c>
       <c r="H71" s="6">
         <f t="shared" si="1"/>
-        <v>23.900000000000002</v>
+        <v>22.599999999999998</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B72" s="2">
         <v>100</v>
@@ -3327,22 +3389,22 @@
         <v>1406.91</v>
       </c>
       <c r="D72" s="24">
-        <v>1299.28562051327</v>
+        <v>1287.63594055659</v>
       </c>
       <c r="E72" s="3">
         <f t="shared" si="0"/>
-        <v>-7.6496989492384038E-2</v>
+        <v>-8.4777320115295263E-2</v>
       </c>
       <c r="F72" s="4">
-        <f>9.33/1000</f>
-        <v>9.3299999999999998E-3</v>
+        <f>9.57/1000</f>
+        <v>9.5700000000000004E-3</v>
       </c>
       <c r="G72" s="1">
         <v>5000</v>
       </c>
       <c r="H72" s="6">
         <f t="shared" si="1"/>
-        <v>46.65</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB94505-E4A1-4643-9A20-E64ED73834C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD19221-6703-46B8-8CDC-7619359E026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3251,15 +3251,15 @@
         <v>9.093610682541442E-3</v>
       </c>
       <c r="F67" s="5">
-        <f>4.27/1000</f>
-        <v>4.2699999999999995E-3</v>
+        <f>4.56/1000</f>
+        <v>4.5599999999999998E-3</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f>F67 * G67</f>
-        <v>21.349999999999998</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -3280,15 +3280,15 @@
         <v>-6.0416154308814418E-2</v>
       </c>
       <c r="F68" s="4">
-        <f>10.79/1000</f>
-        <v>1.0789999999999999E-2</v>
+        <f>11.92/1000</f>
+        <v>1.192E-2</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" ref="H68:H72" si="1">F68 * G68</f>
-        <v>53.949999999999996</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -3309,15 +3309,15 @@
         <v>-3.7795946365992705E-6</v>
       </c>
       <c r="F69" s="4">
-        <f>5.16/1000</f>
-        <v>5.1600000000000005E-3</v>
+        <f>5.58/1000</f>
+        <v>5.5799999999999999E-3</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>25.800000000000004</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -3338,15 +3338,15 @@
         <v>-5.8207599751280981E-6</v>
       </c>
       <c r="F70" s="4">
-        <f>18.95/1000</f>
-        <v>1.8949999999999998E-2</v>
+        <f>19.71/1000</f>
+        <v>1.9710000000000002E-2</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>94.749999999999986</v>
+        <v>98.550000000000011</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -3367,15 +3367,15 @@
         <v>-2.7544773361226738E-2</v>
       </c>
       <c r="F71" s="4">
-        <f>4.52/1000</f>
-        <v>4.5199999999999997E-3</v>
+        <f>4.82/1000</f>
+        <v>4.8200000000000005E-3</v>
       </c>
       <c r="G71" s="1">
         <v>5000</v>
       </c>
       <c r="H71" s="6">
         <f t="shared" si="1"/>
-        <v>22.599999999999998</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
@@ -3396,15 +3396,15 @@
         <v>-8.4777320115295263E-2</v>
       </c>
       <c r="F72" s="4">
-        <f>9.57/1000</f>
-        <v>9.5700000000000004E-3</v>
+        <f>11.12/1000</f>
+        <v>1.112E-2</v>
       </c>
       <c r="G72" s="1">
         <v>5000</v>
       </c>
       <c r="H72" s="6">
         <f t="shared" si="1"/>
-        <v>47.85</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD19221-6703-46B8-8CDC-7619359E026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4A47E9-C24B-4386-8029-44752C64F437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3251,15 +3251,15 @@
         <v>9.093610682541442E-3</v>
       </c>
       <c r="F67" s="5">
-        <f>4.56/1000</f>
-        <v>4.5599999999999998E-3</v>
+        <f>4.86/1000</f>
+        <v>4.8600000000000006E-3</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f>F67 * G67</f>
-        <v>22.8</v>
+        <v>24.300000000000004</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -3280,15 +3280,15 @@
         <v>-6.0416154308814418E-2</v>
       </c>
       <c r="F68" s="4">
-        <f>11.92/1000</f>
-        <v>1.192E-2</v>
+        <f>12.45/1000</f>
+        <v>1.2449999999999999E-2</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" ref="H68:H72" si="1">F68 * G68</f>
-        <v>59.6</v>
+        <v>62.249999999999993</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -3309,15 +3309,15 @@
         <v>-3.7795946365992705E-6</v>
       </c>
       <c r="F69" s="4">
-        <f>5.58/1000</f>
-        <v>5.5799999999999999E-3</v>
+        <f>5.91/1000</f>
+        <v>5.9100000000000003E-3</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>27.9</v>
+        <v>29.55</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -3338,15 +3338,15 @@
         <v>-5.8207599751280981E-6</v>
       </c>
       <c r="F70" s="4">
-        <f>19.71/1000</f>
-        <v>1.9710000000000002E-2</v>
+        <f>20.32/1000</f>
+        <v>2.0320000000000001E-2</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>98.550000000000011</v>
+        <v>101.60000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -3367,15 +3367,15 @@
         <v>-2.7544773361226738E-2</v>
       </c>
       <c r="F71" s="4">
-        <f>4.82/1000</f>
-        <v>4.8200000000000005E-3</v>
+        <f>5.12/1000</f>
+        <v>5.1200000000000004E-3</v>
       </c>
       <c r="G71" s="1">
         <v>5000</v>
       </c>
       <c r="H71" s="6">
         <f t="shared" si="1"/>
-        <v>24.1</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
@@ -3396,15 +3396,15 @@
         <v>-8.4777320115295263E-2</v>
       </c>
       <c r="F72" s="4">
-        <f>11.12/1000</f>
-        <v>1.112E-2</v>
+        <f>11.17/1000</f>
+        <v>1.1169999999999999E-2</v>
       </c>
       <c r="G72" s="1">
         <v>5000</v>
       </c>
       <c r="H72" s="6">
         <f t="shared" si="1"/>
-        <v>55.6</v>
+        <v>55.849999999999994</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4A47E9-C24B-4386-8029-44752C64F437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE13049-74F5-4BEC-89FA-3D26049DE89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1539,15 +1539,15 @@
         <v>-5.3958025929756737E-4</v>
       </c>
       <c r="F67" s="5">
-        <f>3.01/1000</f>
-        <v>3.0099999999999997E-3</v>
+        <f>3.3/1000</f>
+        <v>3.3E-3</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f>F67 * G67</f>
-        <v>15.049999999999999</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -1561,22 +1561,22 @@
         <v>3055.23</v>
       </c>
       <c r="D68" s="26">
-        <v>3128.3186327508502</v>
+        <v>3104.0276306494802</v>
       </c>
       <c r="E68" s="3">
         <f>D68/C68-1</f>
-        <v>2.3922465002913063E-2</v>
+        <v>1.5971835393564504E-2</v>
       </c>
       <c r="F68" s="4">
-        <f>8.1/1000</f>
-        <v>8.0999999999999996E-3</v>
+        <f>8.42/1000</f>
+        <v>8.4200000000000004E-3</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" ref="H68:H71" si="0">F68 * G68</f>
-        <v>40.5</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -1590,22 +1590,22 @@
         <v>1395.85</v>
       </c>
       <c r="D69" s="25">
-        <v>1336.37747640726</v>
+        <v>1333.4039064419301</v>
       </c>
       <c r="E69" s="3">
         <f>D69/C69-1</f>
-        <v>-4.2606672344979724E-2</v>
+        <v>-4.4736965689773145E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>10.63/1000</f>
-        <v>1.0630000000000001E-2</v>
+        <f>11.23/1000</f>
+        <v>1.123E-2</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="0"/>
-        <v>53.150000000000006</v>
+        <v>56.15</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -1619,22 +1619,22 @@
         <v>38684</v>
       </c>
       <c r="D70" s="25">
-        <v>40485.081394866203</v>
+        <v>40964.220637907703</v>
       </c>
       <c r="E70" s="3">
         <f>D70/C70-1</f>
-        <v>4.6558820051344263E-2</v>
+        <v>5.8944799863191566E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>15.56/1000</f>
-        <v>1.5560000000000001E-2</v>
+        <f>15.91/1000</f>
+        <v>1.5910000000000001E-2</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="0"/>
-        <v>77.800000000000011</v>
+        <v>79.55</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -1648,22 +1648,22 @@
         <v>21736</v>
       </c>
       <c r="D71" s="26">
-        <v>22748.082711906602</v>
+        <v>22753.471385720899</v>
       </c>
       <c r="E71" s="3">
         <f>D71/C71-1</f>
-        <v>4.6562509749107583E-2</v>
+        <v>4.6810424444281296E-2</v>
       </c>
       <c r="F71" s="4">
-        <f>22.25/1000</f>
-        <v>2.2249999999999999E-2</v>
+        <f>20.91/1000</f>
+        <v>2.0910000000000002E-2</v>
       </c>
       <c r="G71" s="1">
         <v>5000</v>
       </c>
       <c r="H71" s="1">
         <f t="shared" si="0"/>
-        <v>111.25</v>
+        <v>104.55000000000001</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
@@ -3244,22 +3244,22 @@
         <v>1645.79</v>
       </c>
       <c r="D67" s="6">
-        <v>1660.75617352522</v>
+        <v>1649.0599551073999</v>
       </c>
       <c r="E67" s="3">
         <f>D67/C67-1</f>
-        <v>9.093610682541442E-3</v>
+        <v>1.9868604787973698E-3</v>
       </c>
       <c r="F67" s="5">
-        <f>4.86/1000</f>
-        <v>4.8600000000000006E-3</v>
+        <f>5.17/1000</f>
+        <v>5.1700000000000001E-3</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f>F67 * G67</f>
-        <v>24.300000000000004</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -3273,22 +3273,22 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="D68" s="24">
-        <v>1176.7066208282699</v>
+        <v>1168.62258735657</v>
       </c>
       <c r="E68" s="3">
         <f t="shared" ref="E68:E72" si="0">D68/C68-1</f>
-        <v>-6.0416154308814418E-2</v>
+        <v>-6.6871142428699182E-2</v>
       </c>
       <c r="F68" s="4">
-        <f>12.45/1000</f>
-        <v>1.2449999999999999E-2</v>
+        <f>12.48/1000</f>
+        <v>1.248E-2</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" ref="H68:H72" si="1">F68 * G68</f>
-        <v>62.249999999999993</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -3302,22 +3302,22 @@
         <v>828.94</v>
       </c>
       <c r="D69" s="6">
-        <v>828.93686694282201</v>
+        <v>828.936866942812</v>
       </c>
       <c r="E69" s="3">
         <f t="shared" si="0"/>
-        <v>-3.7795946365992705E-6</v>
+        <v>-3.7795946487007015E-6</v>
       </c>
       <c r="F69" s="4">
-        <f>5.91/1000</f>
-        <v>5.9100000000000003E-3</v>
+        <f>6.05/1000</f>
+        <v>6.0499999999999998E-3</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>29.55</v>
+        <v>30.25</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -3331,22 +3331,22 @@
         <v>591.55999999999995</v>
       </c>
       <c r="D70" s="6">
-        <v>591.55655667122903</v>
+        <v>591.55655667143196</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-5.8207599751280981E-6</v>
+        <v>-5.8207596321802058E-6</v>
       </c>
       <c r="F70" s="4">
-        <f>20.32/1000</f>
-        <v>2.0320000000000001E-2</v>
+        <f>21.02/1000</f>
+        <v>2.102E-2</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>101.60000000000001</v>
+        <v>105.10000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -3360,22 +3360,22 @@
         <v>1696.94</v>
       </c>
       <c r="D71" s="6">
-        <v>1650.1981722923999</v>
+        <v>1645.6655852073</v>
       </c>
       <c r="E71" s="3">
         <f t="shared" si="0"/>
-        <v>-2.7544773361226738E-2</v>
+        <v>-3.0215808922354426E-2</v>
       </c>
       <c r="F71" s="4">
-        <f>5.12/1000</f>
-        <v>5.1200000000000004E-3</v>
+        <f>5.31/1000</f>
+        <v>5.3099999999999996E-3</v>
       </c>
       <c r="G71" s="1">
         <v>5000</v>
       </c>
       <c r="H71" s="6">
         <f t="shared" si="1"/>
-        <v>25.6</v>
+        <v>26.549999999999997</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
@@ -3389,22 +3389,22 @@
         <v>1406.91</v>
       </c>
       <c r="D72" s="24">
-        <v>1287.63594055659</v>
+        <v>1287.7742416317201</v>
       </c>
       <c r="E72" s="3">
         <f t="shared" si="0"/>
-        <v>-8.4777320115295263E-2</v>
+        <v>-8.4679018820166152E-2</v>
       </c>
       <c r="F72" s="4">
-        <f>11.17/1000</f>
-        <v>1.1169999999999999E-2</v>
+        <f>12.38/1000</f>
+        <v>1.238E-2</v>
       </c>
       <c r="G72" s="1">
         <v>5000</v>
       </c>
       <c r="H72" s="6">
         <f t="shared" si="1"/>
-        <v>55.849999999999994</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE13049-74F5-4BEC-89FA-3D26049DE89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CCF451-8549-46EE-AC6C-075C71C1ACEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VRP Benchmarking" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="89">
   <si>
     <t>Best known</t>
   </si>
@@ -227,12 +227,6 @@
     <t>                    :regret3!</t>
   </si>
   <si>
-    <t>                    :intraopt!      ,</t>
-  </si>
-  <si>
-    <t>                    :interopt!      ,</t>
-  </si>
-  <si>
     <t>                    :split!         ,</t>
   </si>
   <si>
@@ -303,6 +297,12 @@
   </si>
   <si>
     <t>        𝜃   =   0.9975                 ,</t>
+  </si>
+  <si>
+    <t>                    :opt!           ,</t>
+  </si>
+  <si>
+    <t>                    :opt!           ,</t>
   </si>
 </sst>
 </file>
@@ -816,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB48D86-1312-4781-AFB7-1DCAC26244E4}">
-  <dimension ref="A1:X276"/>
+  <dimension ref="A1:X275"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
@@ -832,7 +832,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -951,16 +951,16 @@
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -994,7 +994,7 @@
     </row>
     <row r="19" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B19" s="12"/>
       <c r="W19" s="12"/>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="20" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B20" s="12"/>
       <c r="W20" s="12"/>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="21" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B21" s="12"/>
       <c r="U21" s="12"/>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="38" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="39" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="40" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -1235,7 +1235,7 @@
     </row>
     <row r="41" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="47" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="B47" s="12"/>
       <c r="H47" s="9"/>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="48" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B48" s="12"/>
       <c r="H48" s="9"/>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="49" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="B49" s="12"/>
       <c r="H49" s="9"/>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="50" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B50" s="12"/>
       <c r="H50" s="9"/>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="51" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="B51" s="12"/>
       <c r="H51" s="9"/>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="52" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B52" s="12"/>
       <c r="H52" s="9"/>
@@ -1385,7 +1385,7 @@
     </row>
     <row r="53" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B53" s="12"/>
       <c r="H53" s="9"/>
@@ -1396,10 +1396,9 @@
     </row>
     <row r="54" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="B54" s="12"/>
-      <c r="H54" s="9"/>
       <c r="U54" s="12"/>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
@@ -1407,7 +1406,7 @@
     </row>
     <row r="55" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B55" s="12"/>
       <c r="U55" s="12"/>
@@ -1417,7 +1416,7 @@
     </row>
     <row r="56" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="B56" s="12"/>
       <c r="U56" s="12"/>
@@ -1427,7 +1426,7 @@
     </row>
     <row r="57" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B57" s="12"/>
       <c r="U57" s="12"/>
@@ -1437,7 +1436,7 @@
     </row>
     <row r="58" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="B58" s="12"/>
       <c r="U58" s="12"/>
@@ -1447,7 +1446,7 @@
     </row>
     <row r="59" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B59" s="12"/>
       <c r="U59" s="12"/>
@@ -1457,7 +1456,7 @@
     </row>
     <row r="60" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B60" s="12"/>
       <c r="U60" s="12"/>
@@ -1467,204 +1466,197 @@
     </row>
     <row r="61" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" s="12"/>
+        <v>64</v>
+      </c>
       <c r="U61" s="12"/>
       <c r="V61" s="12"/>
-      <c r="W61" s="12"/>
-      <c r="X61" s="12"/>
     </row>
     <row r="62" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="U62" s="12"/>
       <c r="V62" s="12"/>
     </row>
-    <row r="63" spans="1:24" ht="14" x14ac:dyDescent="0.3">
-      <c r="A63" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="U63" s="12"/>
-      <c r="V63" s="12"/>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A64" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B64" s="7"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B65" s="7"/>
+      <c r="A65" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F65" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G65" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" s="18" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B66" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F66" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="G66" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H66" s="18" t="s">
-        <v>5</v>
+      <c r="A66" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" s="2">
+        <v>100</v>
+      </c>
+      <c r="C66" s="25">
+        <v>820</v>
+      </c>
+      <c r="D66" s="25">
+        <v>819.55754418732204</v>
+      </c>
+      <c r="E66" s="3">
+        <f>D66/C66-1</f>
+        <v>-5.3958025936340359E-4</v>
+      </c>
+      <c r="F66" s="5">
+        <f>3.02/1000</f>
+        <v>3.0200000000000001E-3</v>
+      </c>
+      <c r="G66" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H66" s="6">
+        <f>F66 * G66</f>
+        <v>15.100000000000001</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B67" s="2">
-        <v>100</v>
+      <c r="A67" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67" s="1">
+        <v>150</v>
       </c>
       <c r="C67" s="25">
-        <v>820</v>
-      </c>
-      <c r="D67" s="25">
-        <v>819.55754418737604</v>
+        <v>3055.23</v>
+      </c>
+      <c r="D67" s="26">
+        <v>3119.2520262377302</v>
       </c>
       <c r="E67" s="3">
         <f>D67/C67-1</f>
-        <v>-5.3958025929756737E-4</v>
-      </c>
-      <c r="F67" s="5">
-        <f>3.3/1000</f>
-        <v>3.3E-3</v>
+        <v>2.0954895781243987E-2</v>
+      </c>
+      <c r="F67" s="4">
+        <f>8.38/1000</f>
+        <v>8.3800000000000003E-3</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
-        <f>F67 * G67</f>
-        <v>16.5</v>
+        <f t="shared" ref="H67:H70" si="0">F67 * G67</f>
+        <v>41.9</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B68" s="1">
-        <v>150</v>
+      <c r="A68" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" s="2">
+        <v>200</v>
       </c>
       <c r="C68" s="25">
-        <v>3055.23</v>
-      </c>
-      <c r="D68" s="26">
-        <v>3104.0276306494802</v>
+        <v>1395.85</v>
+      </c>
+      <c r="D68" s="25">
+        <v>1333.4754040789301</v>
       </c>
       <c r="E68" s="3">
         <f>D68/C68-1</f>
-        <v>1.5971835393564504E-2</v>
+        <v>-4.4685744113672543E-2</v>
       </c>
       <c r="F68" s="4">
-        <f>8.42/1000</f>
-        <v>8.4200000000000004E-3</v>
+        <f>11.13/1000</f>
+        <v>1.1130000000000001E-2</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
-        <f t="shared" ref="H68:H71" si="0">F68 * G68</f>
-        <v>42.1</v>
+        <f t="shared" si="0"/>
+        <v>55.650000000000006</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B69" s="2">
-        <v>200</v>
+      <c r="A69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B69" s="1">
+        <v>250</v>
       </c>
       <c r="C69" s="25">
-        <v>1395.85</v>
+        <v>38684</v>
       </c>
       <c r="D69" s="25">
-        <v>1333.4039064419301</v>
+        <v>41023.472215590598</v>
       </c>
       <c r="E69" s="3">
         <f>D69/C69-1</f>
-        <v>-4.4736965689773145E-2</v>
+        <v>6.0476481635575396E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>11.23/1000</f>
-        <v>1.123E-2</v>
+        <f>16.54/1000</f>
+        <v>1.6539999999999999E-2</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="0"/>
-        <v>56.15</v>
+        <v>82.699999999999989</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B70" s="1">
-        <v>250</v>
-      </c>
-      <c r="C70" s="25">
-        <v>38684</v>
-      </c>
-      <c r="D70" s="25">
-        <v>40964.220637907703</v>
+        <v>73</v>
+      </c>
+      <c r="B70" s="7">
+        <v>302</v>
+      </c>
+      <c r="C70" s="27">
+        <v>21736</v>
+      </c>
+      <c r="D70" s="26">
+        <v>22858.740516695099</v>
       </c>
       <c r="E70" s="3">
         <f>D70/C70-1</f>
-        <v>5.8944799863191566E-2</v>
+        <v>5.1653501872244156E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>15.91/1000</f>
-        <v>1.5910000000000001E-2</v>
+        <f>21.31/1000</f>
+        <v>2.1309999999999999E-2</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
-      <c r="H70" s="6">
+      <c r="H70" s="1">
         <f t="shared" si="0"/>
-        <v>79.55</v>
+        <v>106.55</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B71" s="7">
-        <v>302</v>
-      </c>
-      <c r="C71" s="27">
-        <v>21736</v>
-      </c>
-      <c r="D71" s="26">
-        <v>22753.471385720899</v>
-      </c>
-      <c r="E71" s="3">
-        <f>D71/C71-1</f>
-        <v>4.6810424444281296E-2</v>
-      </c>
-      <c r="F71" s="4">
-        <f>20.91/1000</f>
-        <v>2.0910000000000002E-2</v>
-      </c>
-      <c r="G71" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H71" s="1">
-        <f t="shared" si="0"/>
-        <v>104.55000000000001</v>
-      </c>
+      <c r="B71" s="7"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B72" s="7"/>
@@ -2277,9 +2269,6 @@
     </row>
     <row r="275" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B275" s="7"/>
-    </row>
-    <row r="276" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B276" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2289,7 +2278,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X282"/>
+  <dimension ref="A1:X281"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
@@ -2305,7 +2294,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -2424,7 +2413,7 @@
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -2433,7 +2422,7 @@
         <v>39</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2460,7 +2449,7 @@
     </row>
     <row r="19" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B19" s="11"/>
       <c r="L19" s="12"/>
@@ -2469,7 +2458,7 @@
     </row>
     <row r="20" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B20" s="11"/>
       <c r="L20" s="12"/>
@@ -2478,7 +2467,7 @@
     </row>
     <row r="21" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -2767,7 +2756,7 @@
     </row>
     <row r="38" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -2784,7 +2773,7 @@
     </row>
     <row r="39" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -2801,7 +2790,7 @@
     </row>
     <row r="40" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -2818,7 +2807,7 @@
     </row>
     <row r="41" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -2920,7 +2909,7 @@
     </row>
     <row r="47" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -2937,7 +2926,7 @@
     </row>
     <row r="48" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -2954,7 +2943,7 @@
     </row>
     <row r="49" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -2971,7 +2960,7 @@
     </row>
     <row r="50" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
@@ -2988,7 +2977,7 @@
     </row>
     <row r="51" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
@@ -3005,7 +2994,7 @@
     </row>
     <row r="52" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -3022,7 +3011,7 @@
     </row>
     <row r="53" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -3039,7 +3028,7 @@
     </row>
     <row r="54" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
@@ -3056,7 +3045,7 @@
     </row>
     <row r="55" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
@@ -3073,7 +3062,7 @@
     </row>
     <row r="56" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
@@ -3090,7 +3079,7 @@
     </row>
     <row r="57" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
@@ -3107,7 +3096,7 @@
     </row>
     <row r="58" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
@@ -3124,7 +3113,7 @@
     </row>
     <row r="59" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -3141,7 +3130,7 @@
     </row>
     <row r="60" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -3158,7 +3147,7 @@
     </row>
     <row r="61" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -3167,15 +3156,12 @@
       <c r="F61" s="12"/>
       <c r="G61" s="12"/>
       <c r="H61" s="12"/>
-      <c r="L61" s="12"/>
       <c r="U61" s="12"/>
       <c r="V61" s="12"/>
-      <c r="W61" s="12"/>
-      <c r="X61" s="12"/>
     </row>
     <row r="62" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
@@ -3187,225 +3173,214 @@
       <c r="U62" s="12"/>
       <c r="V62" s="12"/>
     </row>
-    <row r="63" spans="1:24" ht="14" x14ac:dyDescent="0.3">
-      <c r="A63" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12"/>
-      <c r="U63" s="12"/>
-      <c r="V63" s="12"/>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A64" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B64" s="7"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B65" s="7"/>
+      <c r="A65" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F65" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G65" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" s="18" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B66" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F66" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="G66" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H66" s="18" t="s">
-        <v>5</v>
+      <c r="A66" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B66" s="2">
+        <v>100</v>
+      </c>
+      <c r="C66" s="6">
+        <v>1645.79</v>
+      </c>
+      <c r="D66" s="6">
+        <v>1644.7048641157</v>
+      </c>
+      <c r="E66" s="3">
+        <f>D66/C66-1</f>
+        <v>-6.5934042879101096E-4</v>
+      </c>
+      <c r="F66" s="5">
+        <f>5.14/1000</f>
+        <v>5.1399999999999996E-3</v>
+      </c>
+      <c r="G66" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H66" s="6">
+        <f>F66 * G66</f>
+        <v>25.7</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>41</v>
+      <c r="A67" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="B67" s="2">
         <v>100</v>
       </c>
-      <c r="C67" s="6">
-        <v>1645.79</v>
-      </c>
-      <c r="D67" s="6">
-        <v>1649.0599551073999</v>
+      <c r="C67" s="24">
+        <v>1252.3699999999999</v>
+      </c>
+      <c r="D67" s="24">
+        <v>1179.9333546359801</v>
       </c>
       <c r="E67" s="3">
-        <f>D67/C67-1</f>
-        <v>1.9868604787973698E-3</v>
-      </c>
-      <c r="F67" s="5">
-        <f>5.17/1000</f>
-        <v>5.1700000000000001E-3</v>
+        <f t="shared" ref="E67:E71" si="0">D67/C67-1</f>
+        <v>-5.7839652310435308E-2</v>
+      </c>
+      <c r="F67" s="4">
+        <f>13.49/1000</f>
+        <v>1.349E-2</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
-        <f>F67 * G67</f>
-        <v>25.85</v>
+        <f t="shared" ref="H67:H71" si="1">F67 * G67</f>
+        <v>67.45</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
-        <v>42</v>
+      <c r="A68" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B68" s="2">
         <v>100</v>
       </c>
-      <c r="C68" s="24">
-        <v>1252.3699999999999</v>
-      </c>
-      <c r="D68" s="24">
-        <v>1168.62258735657</v>
+      <c r="C68" s="6">
+        <v>828.94</v>
+      </c>
+      <c r="D68" s="6">
+        <v>828.936866942812</v>
       </c>
       <c r="E68" s="3">
-        <f t="shared" ref="E68:E72" si="0">D68/C68-1</f>
-        <v>-6.6871142428699182E-2</v>
+        <f t="shared" si="0"/>
+        <v>-3.7795946487007015E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>12.48/1000</f>
-        <v>1.248E-2</v>
+        <f>5.85/1000</f>
+        <v>5.8499999999999993E-3</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
-        <f t="shared" ref="H68:H72" si="1">F68 * G68</f>
-        <v>62.4</v>
+        <f t="shared" si="1"/>
+        <v>29.249999999999996</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B69" s="2">
         <v>100</v>
       </c>
       <c r="C69" s="6">
-        <v>828.94</v>
+        <v>591.55999999999995</v>
       </c>
       <c r="D69" s="6">
-        <v>828.936866942812</v>
+        <v>591.55655667143196</v>
       </c>
       <c r="E69" s="3">
         <f t="shared" si="0"/>
-        <v>-3.7795946487007015E-6</v>
+        <v>-5.8207596321802058E-6</v>
       </c>
       <c r="F69" s="4">
-        <f>6.05/1000</f>
-        <v>6.0499999999999998E-3</v>
+        <f>21.05/1000</f>
+        <v>2.1049999999999999E-2</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>30.25</v>
+        <v>105.25</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B70" s="2">
         <v>100</v>
       </c>
       <c r="C70" s="6">
-        <v>591.55999999999995</v>
+        <v>1696.94</v>
       </c>
       <c r="D70" s="6">
-        <v>591.55655667143196</v>
+        <v>1645.5434971790201</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-5.8207596321802058E-6</v>
+        <v>-3.028775491235991E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>21.02/1000</f>
-        <v>2.102E-2</v>
+        <f>5.04/1000</f>
+        <v>5.0400000000000002E-3</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>105.10000000000001</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>45</v>
+      <c r="A71" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="B71" s="2">
         <v>100</v>
       </c>
-      <c r="C71" s="6">
-        <v>1696.94</v>
-      </c>
-      <c r="D71" s="6">
-        <v>1645.6655852073</v>
+      <c r="C71" s="24">
+        <v>1406.91</v>
+      </c>
+      <c r="D71" s="24">
+        <v>1310.38479266175</v>
       </c>
       <c r="E71" s="3">
         <f t="shared" si="0"/>
-        <v>-3.0215808922354426E-2</v>
+        <v>-6.8607947443866446E-2</v>
       </c>
       <c r="F71" s="4">
-        <f>5.31/1000</f>
-        <v>5.3099999999999996E-3</v>
+        <f>10.61/1000</f>
+        <v>1.061E-2</v>
       </c>
       <c r="G71" s="1">
         <v>5000</v>
       </c>
       <c r="H71" s="6">
         <f t="shared" si="1"/>
-        <v>26.549999999999997</v>
+        <v>53.05</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B72" s="2">
-        <v>100</v>
-      </c>
-      <c r="C72" s="24">
-        <v>1406.91</v>
-      </c>
-      <c r="D72" s="24">
-        <v>1287.7742416317201</v>
-      </c>
-      <c r="E72" s="3">
-        <f t="shared" si="0"/>
-        <v>-8.4679018820166152E-2</v>
-      </c>
-      <c r="F72" s="4">
-        <f>12.38/1000</f>
-        <v>1.238E-2</v>
-      </c>
-      <c r="G72" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H72" s="6">
-        <f t="shared" si="1"/>
-        <v>61.9</v>
-      </c>
+      <c r="B72" s="7"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B73" s="7"/>
@@ -4033,9 +4008,6 @@
     </row>
     <row r="281" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B281" s="7"/>
-    </row>
-    <row r="282" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B282" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research related\dev\VRP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CCF451-8549-46EE-AC6C-075C71C1ACEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4E48F5-A817-4065-975C-199A829B5851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1528,15 +1528,15 @@
         <v>-5.3958025936340359E-4</v>
       </c>
       <c r="F66" s="5">
-        <f>3.02/1000</f>
-        <v>3.0200000000000001E-3</v>
+        <f>3.5/1000</f>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G66" s="1">
         <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f>F66 * G66</f>
-        <v>15.100000000000001</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -1550,22 +1550,22 @@
         <v>3055.23</v>
       </c>
       <c r="D67" s="26">
-        <v>3119.2520262377302</v>
+        <v>3119.96558688086</v>
       </c>
       <c r="E67" s="3">
         <f>D67/C67-1</f>
-        <v>2.0954895781243987E-2</v>
+        <v>2.1188449603093629E-2</v>
       </c>
       <c r="F67" s="4">
-        <f>8.38/1000</f>
-        <v>8.3800000000000003E-3</v>
+        <f>9.13/1000</f>
+        <v>9.130000000000001E-3</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" ref="H67:H70" si="0">F67 * G67</f>
-        <v>41.9</v>
+        <v>45.650000000000006</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -1579,22 +1579,22 @@
         <v>1395.85</v>
       </c>
       <c r="D68" s="25">
-        <v>1333.4754040789301</v>
+        <v>1338.8487476749899</v>
       </c>
       <c r="E68" s="3">
         <f>D68/C68-1</f>
-        <v>-4.4685744113672543E-2</v>
+        <v>-4.083623048680729E-2</v>
       </c>
       <c r="F68" s="4">
-        <f>11.13/1000</f>
-        <v>1.1130000000000001E-2</v>
+        <f>11.79/1000</f>
+        <v>1.1789999999999998E-2</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="0"/>
-        <v>55.650000000000006</v>
+        <v>58.949999999999989</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -1608,22 +1608,22 @@
         <v>38684</v>
       </c>
       <c r="D69" s="25">
-        <v>41023.472215590598</v>
+        <v>41277.955247092701</v>
       </c>
       <c r="E69" s="3">
         <f>D69/C69-1</f>
-        <v>6.0476481635575396E-2</v>
+        <v>6.7054990360166933E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>16.54/1000</f>
-        <v>1.6539999999999999E-2</v>
+        <f>17.3/1000</f>
+        <v>1.7299999999999999E-2</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="0"/>
-        <v>82.699999999999989</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -1637,22 +1637,22 @@
         <v>21736</v>
       </c>
       <c r="D70" s="26">
-        <v>22858.740516695099</v>
+        <v>22505.4661764384</v>
       </c>
       <c r="E70" s="3">
         <f>D70/C70-1</f>
-        <v>5.1653501872244156E-2</v>
+        <v>3.5400541794184726E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>21.31/1000</f>
-        <v>2.1309999999999999E-2</v>
+        <f>22.08/1000</f>
+        <v>2.2079999999999999E-2</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="0"/>
-        <v>106.55</v>
+        <v>110.39999999999999</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -3216,22 +3216,22 @@
         <v>1645.79</v>
       </c>
       <c r="D66" s="6">
-        <v>1644.7048641157</v>
+        <v>1643.1353090513301</v>
       </c>
       <c r="E66" s="3">
         <f>D66/C66-1</f>
-        <v>-6.5934042879101096E-4</v>
+        <v>-1.6130192483062578E-3</v>
       </c>
       <c r="F66" s="5">
-        <f>5.14/1000</f>
-        <v>5.1399999999999996E-3</v>
+        <f>5.35/1000</f>
+        <v>5.3499999999999997E-3</v>
       </c>
       <c r="G66" s="1">
         <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f>F66 * G66</f>
-        <v>25.7</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -3245,22 +3245,22 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="D67" s="24">
-        <v>1179.9333546359801</v>
+        <v>1181.38256673258</v>
       </c>
       <c r="E67" s="3">
         <f t="shared" ref="E67:E71" si="0">D67/C67-1</f>
-        <v>-5.7839652310435308E-2</v>
+        <v>-5.6682476638229784E-2</v>
       </c>
       <c r="F67" s="4">
-        <f>13.49/1000</f>
-        <v>1.349E-2</v>
+        <f>13.59/1000</f>
+        <v>1.359E-2</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" ref="H67:H71" si="1">F67 * G67</f>
-        <v>67.45</v>
+        <v>67.95</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -3281,15 +3281,15 @@
         <v>-3.7795946487007015E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>5.85/1000</f>
-        <v>5.8499999999999993E-3</v>
+        <f>6.62/1000</f>
+        <v>6.62E-3</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>29.249999999999996</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -3310,15 +3310,15 @@
         <v>-5.8207596321802058E-6</v>
       </c>
       <c r="F69" s="4">
-        <f>21.05/1000</f>
-        <v>2.1049999999999999E-2</v>
+        <f>22.76/1000</f>
+        <v>2.2760000000000002E-2</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>105.25</v>
+        <v>113.80000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -3332,22 +3332,22 @@
         <v>1696.94</v>
       </c>
       <c r="D70" s="6">
-        <v>1645.5434971790201</v>
+        <v>1646.88100186974</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-3.028775491235991E-2</v>
+        <v>-2.9499568712070046E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>5.04/1000</f>
-        <v>5.0400000000000002E-3</v>
+        <f>5.45/1000</f>
+        <v>5.45E-3</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>25.2</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -3361,22 +3361,22 @@
         <v>1406.91</v>
       </c>
       <c r="D71" s="24">
-        <v>1310.38479266175</v>
+        <v>1289.4397647765099</v>
       </c>
       <c r="E71" s="3">
         <f t="shared" si="0"/>
-        <v>-6.8607947443866446E-2</v>
+        <v>-8.3495202410594938E-2</v>
       </c>
       <c r="F71" s="4">
-        <f>10.61/1000</f>
-        <v>1.061E-2</v>
+        <f>11.71/1000</f>
+        <v>1.1710000000000002E-2</v>
       </c>
       <c r="G71" s="1">
         <v>5000</v>
       </c>
       <c r="H71" s="6">
         <f t="shared" si="1"/>
-        <v>53.05</v>
+        <v>58.550000000000011</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4E48F5-A817-4065-975C-199A829B5851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0A09DD-7777-48C6-BB1B-A553BE5697C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="88">
   <si>
     <t>Best known</t>
   </si>
@@ -68,9 +68,6 @@
     <t>        Ψᵢ  =   [</t>
   </si>
   <si>
-    <t>                    :swap!</t>
-  </si>
-  <si>
     <t>        ω   =   0.05                    ,</t>
   </si>
   <si>
@@ -89,9 +86,6 @@
     <t>        Ψₗ  =   [</t>
   </si>
   <si>
-    <t>                    :move!          ,</t>
-  </si>
-  <si>
     <t>Size</t>
   </si>
   <si>
@@ -227,9 +221,6 @@
     <t>                    :regret3!</t>
   </si>
   <si>
-    <t>                    :split!         ,</t>
-  </si>
-  <si>
     <t>        ρ   =   0.1</t>
   </si>
   <si>
@@ -299,10 +290,16 @@
     <t>        𝜃   =   0.9975                 ,</t>
   </si>
   <si>
-    <t>                    :opt!           ,</t>
-  </si>
-  <si>
-    <t>                    :opt!           ,</t>
+    <t>                    :intraopt!          ,</t>
+  </si>
+  <si>
+    <t>                    :interopt!          ,</t>
+  </si>
+  <si>
+    <t>                    :movecustomer!      ,</t>
+  </si>
+  <si>
+    <t>                    :swapcustomers!</t>
   </si>
 </sst>
 </file>
@@ -832,7 +829,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -850,16 +847,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -867,11 +864,11 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -879,35 +876,35 @@
     </row>
     <row r="6" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1"/>
     </row>
@@ -919,7 +916,7 @@
     </row>
     <row r="12" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -927,40 +924,40 @@
     </row>
     <row r="13" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -975,7 +972,7 @@
     </row>
     <row r="18" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B18" s="8"/>
       <c r="L18" s="12"/>
@@ -994,7 +991,7 @@
     </row>
     <row r="19" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B19" s="12"/>
       <c r="W19" s="12"/>
@@ -1002,7 +999,7 @@
     </row>
     <row r="20" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B20" s="12"/>
       <c r="W20" s="12"/>
@@ -1010,7 +1007,7 @@
     </row>
     <row r="21" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B21" s="12"/>
       <c r="U21" s="12"/>
@@ -1020,7 +1017,7 @@
     </row>
     <row r="22" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B22" s="12"/>
       <c r="U22" s="12"/>
@@ -1030,7 +1027,7 @@
     </row>
     <row r="23" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B23" s="12"/>
       <c r="H23" s="12"/>
@@ -1041,7 +1038,7 @@
     </row>
     <row r="24" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B24" s="12"/>
       <c r="H24" s="12"/>
@@ -1052,7 +1049,7 @@
     </row>
     <row r="25" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B25" s="12"/>
       <c r="H25" s="12"/>
@@ -1074,7 +1071,7 @@
     </row>
     <row r="27" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B27" s="12"/>
       <c r="U27" s="12"/>
@@ -1084,7 +1081,7 @@
     </row>
     <row r="28" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B28" s="12"/>
       <c r="U28" s="12"/>
@@ -1094,7 +1091,7 @@
     </row>
     <row r="29" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B29" s="12"/>
       <c r="U29" s="12"/>
@@ -1104,7 +1101,7 @@
     </row>
     <row r="30" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B30" s="12"/>
       <c r="U30" s="12"/>
@@ -1114,7 +1111,7 @@
     </row>
     <row r="31" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B31" s="12"/>
       <c r="U31" s="12"/>
@@ -1124,7 +1121,7 @@
     </row>
     <row r="32" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B32" s="12"/>
       <c r="U32" s="12"/>
@@ -1134,7 +1131,7 @@
     </row>
     <row r="33" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B33" s="12"/>
       <c r="U33" s="12"/>
@@ -1144,7 +1141,7 @@
     </row>
     <row r="34" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B34" s="12"/>
       <c r="U34" s="12"/>
@@ -1154,7 +1151,7 @@
     </row>
     <row r="35" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B35" s="12"/>
       <c r="U35" s="12"/>
@@ -1184,7 +1181,7 @@
     </row>
     <row r="38" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -1201,7 +1198,7 @@
     </row>
     <row r="39" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -1218,7 +1215,7 @@
     </row>
     <row r="40" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -1235,7 +1232,7 @@
     </row>
     <row r="41" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -1252,7 +1249,7 @@
     </row>
     <row r="42" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -1269,7 +1266,7 @@
     </row>
     <row r="43" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -1297,7 +1294,7 @@
     </row>
     <row r="45" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B45" s="12"/>
       <c r="H45" s="9"/>
@@ -1308,7 +1305,7 @@
     </row>
     <row r="46" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="B46" s="12"/>
       <c r="H46" s="9"/>
@@ -1319,7 +1316,7 @@
     </row>
     <row r="47" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B47" s="12"/>
       <c r="H47" s="9"/>
@@ -1330,7 +1327,7 @@
     </row>
     <row r="48" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B48" s="12"/>
       <c r="H48" s="9"/>
@@ -1341,7 +1338,7 @@
     </row>
     <row r="49" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="B49" s="12"/>
       <c r="H49" s="9"/>
@@ -1363,7 +1360,7 @@
     </row>
     <row r="51" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B51" s="12"/>
       <c r="H51" s="9"/>
@@ -1374,7 +1371,7 @@
     </row>
     <row r="52" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B52" s="12"/>
       <c r="H52" s="9"/>
@@ -1385,7 +1382,7 @@
     </row>
     <row r="53" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B53" s="12"/>
       <c r="H53" s="9"/>
@@ -1396,7 +1393,7 @@
     </row>
     <row r="54" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" s="12"/>
       <c r="U54" s="12"/>
@@ -1406,7 +1403,7 @@
     </row>
     <row r="55" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55" s="12"/>
       <c r="U55" s="12"/>
@@ -1416,7 +1413,7 @@
     </row>
     <row r="56" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B56" s="12"/>
       <c r="U56" s="12"/>
@@ -1426,7 +1423,7 @@
     </row>
     <row r="57" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B57" s="12"/>
       <c r="U57" s="12"/>
@@ -1436,7 +1433,7 @@
     </row>
     <row r="58" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B58" s="12"/>
       <c r="U58" s="12"/>
@@ -1446,7 +1443,7 @@
     </row>
     <row r="59" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B59" s="12"/>
       <c r="U59" s="12"/>
@@ -1456,7 +1453,7 @@
     </row>
     <row r="60" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B60" s="12"/>
       <c r="U60" s="12"/>
@@ -1466,21 +1463,21 @@
     </row>
     <row r="61" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="U61" s="12"/>
       <c r="V61" s="12"/>
     </row>
     <row r="62" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="U62" s="12"/>
       <c r="V62" s="12"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64" s="17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B64" s="7"/>
     </row>
@@ -1489,7 +1486,7 @@
         <v>2</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C65" s="18" t="s">
         <v>0</v>
@@ -1504,7 +1501,7 @@
         <v>4</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H65" s="18" t="s">
         <v>5</v>
@@ -1512,7 +1509,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B66" s="2">
         <v>100</v>
@@ -1521,27 +1518,27 @@
         <v>820</v>
       </c>
       <c r="D66" s="25">
-        <v>819.55754418732204</v>
+        <v>819.55754418729703</v>
       </c>
       <c r="E66" s="3">
         <f>D66/C66-1</f>
-        <v>-5.3958025936340359E-4</v>
+        <v>-5.395802593938237E-4</v>
       </c>
       <c r="F66" s="5">
-        <f>3.5/1000</f>
-        <v>3.5000000000000001E-3</v>
+        <f>3.68/1000</f>
+        <v>3.6800000000000001E-3</v>
       </c>
       <c r="G66" s="1">
         <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f>F66 * G66</f>
-        <v>17.5</v>
+        <v>18.400000000000002</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B67" s="1">
         <v>150</v>
@@ -1550,27 +1547,27 @@
         <v>3055.23</v>
       </c>
       <c r="D67" s="26">
-        <v>3119.96558688086</v>
+        <v>3077.5661725801101</v>
       </c>
       <c r="E67" s="3">
         <f>D67/C67-1</f>
-        <v>2.1188449603093629E-2</v>
+        <v>7.3107990495346886E-3</v>
       </c>
       <c r="F67" s="4">
-        <f>9.13/1000</f>
-        <v>9.130000000000001E-3</v>
+        <f>9.33/1000</f>
+        <v>9.3299999999999998E-3</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" ref="H67:H70" si="0">F67 * G67</f>
-        <v>45.650000000000006</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B68" s="2">
         <v>200</v>
@@ -1579,27 +1576,27 @@
         <v>1395.85</v>
       </c>
       <c r="D68" s="25">
-        <v>1338.8487476749899</v>
+        <v>1348.13445874081</v>
       </c>
       <c r="E68" s="3">
         <f>D68/C68-1</f>
-        <v>-4.083623048680729E-2</v>
+        <v>-3.4183860199297866E-2</v>
       </c>
       <c r="F68" s="4">
-        <f>11.79/1000</f>
-        <v>1.1789999999999998E-2</v>
+        <f>12.41/1000</f>
+        <v>1.2410000000000001E-2</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="0"/>
-        <v>58.949999999999989</v>
+        <v>62.050000000000004</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B69" s="1">
         <v>250</v>
@@ -1608,27 +1605,27 @@
         <v>38684</v>
       </c>
       <c r="D69" s="25">
-        <v>41277.955247092701</v>
+        <v>40435.213384017603</v>
       </c>
       <c r="E69" s="3">
         <f>D69/C69-1</f>
-        <v>6.7054990360166933E-2</v>
+        <v>4.5269707993423669E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>17.3/1000</f>
-        <v>1.7299999999999999E-2</v>
+        <f>18.23/1000</f>
+        <v>1.823E-2</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="0"/>
-        <v>86.5</v>
+        <v>91.149999999999991</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B70" s="7">
         <v>302</v>
@@ -1637,22 +1634,22 @@
         <v>21736</v>
       </c>
       <c r="D70" s="26">
-        <v>22505.4661764384</v>
+        <v>22900.663691351499</v>
       </c>
       <c r="E70" s="3">
         <f>D70/C70-1</f>
-        <v>3.5400541794184726E-2</v>
+        <v>5.3582245645541926E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>22.08/1000</f>
-        <v>2.2079999999999999E-2</v>
+        <f>23.94/1000</f>
+        <v>2.3940000000000003E-2</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="0"/>
-        <v>110.39999999999999</v>
+        <v>119.70000000000002</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -2294,7 +2291,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -2312,16 +2309,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2329,11 +2326,11 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -2341,35 +2338,35 @@
     </row>
     <row r="6" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1"/>
     </row>
@@ -2381,7 +2378,7 @@
     </row>
     <row r="12" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -2389,40 +2386,40 @@
     </row>
     <row r="13" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:6" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2430,7 +2427,7 @@
     </row>
     <row r="18" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B18" s="8"/>
       <c r="L18" s="12"/>
@@ -2449,7 +2446,7 @@
     </row>
     <row r="19" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B19" s="11"/>
       <c r="L19" s="12"/>
@@ -2458,7 +2455,7 @@
     </row>
     <row r="20" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="L20" s="12"/>
@@ -2467,7 +2464,7 @@
     </row>
     <row r="21" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -2484,7 +2481,7 @@
     </row>
     <row r="22" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -2501,7 +2498,7 @@
     </row>
     <row r="23" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -2518,7 +2515,7 @@
     </row>
     <row r="24" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -2535,7 +2532,7 @@
     </row>
     <row r="25" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -2569,7 +2566,7 @@
     </row>
     <row r="27" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -2586,7 +2583,7 @@
     </row>
     <row r="28" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -2603,7 +2600,7 @@
     </row>
     <row r="29" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -2620,7 +2617,7 @@
     </row>
     <row r="30" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -2637,7 +2634,7 @@
     </row>
     <row r="31" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -2654,7 +2651,7 @@
     </row>
     <row r="32" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -2671,7 +2668,7 @@
     </row>
     <row r="33" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -2688,7 +2685,7 @@
     </row>
     <row r="34" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -2705,7 +2702,7 @@
     </row>
     <row r="35" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -2756,7 +2753,7 @@
     </row>
     <row r="38" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -2773,7 +2770,7 @@
     </row>
     <row r="39" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -2790,7 +2787,7 @@
     </row>
     <row r="40" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -2807,7 +2804,7 @@
     </row>
     <row r="41" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -2824,7 +2821,7 @@
     </row>
     <row r="42" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -2841,7 +2838,7 @@
     </row>
     <row r="43" spans="1:24" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -2875,7 +2872,7 @@
     </row>
     <row r="45" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
@@ -2892,7 +2889,7 @@
     </row>
     <row r="46" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -2909,7 +2906,7 @@
     </row>
     <row r="47" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -2926,7 +2923,7 @@
     </row>
     <row r="48" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -2943,7 +2940,7 @@
     </row>
     <row r="49" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -2977,7 +2974,7 @@
     </row>
     <row r="51" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
@@ -2994,7 +2991,7 @@
     </row>
     <row r="52" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -3011,7 +3008,7 @@
     </row>
     <row r="53" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -3028,7 +3025,7 @@
     </row>
     <row r="54" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
@@ -3045,7 +3042,7 @@
     </row>
     <row r="55" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
@@ -3062,7 +3059,7 @@
     </row>
     <row r="56" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
@@ -3079,7 +3076,7 @@
     </row>
     <row r="57" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
@@ -3096,7 +3093,7 @@
     </row>
     <row r="58" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
@@ -3113,7 +3110,7 @@
     </row>
     <row r="59" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -3130,7 +3127,7 @@
     </row>
     <row r="60" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -3147,7 +3144,7 @@
     </row>
     <row r="61" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -3161,7 +3158,7 @@
     </row>
     <row r="62" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
@@ -3175,7 +3172,7 @@
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64" s="17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B64" s="7"/>
     </row>
@@ -3184,7 +3181,7 @@
         <v>2</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C65" s="18" t="s">
         <v>0</v>
@@ -3199,7 +3196,7 @@
         <v>4</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H65" s="18" t="s">
         <v>5</v>
@@ -3207,7 +3204,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B66" s="2">
         <v>100</v>
@@ -3216,27 +3213,27 @@
         <v>1645.79</v>
       </c>
       <c r="D66" s="6">
-        <v>1643.1353090513301</v>
+        <v>1657.37834348964</v>
       </c>
       <c r="E66" s="3">
         <f>D66/C66-1</f>
-        <v>-1.6130192483062578E-3</v>
+        <v>7.0412042178162881E-3</v>
       </c>
       <c r="F66" s="5">
-        <f>5.35/1000</f>
-        <v>5.3499999999999997E-3</v>
+        <f>5.23/1000</f>
+        <v>5.2300000000000003E-3</v>
       </c>
       <c r="G66" s="1">
         <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f>F66 * G66</f>
-        <v>26.75</v>
+        <v>26.150000000000002</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B67" s="2">
         <v>100</v>
@@ -3245,27 +3242,27 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="D67" s="24">
-        <v>1181.38256673258</v>
+        <v>1197.04854263431</v>
       </c>
       <c r="E67" s="3">
         <f t="shared" ref="E67:E71" si="0">D67/C67-1</f>
-        <v>-5.6682476638229784E-2</v>
+        <v>-4.4173413101311843E-2</v>
       </c>
       <c r="F67" s="4">
-        <f>13.59/1000</f>
-        <v>1.359E-2</v>
+        <f>15.07/1000</f>
+        <v>1.507E-2</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" ref="H67:H71" si="1">F67 * G67</f>
-        <v>67.95</v>
+        <v>75.349999999999994</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B68" s="2">
         <v>100</v>
@@ -3281,20 +3278,20 @@
         <v>-3.7795946487007015E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>6.62/1000</f>
-        <v>6.62E-3</v>
+        <f>6.42/1000</f>
+        <v>6.4200000000000004E-3</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>33.1</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B69" s="2">
         <v>100</v>
@@ -3310,20 +3307,20 @@
         <v>-5.8207596321802058E-6</v>
       </c>
       <c r="F69" s="4">
-        <f>22.76/1000</f>
-        <v>2.2760000000000002E-2</v>
+        <f>22.78/1000</f>
+        <v>2.2780000000000002E-2</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>113.80000000000001</v>
+        <v>113.9</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B70" s="2">
         <v>100</v>
@@ -3332,27 +3329,27 @@
         <v>1696.94</v>
       </c>
       <c r="D70" s="6">
-        <v>1646.88100186974</v>
+        <v>1667.0215584974701</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-2.9499568712070046E-2</v>
+        <v>-1.7630818710461127E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>5.45/1000</f>
-        <v>5.45E-3</v>
+        <f>5.74/1000</f>
+        <v>5.7400000000000003E-3</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>27.25</v>
+        <v>28.700000000000003</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B71" s="2">
         <v>100</v>
@@ -3361,22 +3358,22 @@
         <v>1406.91</v>
       </c>
       <c r="D71" s="24">
-        <v>1289.4397647765099</v>
+        <v>1303.8348581678899</v>
       </c>
       <c r="E71" s="3">
         <f t="shared" si="0"/>
-        <v>-8.3495202410594938E-2</v>
+        <v>-7.3263493636487209E-2</v>
       </c>
       <c r="F71" s="4">
-        <f>11.71/1000</f>
-        <v>1.1710000000000002E-2</v>
+        <f>14.73/1000</f>
+        <v>1.473E-2</v>
       </c>
       <c r="G71" s="1">
         <v>5000</v>
       </c>
       <c r="H71" s="6">
         <f t="shared" si="1"/>
-        <v>58.550000000000011</v>
+        <v>73.650000000000006</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0A09DD-7777-48C6-BB1B-A553BE5697C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913D9691-38B4-4753-B917-743590ABB1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1525,15 +1525,15 @@
         <v>-5.395802593938237E-4</v>
       </c>
       <c r="F66" s="5">
-        <f>3.68/1000</f>
-        <v>3.6800000000000001E-3</v>
+        <f>3.44/1000</f>
+        <v>3.4399999999999999E-3</v>
       </c>
       <c r="G66" s="1">
         <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f>F66 * G66</f>
-        <v>18.400000000000002</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -1547,22 +1547,22 @@
         <v>3055.23</v>
       </c>
       <c r="D67" s="26">
-        <v>3077.5661725801101</v>
+        <v>3114.5399906339198</v>
       </c>
       <c r="E67" s="3">
         <f>D67/C67-1</f>
-        <v>7.3107990495346886E-3</v>
+        <v>1.941261071471545E-2</v>
       </c>
       <c r="F67" s="4">
-        <f>9.33/1000</f>
-        <v>9.3299999999999998E-3</v>
+        <f>9.53/1000</f>
+        <v>9.5299999999999985E-3</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" ref="H67:H70" si="0">F67 * G67</f>
-        <v>46.65</v>
+        <v>47.649999999999991</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -1576,22 +1576,22 @@
         <v>1395.85</v>
       </c>
       <c r="D68" s="25">
-        <v>1348.13445874081</v>
+        <v>1341.88947812068</v>
       </c>
       <c r="E68" s="3">
         <f>D68/C68-1</f>
-        <v>-3.4183860199297866E-2</v>
+        <v>-3.8657822745509884E-2</v>
       </c>
       <c r="F68" s="4">
-        <f>12.41/1000</f>
-        <v>1.2410000000000001E-2</v>
+        <f>12.71/1000</f>
+        <v>1.2710000000000001E-2</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="0"/>
-        <v>62.050000000000004</v>
+        <v>63.550000000000004</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -1605,22 +1605,22 @@
         <v>38684</v>
       </c>
       <c r="D69" s="25">
-        <v>40435.213384017603</v>
+        <v>40980.200127624703</v>
       </c>
       <c r="E69" s="3">
         <f>D69/C69-1</f>
-        <v>4.5269707993423669E-2</v>
+        <v>5.9357877355617372E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>18.23/1000</f>
-        <v>1.823E-2</v>
+        <f>19.69/1000</f>
+        <v>1.9690000000000003E-2</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="0"/>
-        <v>91.149999999999991</v>
+        <v>98.450000000000017</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -1634,22 +1634,22 @@
         <v>21736</v>
       </c>
       <c r="D70" s="26">
-        <v>22900.663691351499</v>
+        <v>22701.6539880856</v>
       </c>
       <c r="E70" s="3">
         <f>D70/C70-1</f>
-        <v>5.3582245645541926E-2</v>
+        <v>4.4426480865182194E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>23.94/1000</f>
-        <v>2.3940000000000003E-2</v>
+        <f>24.12/1000</f>
+        <v>2.4120000000000003E-2</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="0"/>
-        <v>119.70000000000002</v>
+        <v>120.60000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -3213,22 +3213,22 @@
         <v>1645.79</v>
       </c>
       <c r="D66" s="6">
-        <v>1657.37834348964</v>
+        <v>1646.2017846456699</v>
       </c>
       <c r="E66" s="3">
         <f>D66/C66-1</f>
-        <v>7.0412042178162881E-3</v>
+        <v>2.5020485339566356E-4</v>
       </c>
       <c r="F66" s="5">
-        <f>5.23/1000</f>
-        <v>5.2300000000000003E-3</v>
+        <f>5.49/1000</f>
+        <v>5.4900000000000001E-3</v>
       </c>
       <c r="G66" s="1">
         <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f>F66 * G66</f>
-        <v>26.150000000000002</v>
+        <v>27.45</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -3242,22 +3242,22 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="D67" s="24">
-        <v>1197.04854263431</v>
+        <v>1190.12509106575</v>
       </c>
       <c r="E67" s="3">
         <f t="shared" ref="E67:E71" si="0">D67/C67-1</f>
-        <v>-4.4173413101311843E-2</v>
+        <v>-4.9701692737968761E-2</v>
       </c>
       <c r="F67" s="4">
-        <f>15.07/1000</f>
-        <v>1.507E-2</v>
+        <f>15.21/1000</f>
+        <v>1.5210000000000001E-2</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" ref="H67:H71" si="1">F67 * G67</f>
-        <v>75.349999999999994</v>
+        <v>76.050000000000011</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -3329,22 +3329,22 @@
         <v>1696.94</v>
       </c>
       <c r="D70" s="6">
-        <v>1667.0215584974701</v>
+        <v>1659.0532618919001</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-1.7630818710461127E-2</v>
+        <v>-2.2326504241811707E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>5.74/1000</f>
-        <v>5.7400000000000003E-3</v>
+        <f>5.71/1000</f>
+        <v>5.7099999999999998E-3</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>28.700000000000003</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -3358,22 +3358,22 @@
         <v>1406.91</v>
       </c>
       <c r="D71" s="24">
-        <v>1303.8348581678899</v>
+        <v>1303.08242903631</v>
       </c>
       <c r="E71" s="3">
         <f t="shared" si="0"/>
-        <v>-7.3263493636487209E-2</v>
+        <v>-7.3798303348252547E-2</v>
       </c>
       <c r="F71" s="4">
-        <f>14.73/1000</f>
-        <v>1.473E-2</v>
+        <f>13.92/1000</f>
+        <v>1.392E-2</v>
       </c>
       <c r="G71" s="1">
         <v>5000</v>
       </c>
       <c r="H71" s="6">
         <f t="shared" si="1"/>
-        <v>73.650000000000006</v>
+        <v>69.599999999999994</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913D9691-38B4-4753-B917-743590ABB1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6BCD5A-94C2-4334-9427-39B3B1AA6B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6BCD5A-94C2-4334-9427-39B3B1AA6B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC41AF92-30FE-4363-8A1C-F1558B9E5736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="89">
   <si>
     <t>Best known</t>
   </si>
@@ -284,9 +284,6 @@
     <t>                    :greedyperturb! ,</t>
   </si>
   <si>
-    <t>MersenneTwister(1104); MersenneTwister(1234); MersenneTwister(1403)</t>
-  </si>
-  <si>
     <t>        𝜃   =   0.9975                 ,</t>
   </si>
   <si>
@@ -300,6 +297,12 @@
   </si>
   <si>
     <t>                    :swapcustomers!</t>
+  </si>
+  <si>
+    <t>MersenneTwister(1104); MersenneTwister(1234); MersenneTwister(1403); MersenneTwister(2104); MersenneTwister(2109)</t>
+  </si>
+  <si>
+    <t>MersenneTwister(1104); MersenneTwister(1234); MersenneTwister(1403); MersenneTwister(2104); MersenneTwister(2111)</t>
   </si>
 </sst>
 </file>
@@ -948,7 +951,7 @@
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -1305,7 +1308,7 @@
     </row>
     <row r="46" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B46" s="12"/>
       <c r="H46" s="9"/>
@@ -1316,7 +1319,7 @@
     </row>
     <row r="47" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B47" s="12"/>
       <c r="H47" s="9"/>
@@ -1327,7 +1330,7 @@
     </row>
     <row r="48" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B48" s="12"/>
       <c r="H48" s="9"/>
@@ -1338,7 +1341,7 @@
     </row>
     <row r="49" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B49" s="12"/>
       <c r="H49" s="9"/>
@@ -1413,7 +1416,7 @@
     </row>
     <row r="56" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B56" s="12"/>
       <c r="U56" s="12"/>
@@ -1525,15 +1528,15 @@
         <v>-5.395802593938237E-4</v>
       </c>
       <c r="F66" s="5">
-        <f>3.44/1000</f>
-        <v>3.4399999999999999E-3</v>
+        <f>3.42/1000</f>
+        <v>3.4199999999999999E-3</v>
       </c>
       <c r="G66" s="1">
         <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f>F66 * G66</f>
-        <v>17.2</v>
+        <v>17.099999999999998</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -1547,22 +1550,22 @@
         <v>3055.23</v>
       </c>
       <c r="D67" s="26">
-        <v>3114.5399906339198</v>
+        <v>3093.2221530659699</v>
       </c>
       <c r="E67" s="3">
         <f>D67/C67-1</f>
-        <v>1.941261071471545E-2</v>
+        <v>1.2435120454423965E-2</v>
       </c>
       <c r="F67" s="4">
-        <f>9.53/1000</f>
-        <v>9.5299999999999985E-3</v>
+        <f>9.02/1000</f>
+        <v>9.0200000000000002E-3</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" ref="H67:H70" si="0">F67 * G67</f>
-        <v>47.649999999999991</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -1576,22 +1579,22 @@
         <v>1395.85</v>
       </c>
       <c r="D68" s="25">
-        <v>1341.88947812068</v>
+        <v>1336.02518160913</v>
       </c>
       <c r="E68" s="3">
         <f>D68/C68-1</f>
-        <v>-3.8657822745509884E-2</v>
+        <v>-4.2859059634538066E-2</v>
       </c>
       <c r="F68" s="4">
-        <f>12.71/1000</f>
-        <v>1.2710000000000001E-2</v>
+        <f>12.5/1000</f>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="0"/>
-        <v>63.550000000000004</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -1605,22 +1608,22 @@
         <v>38684</v>
       </c>
       <c r="D69" s="25">
-        <v>40980.200127624703</v>
+        <v>40601.526723655501</v>
       </c>
       <c r="E69" s="3">
         <f>D69/C69-1</f>
-        <v>5.9357877355617372E-2</v>
+        <v>4.9568987789667673E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>19.69/1000</f>
-        <v>1.9690000000000003E-2</v>
+        <f>17.94/1000</f>
+        <v>1.7940000000000001E-2</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="0"/>
-        <v>98.450000000000017</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -1634,22 +1637,22 @@
         <v>21736</v>
       </c>
       <c r="D70" s="26">
-        <v>22701.6539880856</v>
+        <v>22488.8540592141</v>
       </c>
       <c r="E70" s="3">
         <f>D70/C70-1</f>
-        <v>4.4426480865182194E-2</v>
+        <v>3.4636274347354501E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>24.12/1000</f>
-        <v>2.4120000000000003E-2</v>
+        <f>23.1/1000</f>
+        <v>2.3100000000000002E-2</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="0"/>
-        <v>120.60000000000001</v>
+        <v>115.50000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -2410,7 +2413,7 @@
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -2889,7 +2892,7 @@
     </row>
     <row r="46" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -2906,7 +2909,7 @@
     </row>
     <row r="47" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -2923,7 +2926,7 @@
     </row>
     <row r="48" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -2940,7 +2943,7 @@
     </row>
     <row r="49" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -3059,7 +3062,7 @@
     </row>
     <row r="56" spans="1:24" ht="14" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
@@ -3213,22 +3216,22 @@
         <v>1645.79</v>
       </c>
       <c r="D66" s="6">
-        <v>1646.2017846456699</v>
+        <v>1651.6099471647799</v>
       </c>
       <c r="E66" s="3">
         <f>D66/C66-1</f>
-        <v>2.5020485339566356E-4</v>
+        <v>3.5362635359188488E-3</v>
       </c>
       <c r="F66" s="5">
-        <f>5.49/1000</f>
-        <v>5.4900000000000001E-3</v>
+        <f>5.22/1000</f>
+        <v>5.2199999999999998E-3</v>
       </c>
       <c r="G66" s="1">
         <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f>F66 * G66</f>
-        <v>27.45</v>
+        <v>26.099999999999998</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -3242,22 +3245,22 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="D67" s="24">
-        <v>1190.12509106575</v>
+        <v>1173.8423924108399</v>
       </c>
       <c r="E67" s="3">
         <f t="shared" ref="E67:E71" si="0">D67/C67-1</f>
-        <v>-4.9701692737968761E-2</v>
+        <v>-6.2703200802606274E-2</v>
       </c>
       <c r="F67" s="4">
-        <f>15.21/1000</f>
-        <v>1.5210000000000001E-2</v>
+        <f>14.25/1000</f>
+        <v>1.4250000000000001E-2</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" ref="H67:H71" si="1">F67 * G67</f>
-        <v>76.050000000000011</v>
+        <v>71.25</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -3278,15 +3281,15 @@
         <v>-3.7795946487007015E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>6.42/1000</f>
-        <v>6.4200000000000004E-3</v>
+        <f>6.32/1000</f>
+        <v>6.3200000000000001E-3</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>32.1</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -3307,15 +3310,15 @@
         <v>-5.8207596321802058E-6</v>
       </c>
       <c r="F69" s="4">
-        <f>22.78/1000</f>
-        <v>2.2780000000000002E-2</v>
+        <f>21.85/1000</f>
+        <v>2.1850000000000001E-2</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>113.9</v>
+        <v>109.25</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -3329,22 +3332,22 @@
         <v>1696.94</v>
       </c>
       <c r="D70" s="6">
-        <v>1659.0532618919001</v>
+        <v>1646.5586337392799</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-2.2326504241811707E-2</v>
+        <v>-2.9689538970570695E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>5.71/1000</f>
-        <v>5.7099999999999998E-3</v>
+        <f>5.3/1000</f>
+        <v>5.3E-3</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>28.55</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -3358,22 +3361,22 @@
         <v>1406.91</v>
       </c>
       <c r="D71" s="24">
-        <v>1303.08242903631</v>
+        <v>1284.5587937903999</v>
       </c>
       <c r="E71" s="3">
         <f t="shared" si="0"/>
-        <v>-7.3798303348252547E-2</v>
+        <v>-8.696448686099334E-2</v>
       </c>
       <c r="F71" s="4">
-        <f>13.92/1000</f>
-        <v>1.392E-2</v>
+        <f>11.03/1000</f>
+        <v>1.103E-2</v>
       </c>
       <c r="G71" s="1">
         <v>5000</v>
       </c>
       <c r="H71" s="6">
         <f t="shared" si="1"/>
-        <v>69.599999999999994</v>
+        <v>55.15</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC41AF92-30FE-4363-8A1C-F1558B9E5736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0F8E82-F678-4A91-8FCB-229676CF3EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VRP Benchmarking" sheetId="2" r:id="rId1"/>
@@ -1521,22 +1521,22 @@
         <v>820</v>
       </c>
       <c r="D66" s="25">
-        <v>819.55754418729703</v>
+        <v>819.55754418738104</v>
       </c>
       <c r="E66" s="3">
         <f>D66/C66-1</f>
-        <v>-5.395802593938237E-4</v>
+        <v>-5.3958025929146114E-4</v>
       </c>
       <c r="F66" s="5">
-        <f>3.42/1000</f>
-        <v>3.4199999999999999E-3</v>
+        <f>3.41/1000</f>
+        <v>3.4100000000000003E-3</v>
       </c>
       <c r="G66" s="1">
         <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f>F66 * G66</f>
-        <v>17.099999999999998</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -1550,22 +1550,22 @@
         <v>3055.23</v>
       </c>
       <c r="D67" s="26">
-        <v>3093.2221530659699</v>
+        <v>3104.6502215696901</v>
       </c>
       <c r="E67" s="3">
         <f>D67/C67-1</f>
-        <v>1.2435120454423965E-2</v>
+        <v>1.6175614133695282E-2</v>
       </c>
       <c r="F67" s="4">
-        <f>9.02/1000</f>
-        <v>9.0200000000000002E-3</v>
+        <f>8.96/1000</f>
+        <v>8.9600000000000009E-3</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" ref="H67:H70" si="0">F67 * G67</f>
-        <v>45.1</v>
+        <v>44.800000000000004</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -1579,22 +1579,22 @@
         <v>1395.85</v>
       </c>
       <c r="D68" s="25">
-        <v>1336.02518160913</v>
+        <v>1326.80755286926</v>
       </c>
       <c r="E68" s="3">
         <f>D68/C68-1</f>
-        <v>-4.2859059634538066E-2</v>
+        <v>-4.9462655106737752E-2</v>
       </c>
       <c r="F68" s="4">
-        <f>12.5/1000</f>
-        <v>1.2500000000000001E-2</v>
+        <f>12.13/1000</f>
+        <v>1.213E-2</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="0"/>
-        <v>62.5</v>
+        <v>60.65</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -1608,22 +1608,22 @@
         <v>38684</v>
       </c>
       <c r="D69" s="25">
-        <v>40601.526723655501</v>
+        <v>40802.580041417299</v>
       </c>
       <c r="E69" s="3">
         <f>D69/C69-1</f>
-        <v>4.9568987789667673E-2</v>
+        <v>5.4766312724053856E-2</v>
       </c>
       <c r="F69" s="4">
-        <f>17.94/1000</f>
-        <v>1.7940000000000001E-2</v>
+        <f>17.95/1000</f>
+        <v>1.7950000000000001E-2</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="0"/>
-        <v>89.7</v>
+        <v>89.75</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -1637,22 +1637,22 @@
         <v>21736</v>
       </c>
       <c r="D70" s="26">
-        <v>22488.8540592141</v>
+        <v>22782.558751227101</v>
       </c>
       <c r="E70" s="3">
         <f>D70/C70-1</f>
-        <v>3.4636274347354501E-2</v>
+        <v>4.8148635960024944E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>23.1/1000</f>
-        <v>2.3100000000000002E-2</v>
+        <f>23.75/1000</f>
+        <v>2.375E-2</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="0"/>
-        <v>115.50000000000001</v>
+        <v>118.75</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -3216,22 +3216,22 @@
         <v>1645.79</v>
       </c>
       <c r="D66" s="6">
-        <v>1651.6099471647799</v>
+        <v>1644.77986458692</v>
       </c>
       <c r="E66" s="3">
         <f>D66/C66-1</f>
-        <v>3.5362635359188488E-3</v>
+        <v>-6.1376932238010884E-4</v>
       </c>
       <c r="F66" s="5">
-        <f>5.22/1000</f>
-        <v>5.2199999999999998E-3</v>
+        <f>5.53/1000</f>
+        <v>5.5300000000000002E-3</v>
       </c>
       <c r="G66" s="1">
         <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f>F66 * G66</f>
-        <v>26.099999999999998</v>
+        <v>27.650000000000002</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -3245,22 +3245,22 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="D67" s="24">
-        <v>1173.8423924108399</v>
+        <v>1177.53321827185</v>
       </c>
       <c r="E67" s="3">
         <f t="shared" ref="E67:E71" si="0">D67/C67-1</f>
-        <v>-6.2703200802606274E-2</v>
+        <v>-5.9756127764278855E-2</v>
       </c>
       <c r="F67" s="4">
-        <f>14.25/1000</f>
-        <v>1.4250000000000001E-2</v>
+        <f>14.98/1000</f>
+        <v>1.498E-2</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" ref="H67:H71" si="1">F67 * G67</f>
-        <v>71.25</v>
+        <v>74.900000000000006</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -3281,15 +3281,15 @@
         <v>-3.7795946487007015E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>6.32/1000</f>
-        <v>6.3200000000000001E-3</v>
+        <f>6.55/1000</f>
+        <v>6.5499999999999994E-3</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>31.6</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -3310,15 +3310,15 @@
         <v>-5.8207596321802058E-6</v>
       </c>
       <c r="F69" s="4">
-        <f>21.85/1000</f>
-        <v>2.1850000000000001E-2</v>
+        <f>20.3/1000</f>
+        <v>2.0300000000000002E-2</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>109.25</v>
+        <v>101.50000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -3332,22 +3332,22 @@
         <v>1696.94</v>
       </c>
       <c r="D70" s="6">
-        <v>1646.5586337392799</v>
+        <v>1642.86396875943</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-2.9689538970570695E-2</v>
+        <v>-3.1866790364167286E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>5.3/1000</f>
-        <v>5.3E-3</v>
+        <f>5.71/1000</f>
+        <v>5.7099999999999998E-3</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>26.5</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -3361,22 +3361,22 @@
         <v>1406.91</v>
       </c>
       <c r="D71" s="24">
-        <v>1284.5587937903999</v>
+        <v>1285.66233170286</v>
       </c>
       <c r="E71" s="3">
         <f t="shared" si="0"/>
-        <v>-8.696448686099334E-2</v>
+        <v>-8.6180116920869243E-2</v>
       </c>
       <c r="F71" s="4">
-        <f>11.03/1000</f>
-        <v>1.103E-2</v>
+        <f>12.24/1000</f>
+        <v>1.2240000000000001E-2</v>
       </c>
       <c r="G71" s="1">
         <v>5000</v>
       </c>
       <c r="H71" s="6">
         <f t="shared" si="1"/>
-        <v>55.15</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0F8E82-F678-4A91-8FCB-229676CF3EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35109EC9-9756-47C8-A594-4CC06C5871B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/benchmarks.xlsx
+++ b/benchmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Academia\Research\dev\VRP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35109EC9-9756-47C8-A594-4CC06C5871B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6405008B-93DA-4EBE-B61D-078E7D8245E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="88">
   <si>
     <t>Best known</t>
   </si>
@@ -299,10 +299,7 @@
     <t>                    :swapcustomers!</t>
   </si>
   <si>
-    <t>MersenneTwister(1104); MersenneTwister(1234); MersenneTwister(1403); MersenneTwister(2104); MersenneTwister(2109)</t>
-  </si>
-  <si>
-    <t>MersenneTwister(1104); MersenneTwister(1234); MersenneTwister(1403); MersenneTwister(2104); MersenneTwister(2111)</t>
+    <t>MersenneTwister(1104); MersenneTwister(2104); MersenneTwister(2806); MersenneTwister(1010); MersenneTwister(2111)</t>
   </si>
 </sst>
 </file>
@@ -1528,15 +1525,15 @@
         <v>-5.3958025929146114E-4</v>
       </c>
       <c r="F66" s="5">
-        <f>3.41/1000</f>
-        <v>3.4100000000000003E-3</v>
+        <f>3.44/1000</f>
+        <v>3.4399999999999999E-3</v>
       </c>
       <c r="G66" s="1">
         <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f>F66 * G66</f>
-        <v>17.05</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -1550,22 +1547,22 @@
         <v>3055.23</v>
       </c>
       <c r="D67" s="26">
-        <v>3104.6502215696901</v>
+        <v>3127.0184374894502</v>
       </c>
       <c r="E67" s="3">
         <f>D67/C67-1</f>
-        <v>1.6175614133695282E-2</v>
+        <v>2.3496901211840004E-2</v>
       </c>
       <c r="F67" s="4">
-        <f>8.96/1000</f>
-        <v>8.9600000000000009E-3</v>
+        <f>9.2/1000</f>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" ref="H67:H70" si="0">F67 * G67</f>
-        <v>44.800000000000004</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -1579,22 +1576,22 @@
         <v>1395.85</v>
       </c>
       <c r="D68" s="25">
-        <v>1326.80755286926</v>
+        <v>1330.5249808926301</v>
       </c>
       <c r="E68" s="3">
         <f>D68/C68-1</f>
-        <v>-4.9462655106737752E-2</v>
+        <v>-4.6799454889400627E-2</v>
       </c>
       <c r="F68" s="4">
-        <f>12.13/1000</f>
-        <v>1.213E-2</v>
+        <f>12.72/1000</f>
+        <v>1.272E-2</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="0"/>
-        <v>60.65</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -1608,11 +1605,11 @@
         <v>38684</v>
       </c>
       <c r="D69" s="25">
-        <v>40802.580041417299</v>
+        <v>40826.732204664899</v>
       </c>
       <c r="E69" s="3">
         <f>D69/C69-1</f>
-        <v>5.4766312724053856E-2</v>
+        <v>5.5390657756821948E-2</v>
       </c>
       <c r="F69" s="4">
         <f>17.95/1000</f>
@@ -1637,22 +1634,22 @@
         <v>21736</v>
       </c>
       <c r="D70" s="26">
-        <v>22782.558751227101</v>
+        <v>22538.6179842979</v>
       </c>
       <c r="E70" s="3">
         <f>D70/C70-1</f>
-        <v>4.8148635960024944E-2</v>
+        <v>3.6925744584923592E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>23.75/1000</f>
-        <v>2.375E-2</v>
+        <f>23.66/1000</f>
+        <v>2.366E-2</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="0"/>
-        <v>118.75</v>
+        <v>118.3</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -2413,7 +2410,7 @@
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -3216,22 +3213,22 @@
         <v>1645.79</v>
       </c>
       <c r="D66" s="6">
-        <v>1644.77986458692</v>
+        <v>1644.5618805464301</v>
       </c>
       <c r="E66" s="3">
         <f>D66/C66-1</f>
-        <v>-6.1376932238010884E-4</v>
+        <v>-7.4621880894276682E-4</v>
       </c>
       <c r="F66" s="5">
-        <f>5.53/1000</f>
-        <v>5.5300000000000002E-3</v>
+        <f>5.32/1000</f>
+        <v>5.3200000000000001E-3</v>
       </c>
       <c r="G66" s="1">
         <v>5000</v>
       </c>
       <c r="H66" s="6">
         <f>F66 * G66</f>
-        <v>27.650000000000002</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -3245,22 +3242,22 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="D67" s="24">
-        <v>1177.53321827185</v>
+        <v>1177.2791490555001</v>
       </c>
       <c r="E67" s="3">
         <f t="shared" ref="E67:E71" si="0">D67/C67-1</f>
-        <v>-5.9756127764278855E-2</v>
+        <v>-5.9958998494454407E-2</v>
       </c>
       <c r="F67" s="4">
-        <f>14.98/1000</f>
-        <v>1.498E-2</v>
+        <f>13.54/1000</f>
+        <v>1.354E-2</v>
       </c>
       <c r="G67" s="1">
         <v>5000</v>
       </c>
       <c r="H67" s="6">
         <f t="shared" ref="H67:H71" si="1">F67 * G67</f>
-        <v>74.900000000000006</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -3281,15 +3278,15 @@
         <v>-3.7795946487007015E-6</v>
       </c>
       <c r="F68" s="4">
-        <f>6.55/1000</f>
-        <v>6.5499999999999994E-3</v>
+        <f>6.46/1000</f>
+        <v>6.4599999999999996E-3</v>
       </c>
       <c r="G68" s="1">
         <v>5000</v>
       </c>
       <c r="H68" s="6">
         <f t="shared" si="1"/>
-        <v>32.75</v>
+        <v>32.299999999999997</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -3310,15 +3307,15 @@
         <v>-5.8207596321802058E-6</v>
       </c>
       <c r="F69" s="4">
-        <f>20.3/1000</f>
-        <v>2.0300000000000002E-2</v>
+        <f>21.19/1000</f>
+        <v>2.1190000000000001E-2</v>
       </c>
       <c r="G69" s="1">
         <v>5000</v>
       </c>
       <c r="H69" s="6">
         <f t="shared" si="1"/>
-        <v>101.50000000000001</v>
+        <v>105.95</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -3332,22 +3329,22 @@
         <v>1696.94</v>
       </c>
       <c r="D70" s="6">
-        <v>1642.86396875943</v>
+        <v>1646.16818325903</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="0"/>
-        <v>-3.1866790364167286E-2</v>
+        <v>-2.9919629887308896E-2</v>
       </c>
       <c r="F70" s="4">
-        <f>5.71/1000</f>
-        <v>5.7099999999999998E-3</v>
+        <f>5.57/1000</f>
+        <v>5.5700000000000003E-3</v>
       </c>
       <c r="G70" s="1">
         <v>5000</v>
       </c>
       <c r="H70" s="6">
         <f t="shared" si="1"/>
-        <v>28.55</v>
+        <v>27.85</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -3361,22 +3358,22 @@
         <v>1406.91</v>
       </c>
       <c r="D71" s="24">
-        <v>1285.66233170286</v>
+        <v>1291.8230969117001</v>
       </c>
       <c r="E71" s="3">
         <f t="shared" si="0"/>
-        <v>-8.6180116920869243E-2</v>
+        <v>-8.1801183507331676E-2</v>
       </c>
       <c r="F71" s="4">
-        <f>12.24/1000</f>
-        <v>1.2240000000000001E-2</v>
+        <f>12.01/1000</f>
+        <v>1.201E-2</v>
       </c>
       <c r="G71" s="1">
         <v>5000</v>
       </c>
       <c r="H71" s="6">
         <f t="shared" si="1"/>
-        <v>61.2</v>
+        <v>60.05</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
